--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/aeu.00037_19470820/aeu.00037_19470820.4.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y301"/>
+  <dimension ref="A1:Y197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\aeu.00037_19470820\aeu.00037_19470820.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: r Ã© colte</t>
+          <t>L89: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: (276, 000, 000)； orge, 144, 600, 000 (145, 000,-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Un deuxiÃ¨me groupe</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]La Survivance</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]La Survivance</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L7: isolated marker/symbol line :: 2</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -649,12 +653,12 @@
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr">
         <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: La retraite prÃ©e par le R.P. Mor-</t>
+          <t>L198: abbreviation/spacing may be garbled :: La retraite prée par le R.P. Mor-</t>
         </is>
       </c>
       <c r="W2" s="1" t="inlineStr">
         <is>
-          <t>L56: abbreviation/spacing may be garbled :: terdam Ã bord du M.S. "Tabinta" le 2</t>
+          <t>L56: abbreviation/spacing may be garbled :: terdam à bord du M.S. "Tabinta" le 2</t>
         </is>
       </c>
       <c r="X2" s="1" t="inlineStr"/>
@@ -673,7 +677,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>736</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -692,12 +696,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: c Ã© r Ã© ales</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 700,000 (55,000,000)；orge,40,500,000 (48,-,-</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+00A8 DIAERESIS :: MontrÃ©al. â€” Le deuxiÃ¨me convoi</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -737,7 +741,7 @@
       </c>
       <c r="W3" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: La retraite prÃªchÃ©e par le R.P. Mor-</t>
+          <t>L148: abbreviation/spacing may be garbled :: La retraite prêchée par le R.P. Mor-</t>
         </is>
       </c>
       <c r="X3" s="1" t="inlineStr"/>
@@ -756,7 +760,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
@@ -775,12 +779,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: niÃ¨re, sa premiÃ¨re estimation du ren-</t>
+          <t>L98: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 000,000(46000000)；seigle,8252,000(3,-,-</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Production de cÃ©rÃ©ales dans les</t>
+          <t>L557: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -816,7 +820,7 @@
       </c>
       <c r="W4" s="1" t="inlineStr">
         <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: le R.P. L. Nadeau, qui a Ã©tÃ© ici, durant</t>
+          <t>L236: abbreviation/spacing may be garbled :: le R.P. L. Nadeau, qui a été ici, durant</t>
         </is>
       </c>
       <c r="X4" s="1" t="inlineStr"/>
@@ -830,12 +834,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>228</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>89</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -844,24 +848,20 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>L323: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e Ã© stage) Edmonton</t>
+          <t>L323: suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e é stage) Edmonton</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e Ã©tage) Edmonton</t>
+          <t>L720: suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e étage) Edmonton</t>
         </is>
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dement des principales cultures de c Ã©-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: La premiÃ¨re estimation de la produc-</t>
-        </is>
-      </c>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 000,000)； avoine,73,200,000 (104,000,-,-</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -928,19 +928,15 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | suspicious token(s): ont1 (letter/digit mix) :: prÃ¨s de Paris. Ces scouts italiens ont1</t>
+          <t>L726: suspicious token(s): ont1 (letter/digit mix) :: près de Paris. Ces scouts italiens ont1</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dentes, la premi estimation des r Ã©-</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L19: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tion de cÃ©rÃ©ales des provinces des Prai-</t>
-        </is>
-      </c>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: 000);orge,54,100,000(51,000,000)； seigle,</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -962,7 +958,7 @@
       <c r="V6" s="1" t="inlineStr"/>
       <c r="W6" s="1" t="inlineStr">
         <is>
-          <t>L449: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: tiÃ¨re d'Ã©tudes religieuses et sociales pour nualt, o.m.i., missionnaire de MontrÃ©al,</t>
+          <t>L449: abbreviation/spacing may be garbled :: tière d'études religieuses et sociales pour nualt, o.m.i., missionnaire de Montréal,</t>
         </is>
       </c>
       <c r="X6" s="1" t="inlineStr"/>
@@ -990,7 +986,7 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr">
         <is>
-          <t>L326: suspicious token(s): 0rge (letter/digit mix) :: 069,000)ï¼›0rge,154,554,000(159,887,000););</t>
+          <t>L326: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 0rge (letter/digit mix) :: 069,000)；0rge,154,554,000(159,887,000););</t>
         </is>
       </c>
       <c r="I7" s="1" t="inlineStr">
@@ -1000,14 +996,10 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: coltes de cÃ©rÃ©ales Ã©tait publiÃ©e en sep-</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: thÃ¨ses: Les trois provinces: BlÃ© 336,000,-</t>
-        </is>
-      </c>
+          <t>L172: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1029,7 +1021,7 @@
       <c r="V7" s="1" t="inlineStr"/>
       <c r="W7" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: | Mgr Langlois, o.m.i., notre Ã©vÃªque,</t>
+          <t>L484: abbreviation/spacing may be garbled :: | Mgr Langlois, o.m.i., notre évêque,</t>
         </is>
       </c>
       <c r="X7" s="1" t="inlineStr"/>
@@ -1067,14 +1059,10 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: estimations sont bas Ã© es sur des rap-!</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: BlÃ©, 50,000,000 (61,000,000); avoine, 40,-</t>
-        </is>
-      </c>
+          <t>L271: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1096,7 +1084,7 @@
       <c r="V8" s="1" t="inlineStr"/>
       <c r="W8" s="1" t="inlineStr">
         <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | abbreviation/spacing may be garbled :: PÃ¨re Gabriel Morvan, o.m.i.</t>
+          <t>L494: abbreviation/spacing may be garbled :: Père Gabriel Morvan, o.m.i.</t>
         </is>
       </c>
       <c r="X8" s="1" t="inlineStr"/>
@@ -1134,14 +1122,10 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bl Ã©</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000,000); segile, 677,000 (415,000); grai- sent de coeur aux Ã©loges, aux regrets et</t>
-        </is>
-      </c>
+          <t>L308: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1163,7 +1147,7 @@
       <c r="V9" s="1" t="inlineStr"/>
       <c r="W9" s="1" t="inlineStr">
         <is>
-          <t>L536: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: Une rÃ©union de J.E.C. fÃ©minine a</t>
+          <t>L536: abbreviation/spacing may be garbled :: Une réunion de J.E.C. féminine a</t>
         </is>
       </c>
       <c r="X9" s="1" t="inlineStr"/>
@@ -1177,12 +1161,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1196,19 +1180,15 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 109e (letter/digit mix) :: 10330 - 109e rue TÃ©l. 24165</t>
+          <t>L853: suspicious token(s): 109e (letter/digit mix) :: 10330 - 109e rue Tél. 24165</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La r Ã© colte de bl Ã© pour tout le Canada</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: aux priÃ¨res de ses parents et de ses!</t>
-        </is>
-      </c>
+          <t>L326: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): 0rge (letter/digit mix) :: 069,000)；0rge,154,554,000(159,887,000););</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1249,7 +1229,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1268,14 +1248,10 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: en 1947 est estimÃ©e Ã 358,786,000 bois-</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: fidÃ¨les paroissiens.</t>
-        </is>
-      </c>
+          <t>L445: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1311,7 +1287,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>193</t>
+          <t>196</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1330,19 +1306,15 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L936: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 124e (letter/digit mix) :: RÃ©sidence 10248-124e rue TÃ©l. 84691</t>
+          <t>L936: suspicious token(s): 124e (letter/digit mix) :: Résidence 10248-124e rue Tél. 84691</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L31: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rendement revis Ã© de 17.5 boisseaux par</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Estimation de la rÃ©colte de</t>
-        </is>
-      </c>
+          <t>L457: stray/suspicious non-ASCII glyph(s): U+4E8C CJK UNIFIED IDEOGRAPH-4E8C :: 二 4</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1398,14 +1370,10 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L34: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: par acre. La r Ã© colte courante sera prise</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cÃ©rÃ©ales au Canada en 1947</t>
-        </is>
-      </c>
+          <t>L538: stray/suspicious non-ASCII glyph(s): U+706B CJK UNIFIED IDEOGRAPH-706B | isolated marker/symbol line :: 火</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1461,14 +1429,10 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'une superficie ensemenc Ã© e estimative</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: deuil de Morinville ont Ã©tÃ© vivement dâ€™immigrants hollandais annoncÃ© il y a</t>
-        </is>
-      </c>
+          <t>L560: stray/suspicious non-ASCII glyph(s): U+00F7 DIVISION SIGN | isolated marker/symbol line :: ÷</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1520,14 +1484,10 @@
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L37: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production pr Ã© vue de bl Ã© dans les</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©jÃ quelque temps arrivera au Canada</t>
-        </is>
-      </c>
+          <t>L561: stray/suspicious non-ASCII glyph(s): U+00F7 DIVISION SIGN | isolated marker/symbol line :: ÷</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1579,14 +1539,10 @@
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le rendement moyen pr Ã© vu de bl Ã© dans</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: diocÃ¨se. Par ses fonctions de doyen de</t>
-        </is>
-      </c>
+          <t>L667: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1638,14 +1594,10 @@
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L41: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: les provinces des Prairies cette ann Ã© e</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la rÃ©gion, 1'llustre prÃ©lat appartenait</t>
-        </is>
-      </c>
+          <t>L701: stray/suspicious non-ASCII glyph(s): U+FF21 FULLWIDTH LATIN CAPITAL LETTER A, U+FF36 FULLWIDTH LATIN CAPITAL LETTER V, U+FF33 FULLWIDTH LATIN CAPITAL LETTER S :: ＡＶ I Ｓ</t>
+        </is>
+      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1685,14 +1637,10 @@
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000 boisseaux inf Ã© rieure a celle de l'an</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: coup Ã tous les Canadiens. AprÃ¨s, cin-</t>
-        </is>
-      </c>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1728,14 +1676,10 @@
       <c r="I19" s="1" t="inlineStr"/>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et Ã© en partie contre-balanc Ã© es par une</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: quante ans de ministÃ¨re, ses oeuvres lui</t>
-        </is>
-      </c>
+          <t>L845: stray/suspicious non-ASCII glyph(s): U+6211 CJK UNIFIED IDEOGRAPH-6211 | isolated marker/symbol line :: 我</t>
+        </is>
+      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1771,14 +1715,10 @@
       <c r="I20" s="1" t="inlineStr"/>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: augmentation marqu Ã© e en Saskatche-</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: ou en hÃ©ritage une paroisse modÃ¨le. Les</t>
-        </is>
-      </c>
+          <t>L911: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
+        </is>
+      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1812,16 +1752,8 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: eside production cette annÃ©e proviennent</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L52: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: prÃªtres et les citoyens de Legal sâ€™unis-</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1855,21 +1787,13 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des deux vari Ã© t Ã© s de seigle, ainsi qu'une</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: septembre. Attendus Ã QuÃ©bec le 12</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: ***</t>
+          <t>L172: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1898,21 +1822,13 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: augmentation appr Ã© ciable du rendement</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: taines formalitÃ©s d'immigration, ils dÃ©-</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: :</t>
+          <t>L180: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1941,21 +1857,13 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: g Ã© n Ã© rale. La Saskatchewan et I'Alberta</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: barqueront Ã MontrÃ©al le 13 d'oÃ¹ ils se</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L182: isolated marker/symbol line :: *</t>
+          <t>L181: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -1984,21 +1892,13 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des acr Ã© ages ensemenc Ã© s dans les trois</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: '000 boisseaux infÃ©rieure Ã celle de l'an</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: *</t>
+          <t>L182: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2027,21 +1927,13 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tre-balance Ã© la baisse du rendement par</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©tÃ© en partie contre-balancÃ©es par une</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L209: isolated marker/symbol line :: *</t>
+          <t>L183: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2070,21 +1962,13 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: Premi Ã¨ re estimation de la r Ã© colte</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: Ottawa. â€” Le Bureau fÃ©dÃ©ral de la acre en</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L210: isolated marker/symbol line :: *</t>
+          <t>L209: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2113,21 +1997,13 @@
       <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L72: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de c Ã© r Ã© ales</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Statistique a publiÃ©, la semaine der-</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L211: isolated marker/symbol line :: *</t>
+          <t>L210: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2156,21 +2032,13 @@
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L73: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production totale de la r Ã© colte des</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L212: isolated marker/symbol line :: *</t>
+          <t>L211: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2199,21 +2067,13 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L74: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: principales c Ã© ales au Canada en 1947</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: niÃ¨re, sa premiÃ¨re estimation du ren-</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L213: isolated marker/symbol line :: *</t>
+          <t>L212: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2242,21 +2102,13 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: parnÃ¨se Ã¨ ses: Bl Ã© d'automne 19, 090, 000</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dement des principales cultures de cÃ©-</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L253: isolated marker/symbol line :: ***</t>
+          <t>L213: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2285,26 +2137,18 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: (16,274,000); blÃ© de printemps, 339,696,-,-,-</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: rÃ©ales, de foin et trÃ¨fle, et de luzerne</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L254: isolated marker/symbol line :: *</t>
+          <t>L253: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L557: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2328,21 +2172,13 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Production de c Ã© r Ã© ales dans les</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: au Canada, en 1947. Les annÃ©es prÃ©cÃ©-</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L255: isolated marker/symbol line :: *</t>
+          <t>L254: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2371,21 +2207,13 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ses: Les trois provinces: BlÃ© 336,000,-,-</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: dentes, la premiÃ¨re estimation des rÃ©-</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L256: isolated marker/symbol line :: *</t>
+          <t>L255: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2414,21 +2242,13 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: BlÃ©,50,000,000 (61,000000);avoine,40,-,-</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L88: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: coltes de cÃ©rÃ©ales Ã©tait publiÃ©e en sep-</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L267: isolated marker/symbol line :: 1</t>
+          <t>L256: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2457,21 +2277,13 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chewan: BlÃ©, 183,000,000 (208,000,000););</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L92: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: effectuÃ© cette annÃ©e en vue d'amÃ©liorer augmentation marquÃ©e en Saskatche-</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L267: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2500,21 +2312,13 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000). Alberta: BlÃ©, 103,000000 (131,000,-,-</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'opportunitÃ© des rapports agricoles du wan et en Alberta. Les augmentations</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L275: isolated marker/symbol line :: :</t>
+          <t>L271: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2543,21 +2347,13 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Vancouver, ont visit Ã© leurs fils Paul et</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bureau et les estimations ici donnÃ©es de production cette annÃ©e proviennent</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L286: isolated marker/symbol line :: '</t>
+          <t>L275: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2586,21 +2382,13 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Ia paroisse, derniÃ¨rement.</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L95: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: sont sujettes Ã revision Ã la lumiÃ¨re de plus vastes superficies ensemencÃ©es,</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L286: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
@@ -2629,21 +2417,13 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: ne derni Ã¨ re, la visite de ses deux frÃ¨res</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des conditions rÃ©elles de la moisson. Les Seigle</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L351: isolated marker/symbol line :: 1</t>
+          <t>L308: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
@@ -2672,21 +2452,13 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L112: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la province de Qu Ã© bec, M. Godefroid</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: estimations sont basÃ©es sur des rap- La production globale de seigle dâ€™au-</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L351: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
@@ -2715,21 +2487,13 @@
       <c r="G42" s="1" t="inlineStr"/>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr">
-        <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Tardif et le R Ã© v. Frere Shephen, des</t>
-        </is>
-      </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: travers le Canada et sur des renseigne- estimÃ©e Ã 14,906,000 boisseaux, augmen-</t>
-        </is>
-      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L369: isolated marker/symbol line :: :</t>
+          <t>L368: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
@@ -2758,21 +2522,13 @@
       <c r="G43" s="1" t="inlineStr"/>
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ecoles Chr Ã© tiennes de Montreal. M. et</t>
-        </is>
-      </c>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: diverses provinces. 1 plus grandes superficies ensemencÃ©es</t>
-        </is>
-      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L370: isolated marker/symbol line :: *</t>
+          <t>L369: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
@@ -2801,21 +2557,13 @@
       <c r="G44" s="1" t="inlineStr"/>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Tardif ont accompagnÃ© leurs visites-</t>
-        </is>
-      </c>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des deux variÃ©tÃ©s de seigle, ainsi qu'une</t>
-        </is>
-      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L371: isolated marker/symbol line :: *</t>
+          <t>L370: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
@@ -2844,21 +2592,13 @@
       <c r="G45" s="1" t="inlineStr"/>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr">
-        <is>
-          <t>L128: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et anciens ves Ã© taient heureux de les</t>
-        </is>
-      </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L106: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: BlÃ©- augmentation apprÃ©ciable du rendement</t>
-        </is>
-      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L372: isolated marker/symbol line :: *</t>
+          <t>L371: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
@@ -2887,21 +2627,13 @@
       <c r="G46" s="1" t="inlineStr"/>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr">
-        <is>
-          <t>L133: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: diocÃ¨se. Par ses fonctions de doyen de</t>
-        </is>
-      </c>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La rÃ©colte de blÃ© pour tout le Canada par acre du seigle d'automne, sont les</t>
-        </is>
-      </c>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L373: isolated marker/symbol line :: *</t>
+          <t>L372: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
@@ -2930,21 +2662,13 @@
       <c r="G47" s="1" t="inlineStr"/>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr">
-        <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: la r Ã© gion, l'llustre pr Ã© lat appartenait</t>
-        </is>
-      </c>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: en 1947 est estimÃ©e Ã 358,786,000 bois- principaux facteurs de l'augmentation</t>
-        </is>
-      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L378: isolated marker/symbol line :: *</t>
+          <t>L373: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
@@ -2973,21 +2697,13 @@
       <c r="G48" s="1" t="inlineStr"/>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr">
-        <is>
-          <t>L139: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ou en h Ã© ritage une paroisse mod. Les</t>
-        </is>
-      </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: seaux, soit environ 62,000,000 de bois- gÃ©nÃ©rale. La Saskatchewan et l'Alberta</t>
-        </is>
-      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L379: isolated marker/symbol line :: **</t>
+          <t>L378: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
@@ -3016,21 +2732,13 @@
       <c r="G49" s="1" t="inlineStr"/>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tres et les citoyens de Legal sâ€™unis-sent-</t>
-        </is>
-      </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L115: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: "VÃ©rifiÃ©e"/</t>
-        </is>
-      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L380: isolated marker/symbol line :: *</t>
+          <t>L379: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
@@ -3059,21 +2767,13 @@
       <c r="G50" s="1" t="inlineStr"/>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: aux priÃ¨res de ses parents et de ses</t>
-        </is>
-      </c>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: chewan: BlÃ©, 183,000,000 (208,000,000);</t>
-        </is>
-      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L381: isolated marker/symbol line :: *</t>
+          <t>L380: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
@@ -3102,21 +2802,13 @@
       <c r="G51" s="1" t="inlineStr"/>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr">
-        <is>
-          <t>L150: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Filles de J Ã© sus, se sont rencontr a</t>
-        </is>
-      </c>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L124: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000). Alberta: BlÃ©, 103,000,000 (131,000,-</t>
-        </is>
-      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L382: isolated marker/symbol line :: *</t>
+          <t>L381: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
@@ -3145,21 +2837,13 @@
       <c r="G52" s="1" t="inlineStr"/>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: beth, sup Ã© rieure Ã Vimy, tait ses 25</t>
-        </is>
-      </c>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L134: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Filles de JÃ©sus, se sont rencontrÃ©es Ã</t>
-        </is>
-      </c>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L386: isolated marker/symbol line :: *</t>
+          <t>L382: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
@@ -3188,21 +2872,13 @@
       <c r="G53" s="1" t="inlineStr"/>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Edouard Massie Ã© taient de la</t>
-        </is>
-      </c>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L137: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: beth, supÃ©rieure Ã Vimy, fÃªtait ses 25</t>
-        </is>
-      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L387: isolated marker/symbol line :: X</t>
+          <t>L386: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
@@ -3231,21 +2907,13 @@
       <c r="G54" s="1" t="inlineStr"/>
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr">
-        <is>
-          <t>L172: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ç±³</t>
-        </is>
-      </c>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Edouard Massie Ã©taient de la</t>
-        </is>
-      </c>
+      <c r="J54" s="1" t="inlineStr"/>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L388: isolated marker/symbol line :: *</t>
+          <t>L387: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
@@ -3274,21 +2942,13 @@
       <c r="G55" s="1" t="inlineStr"/>
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: a Windsor, en voyage d'affaires, sa m Ã¨ re</t>
-        </is>
-      </c>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: La retraite prÃªchÃ©e par le R.P. Mor-</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="inlineStr"/>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L389: isolated marker/symbol line :: *</t>
+          <t>L388: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
@@ -3317,21 +2977,13 @@
       <c r="G56" s="1" t="inlineStr"/>
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr">
-        <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rhode-Island, accompagn Ã© de son e-</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L149: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: van s'est terminÃ©e samedi soir, le 9</t>
-        </is>
-      </c>
+      <c r="J56" s="1" t="inlineStr"/>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L390: isolated marker/symbol line :: *</t>
+          <t>L389: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
@@ -3360,21 +3012,13 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr">
-        <is>
-          <t>L184: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Un deuxi Ã¨ me groupe</t>
-        </is>
-      </c>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L151: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: rÃ©guliÃ¨rement et tous ceux qui eurent</t>
-        </is>
-      </c>
+      <c r="J57" s="1" t="inlineStr"/>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L391: isolated marker/symbol line :: *</t>
+          <t>L390: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
@@ -3403,21 +3047,13 @@
       <c r="G58" s="1" t="inlineStr"/>
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr">
-        <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Montr Ã© al.</t>
-        </is>
-      </c>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'avantage d'entendre la chaude prÃ©di-</t>
-        </is>
-      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L395: isolated marker/symbol line :: *</t>
+          <t>L391: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
@@ -3446,21 +3082,13 @@
       <c r="G59" s="1" t="inlineStr"/>
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr">
-        <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A8 DIAERESIS :: â€” Le deuxiÃ¨me convai</t>
-        </is>
-      </c>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: cation du RÃ©v. PÃ¨re, en ont retirÃ©, pour</t>
-        </is>
-      </c>
+      <c r="J59" s="1" t="inlineStr"/>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L396: isolated marker/symbol line :: :</t>
+          <t>L395: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
@@ -3489,21 +3117,13 @@
       <c r="G60" s="1" t="inlineStr"/>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr">
-        <is>
-          <t>L188: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d Ã© j Ã quelque temps arrivera au Canada</t>
-        </is>
-      </c>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: une grande reconnaissance au R. PÃ¨re</t>
-        </is>
-      </c>
+      <c r="J60" s="1" t="inlineStr"/>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L397: isolated marker/symbol line :: *</t>
+          <t>L396: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
@@ -3532,21 +3152,13 @@
       <c r="G61" s="1" t="inlineStr"/>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: septembre. Attendus Ã Qu Ã© bec le 12</t>
-        </is>
-      </c>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L157: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: prÃ©dicateur pour le bien qu'il est venu</t>
-        </is>
-      </c>
+      <c r="J61" s="1" t="inlineStr"/>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L398: isolated marker/symbol line :: *</t>
+          <t>L397: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
@@ -3575,21 +3187,13 @@
       <c r="G62" s="1" t="inlineStr"/>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr">
-        <is>
-          <t>L195: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: barqueront Ã Montr Ã© al le 13 d'o Ã¹ ils se</t>
-        </is>
-      </c>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L158: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gÃ©nÃ©reusement semer dans la paroisse.</t>
-        </is>
-      </c>
+      <c r="J62" s="1" t="inlineStr"/>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L399: isolated marker/symbol line :: *</t>
+          <t>L398: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
@@ -3618,21 +3222,13 @@
       <c r="G63" s="1" t="inlineStr"/>
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr">
-        <is>
-          <t>L198: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: La retraite prÃ©e par le R.P. Mor-</t>
-        </is>
-      </c>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L164: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: -La forme la plus pure sous laquelle le tabac peut Ãªtre fumÃ©"</t>
-        </is>
-      </c>
+      <c r="J63" s="1" t="inlineStr"/>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L403: isolated marker/symbol line :: ***</t>
+          <t>L399: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3657,21 +3253,13 @@
       <c r="G64" s="1" t="inlineStr"/>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr">
-        <is>
-          <t>L201: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: r Ã© rement et tous ceux qui eurent</t>
-        </is>
-      </c>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Vancouver, ont visitÃ© leurs fils Paul et</t>
-        </is>
-      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L404: isolated marker/symbol line :: **</t>
+          <t>L403: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3696,21 +3284,13 @@
       <c r="G65" s="1" t="inlineStr"/>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr">
-        <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'avantage d'entendre la chaude prÃ©di</t>
-        </is>
-      </c>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: la paroisse, derniÃ¨rement.</t>
-        </is>
-      </c>
+      <c r="J65" s="1" t="inlineStr"/>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: *</t>
+          <t>L404: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3735,21 +3315,13 @@
       <c r="G66" s="1" t="inlineStr"/>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr">
-        <is>
-          <t>L203: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: cation du R Ã© v. P Ã¨ re, en ont retir Ã©, pour</t>
-        </is>
-      </c>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L182: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: ne derniÃ¨re, la visite de ses deux frÃ¨res</t>
-        </is>
-      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L408: isolated marker/symbol line :: ***</t>
+          <t>L405: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3774,21 +3346,13 @@
       <c r="G67" s="1" t="inlineStr"/>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr">
-        <is>
-          <t>L207: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pr Ã© dicateur pour le bien qu'il est venu</t>
-        </is>
-      </c>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L183: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la province de QuÃ©bec, M. Godefroid</t>
-        </is>
-      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L409: isolated marker/symbol line :: **</t>
+          <t>L408: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3813,21 +3377,13 @@
       <c r="G68" s="1" t="inlineStr"/>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr">
-        <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: g Ã© n Ã© reusement semer dans la paroisse.</t>
-        </is>
-      </c>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L184: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Tardif et le RÃ©v. FrÃ¨re Shephen, des</t>
-        </is>
-      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L410: isolated marker/symbol line :: *</t>
+          <t>L409: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3852,21 +3408,13 @@
       <c r="G69" s="1" t="inlineStr"/>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr">
-        <is>
-          <t>L215: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: le dÃ©part prochain de notre bon curÃ©,</t>
-        </is>
-      </c>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ecoles ChrÃ©tiennes de MontrÃ©al. M. et</t>
-        </is>
-      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L414: isolated marker/symbol line :: ***</t>
+          <t>L410: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3891,21 +3439,13 @@
       <c r="G70" s="1" t="inlineStr"/>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr">
-        <is>
-          <t>L216: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: le R. P. L. Nadeau, qui a et Ã© ici, durant</t>
-        </is>
-      </c>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L186: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Tardif ont accompagnÃ© leurs visi-</t>
-        </is>
-      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L415: isolated marker/symbol line :: *</t>
+          <t>L414: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3930,21 +3470,13 @@
       <c r="G71" s="1" t="inlineStr"/>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: quatre brÃ¨ves annÃ©es, le conseiller mo-</t>
-        </is>
-      </c>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sa femme Ã©taient en visite chz M. Henri</t>
-        </is>
-      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L416: isolated marker/symbol line :: *</t>
+          <t>L415: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3969,21 +3501,13 @@
       <c r="G72" s="1" t="inlineStr"/>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr">
-        <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Falher. Nous n'h Ã© sitons pas Ã dire que</t>
-        </is>
-      </c>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L195: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: et anciens Ã©lÃ¨ves Ã©taient heureux de les</t>
-        </is>
-      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L417: isolated marker/symbol line :: *</t>
+          <t>L416: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4008,21 +3532,13 @@
       <c r="G73" s="1" t="inlineStr"/>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr">
-        <is>
-          <t>L223: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Dieu par son activit Ã© inlassable, par son</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ils Ã©taient en vacances depuis plus d'u-</t>
-        </is>
-      </c>
+      <c r="J73" s="1" t="inlineStr"/>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L422: isolated marker/symbol line :: ***</t>
+          <t>L417: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4047,21 +3563,13 @@
       <c r="G74" s="1" t="inlineStr"/>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr">
-        <is>
-          <t>L224: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d Ã© vouement constant a la grande cause</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L213: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. et Mme John Fitzgerald ont passÃ©</t>
-        </is>
-      </c>
+      <c r="J74" s="1" t="inlineStr"/>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L423: isolated marker/symbol line :: ***</t>
+          <t>L422: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4086,21 +3594,13 @@
       <c r="G75" s="1" t="inlineStr"/>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ide l 'Ã© glise paroissiale, Ã celle de l'ecole</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L215: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derniÃ¨re, en voyage d'affaires.</t>
-        </is>
-      </c>
+      <c r="J75" s="1" t="inlineStr"/>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L442: isolated marker/symbol line :: *</t>
+          <t>L423: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4125,21 +3625,13 @@
       <c r="G76" s="1" t="inlineStr"/>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr">
-        <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et de tous les paroissiens confi Ã© s a sa</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: passÃ© la fin de semaine derniÃ¨re en vil-</t>
-        </is>
-      </c>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L443: isolated marker/symbol line :: *</t>
+          <t>L442: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4164,21 +3656,13 @@
       <c r="G77" s="1" t="inlineStr"/>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr">
-        <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: juridiction. Tout cela, en d Ã© pit d'une</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: lÃ©giature au Lac Froid.</t>
-        </is>
-      </c>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L444: isolated marker/symbol line :: *</t>
+          <t>L443: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4203,21 +3687,13 @@
       <c r="G78" s="1" t="inlineStr"/>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr">
-        <is>
-          <t>L228: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sant Ã© fragile. Un Ã© v Ä“ que lui succ Ã© dera</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Mlle IrÃ¨ne Viel est de retour dans sa</t>
-        </is>
-      </c>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L454: isolated marker/symbol line :: ***</t>
+          <t>L444: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4242,21 +3718,13 @@
       <c r="G79" s="1" t="inlineStr"/>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr">
-        <is>
-          <t>L238: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et Mme Emile Dumas, baptis Ã© le 17</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Un hangar s'Ã©lÃ¨ve Ã l'est du village.</t>
-        </is>
-      </c>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L455: isolated marker/symbol line :: *</t>
+          <t>L445: stray/suspicious non-ASCII glyph(s): U+7C73 CJK UNIFIED IDEOGRAPH-7C73 | isolated marker/symbol line :: 米</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4281,21 +3749,13 @@
       <c r="G80" s="1" t="inlineStr"/>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>L241: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: fant, remplac Ã© s par M. et Mme Paul</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce sera l'abri de l'avion Ã M. le curÃ©</t>
-        </is>
-      </c>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
       <c r="L80" s="1" t="inlineStr"/>
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L456: isolated marker/symbol line :: *</t>
+          <t>L454: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4320,21 +3780,13 @@
       <c r="G81" s="1" t="inlineStr"/>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr">
-        <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. ElizÃ©e Ouellette et ses trois en-</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: le dÃ©part prochain de notre bon curÃ©,</t>
-        </is>
-      </c>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
       <c r="L81" s="1" t="inlineStr"/>
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L466: isolated marker/symbol line :: ***</t>
+          <t>L455: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4359,21 +3811,13 @@
       <c r="G82" s="1" t="inlineStr"/>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: fants ont termin Ã© leurs vacances et sont</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: le R.P. L. Nadeau, qui a Ã©tÃ© ici, durant</t>
-        </is>
-      </c>
+      <c r="J82" s="1" t="inlineStr"/>
+      <c r="K82" s="1" t="inlineStr"/>
       <c r="L82" s="1" t="inlineStr"/>
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L467: isolated marker/symbol line :: *</t>
+          <t>L456: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4398,21 +3842,13 @@
       <c r="G83" s="1" t="inlineStr"/>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: retourn Ã© s Ã Vancouver. M. Ouellette</t>
-        </is>
-      </c>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L237: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: quatre brÃ¨ves annÃ©es, le conseiller mo-</t>
-        </is>
-      </c>
+      <c r="J83" s="1" t="inlineStr"/>
+      <c r="K83" s="1" t="inlineStr"/>
       <c r="L83" s="1" t="inlineStr"/>
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L468: isolated marker/symbol line :: *</t>
+          <t>L466: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4437,21 +3873,13 @@
       <c r="G84" s="1" t="inlineStr"/>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: amÃ¨ne a avec lui sa vieille m Ã¨ re pour pas-</t>
-        </is>
-      </c>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L246: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: des acrÃ©ages ensemencÃ©s dans les trois</t>
-        </is>
-      </c>
+      <c r="J84" s="1" t="inlineStr"/>
+      <c r="K84" s="1" t="inlineStr"/>
       <c r="L84" s="1" t="inlineStr"/>
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L469: isolated marker/symbol line :: *</t>
+          <t>L467: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4476,21 +3904,13 @@
       <c r="G85" s="1" t="inlineStr"/>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr">
-        <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: qui sera tr Ã¨ s bien pour les enfants d 'Ã©-</t>
-        </is>
-      </c>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tre-balancÃ© la baisse du rendement par</t>
-        </is>
-      </c>
+      <c r="J85" s="1" t="inlineStr"/>
+      <c r="K85" s="1" t="inlineStr"/>
       <c r="L85" s="1" t="inlineStr"/>
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L492: isolated marker/symbol line :: *</t>
+          <t>L468: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4515,21 +3935,13 @@
       <c r="G86" s="1" t="inlineStr"/>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr">
-        <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cole. Esp Ã© rons qu'in sera rempli pour le</t>
-        </is>
-      </c>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: PremiÃ¨re estimation de la rÃ©colte</t>
-        </is>
-      </c>
+      <c r="J86" s="1" t="inlineStr"/>
+      <c r="K86" s="1" t="inlineStr"/>
       <c r="L86" s="1" t="inlineStr"/>
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: *</t>
+          <t>L469: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4554,21 +3966,13 @@
       <c r="G87" s="1" t="inlineStr"/>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr">
-        <is>
-          <t>L268: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " V Ã© rifi Ã© e "</t>
-        </is>
-      </c>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L253: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de cÃ©rÃ©ales</t>
-        </is>
-      </c>
+      <c r="J87" s="1" t="inlineStr"/>
+      <c r="K87" s="1" t="inlineStr"/>
       <c r="L87" s="1" t="inlineStr"/>
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L494: isolated marker/symbol line :: *</t>
+          <t>L492: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4593,21 +3997,13 @@
       <c r="G88" s="1" t="inlineStr"/>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr">
-        <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: deuil de Morinville ont Ã© t Ã© vivement d'immigrants hollandais annonc Ã© il y a</t>
-        </is>
-      </c>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L255: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production totale de la rÃ©colte des</t>
-        </is>
-      </c>
+      <c r="J88" s="1" t="inlineStr"/>
+      <c r="K88" s="1" t="inlineStr"/>
       <c r="L88" s="1" t="inlineStr"/>
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L508: isolated marker/symbol line :: T</t>
+          <t>L493: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4632,21 +4028,13 @@
       <c r="G89" s="1" t="inlineStr"/>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L256: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: principales cÃ©rÃ©ales au Canada en 1947</t>
-        </is>
-      </c>
+      <c r="J89" s="1" t="inlineStr"/>
+      <c r="K89" s="1" t="inlineStr"/>
       <c r="L89" s="1" t="inlineStr"/>
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L512: isolated marker/symbol line :: 1</t>
+          <t>L494: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4671,21 +4059,13 @@
       <c r="G90" s="1" t="inlineStr"/>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr">
-        <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Statistique a publi Ã©, la semaine der-des Prairies.</t>
-        </is>
-      </c>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: est actuellement estimÃ©e comme suit, en</t>
-        </is>
-      </c>
+      <c r="J90" s="1" t="inlineStr"/>
+      <c r="K90" s="1" t="inlineStr"/>
       <c r="L90" s="1" t="inlineStr"/>
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L513: isolated marker/symbol line :: *</t>
+          <t>L508: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4710,21 +4090,13 @@
       <c r="G91" s="1" t="inlineStr"/>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: rÃ©ales, de foin et trÃ¨fle, et de luzerne 154, 554, 000 boisseaux ou environ 5, 00,-</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: parnethÃ¨ses: BlÃ© d'automne 19,090,000</t>
-        </is>
-      </c>
+      <c r="J91" s="1" t="inlineStr"/>
+      <c r="K91" s="1" t="inlineStr"/>
       <c r="L91" s="1" t="inlineStr"/>
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L514: isolated marker/symbol line :: *</t>
+          <t>L512: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4749,21 +4121,13 @@
       <c r="G92" s="1" t="inlineStr"/>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: au Canada, en 1947. Les ann Ã© es pr Ã© ce- 000 boisseaux inf Ã© rieure Ã celle de lan</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: (16,274,000); blÃ© de printemps, 339,696,-</t>
-        </is>
-      </c>
+      <c r="J92" s="1" t="inlineStr"/>
+      <c r="K92" s="1" t="inlineStr"/>
       <c r="L92" s="1" t="inlineStr"/>
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L515: isolated marker/symbol line :: *</t>
+          <t>L513: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4788,21 +4152,13 @@
       <c r="G93" s="1" t="inlineStr"/>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr">
-        <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tembre. Le changement de politique est et Ã© en partie contre-balanc par une</t>
-        </is>
-      </c>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L261: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000 (404,451,000); tout blÃ©, 358,786,000</t>
-        </is>
-      </c>
+      <c r="J93" s="1" t="inlineStr"/>
+      <c r="K93" s="1" t="inlineStr"/>
       <c r="L93" s="1" t="inlineStr"/>
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: *</t>
+          <t>L514: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4827,21 +4183,13 @@
       <c r="G94" s="1" t="inlineStr"/>
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr">
-        <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: effectu Ã© cette ann Ã© e en vue d'ameliorer augmentation marqu en Saskatche-ne</t>
-        </is>
-      </c>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mÃ© comme suit, en boisseaux, avec</t>
-        </is>
-      </c>
+      <c r="J94" s="1" t="inlineStr"/>
+      <c r="K94" s="1" t="inlineStr"/>
       <c r="L94" s="1" t="inlineStr"/>
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L517: isolated marker/symbol line :: *</t>
+          <t>L515: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -4866,21 +4214,13 @@
       <c r="G95" s="1" t="inlineStr"/>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr">
-        <is>
-          <t>L278: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'opportunit Ã© des rapports agricoles du wan et en Alberta. Les augmentations</t>
-        </is>
-      </c>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L271: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: moyenne de 1946 entre parenthÃ¨ses: BlÃ©</t>
-        </is>
-      </c>
+      <c r="J95" s="1" t="inlineStr"/>
+      <c r="K95" s="1" t="inlineStr"/>
       <c r="L95" s="1" t="inlineStr"/>
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L521: isolated marker/symbol line :: ***</t>
+          <t>L516: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -4905,21 +4245,13 @@
       <c r="G96" s="1" t="inlineStr"/>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr">
-        <is>
-          <t>L279: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bureau et les estimations ici donn ide production cette ann Ã© e proviennent</t>
-        </is>
-      </c>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'automne, 26.8 (29.8); blÃ© de printemps,</t>
-        </is>
-      </c>
+      <c r="J96" s="1" t="inlineStr"/>
+      <c r="K96" s="1" t="inlineStr"/>
       <c r="L96" s="1" t="inlineStr"/>
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L522: isolated marker/symbol line :: *</t>
+          <t>L517: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -4944,21 +4276,13 @@
       <c r="G97" s="1" t="inlineStr"/>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: sont sujettes a revision a la lumi de plus vastes superficies ensemenc Ã© es.</t>
-        </is>
-      </c>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L273: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 14.7 (17.2); tout blÃ©, 15.0 (17.5); avoine,</t>
-        </is>
-      </c>
+      <c r="J97" s="1" t="inlineStr"/>
+      <c r="K97" s="1" t="inlineStr"/>
       <c r="L97" s="1" t="inlineStr"/>
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L523: isolated marker/symbol line :: *</t>
+          <t>L521: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -4983,21 +4307,13 @@
       <c r="G98" s="1" t="inlineStr"/>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr">
-        <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: travers le Canada et sur des renseigne Ã© e a 14, 906, 000 boisseaux, augmen-</t>
-        </is>
-      </c>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 26.2 (33.1); orge, 20.8 (25.5); seigle dâ€™au-</t>
-        </is>
-      </c>
+      <c r="J98" s="1" t="inlineStr"/>
+      <c r="K98" s="1" t="inlineStr"/>
       <c r="L98" s="1" t="inlineStr"/>
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L524: isolated marker/symbol line :: *</t>
+          <t>L522: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5022,21 +4338,13 @@
       <c r="G99" s="1" t="inlineStr"/>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr">
-        <is>
-          <t>L288: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production estimative de bl Ã© dans</t>
-        </is>
-      </c>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cÃ©s et d'un dÃ©clin des rendements par tomne, 14.0 (10.8); seigle de printemps,</t>
-        </is>
-      </c>
+      <c r="J99" s="1" t="inlineStr"/>
+      <c r="K99" s="1" t="inlineStr"/>
       <c r="L99" s="1" t="inlineStr"/>
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç�«</t>
+          <t>L523: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5061,21 +4369,13 @@
       <c r="G100" s="1" t="inlineStr"/>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: les autres provinces s 'Ã© l Ã¨ ve Ã 22, 786, 000</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sion de lâ€™Ile-Ã -la-Crosse.</t>
-        </is>
-      </c>
+      <c r="J100" s="1" t="inlineStr"/>
+      <c r="K100" s="1" t="inlineStr"/>
       <c r="L100" s="1" t="inlineStr"/>
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L539: isolated marker/symbol line :: *</t>
+          <t>L524: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5100,21 +4400,13 @@
       <c r="G101" s="1" t="inlineStr"/>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr">
-        <is>
-          <t>L291: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: soit 19,603,000, est prÃ©vue pour l'Ont.</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Ã Windsor, en voyage d'affaires, sa mÃ¨re</t>
-        </is>
-      </c>
+      <c r="J101" s="1" t="inlineStr"/>
+      <c r="K101" s="1" t="inlineStr"/>
       <c r="L101" s="1" t="inlineStr"/>
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L540: isolated marker/symbol line :: *</t>
+          <t>L538: stray/suspicious non-ASCII glyph(s): U+706B CJK UNIFIED IDEOGRAPH-706B | isolated marker/symbol line :: 火</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5139,21 +4431,13 @@
       <c r="G102" s="1" t="inlineStr"/>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr">
-        <is>
-          <t>L293: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cept Ã© 513, 000 boisseaux, est de ble d'au-</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: miÃ¨re fois, la visite de son frÃ¨re M.</t>
-        </is>
-      </c>
+      <c r="J102" s="1" t="inlineStr"/>
+      <c r="K102" s="1" t="inlineStr"/>
       <c r="L102" s="1" t="inlineStr"/>
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L541: isolated marker/symbol line :: :</t>
+          <t>L539: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5178,21 +4462,13 @@
       <c r="G103" s="1" t="inlineStr"/>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr">
-        <is>
-          <t>L296: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La r Ã© colte d'avoine en 1947 est estim</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L290: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Josaphat HÃ©bert, de West-Warwick,</t>
-        </is>
-      </c>
+      <c r="J103" s="1" t="inlineStr"/>
+      <c r="K103" s="1" t="inlineStr"/>
       <c r="L103" s="1" t="inlineStr"/>
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L548: isolated marker/symbol line :: ***</t>
+          <t>L540: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5217,21 +4493,13 @@
       <c r="G104" s="1" t="inlineStr"/>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr">
-        <is>
-          <t>L300: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'une diminution des acrÃ©ages ensemen-</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L291: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Rhode-Island, accompagnÃ© de son Ã©-</t>
-        </is>
-      </c>
+      <c r="J104" s="1" t="inlineStr"/>
+      <c r="K104" s="1" t="inlineStr"/>
       <c r="L104" s="1" t="inlineStr"/>
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L549: isolated marker/symbol line :: *</t>
+          <t>L541: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5256,21 +4524,13 @@
       <c r="G105" s="1" t="inlineStr"/>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr">
-        <is>
-          <t>L301: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ces et d'un dÃ©clin des rendements par</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L297: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: berley, Ã©taient en visite d'Ã©tÃ© chez</t>
-        </is>
-      </c>
+      <c r="J105" s="1" t="inlineStr"/>
+      <c r="K105" s="1" t="inlineStr"/>
       <c r="L105" s="1" t="inlineStr"/>
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L550: isolated marker/symbol line :: *</t>
+          <t>L548: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5295,21 +4555,13 @@
       <c r="G106" s="1" t="inlineStr"/>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr">
-        <is>
-          <t>L302: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Morin &amp; Fr Ã¨ res</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L303: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: revenus de voyage derniÃ¨rement; M.</t>
-        </is>
-      </c>
+      <c r="J106" s="1" t="inlineStr"/>
+      <c r="K106" s="1" t="inlineStr"/>
       <c r="L106" s="1" t="inlineStr"/>
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L551: isolated marker/symbol line :: *</t>
+          <t>L549: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5334,21 +4586,13 @@
       <c r="G107" s="1" t="inlineStr"/>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr">
-        <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© l Ã© phone 26405</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Jerry Fox et M. et Mme LÃ©onard Blan-</t>
-        </is>
-      </c>
+      <c r="J107" s="1" t="inlineStr"/>
+      <c r="K107" s="1" t="inlineStr"/>
       <c r="L107" s="1" t="inlineStr"/>
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L556: isolated marker/symbol line :: *</t>
+          <t>L550: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5373,21 +4617,13 @@
       <c r="G108" s="1" t="inlineStr"/>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr">
-        <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L306: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: framboise, M. et Mme AdÃ©lard De</t>
-        </is>
-      </c>
+      <c r="J108" s="1" t="inlineStr"/>
+      <c r="K108" s="1" t="inlineStr"/>
       <c r="L108" s="1" t="inlineStr"/>
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: :</t>
+          <t>L551: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5412,21 +4648,13 @@
       <c r="G109" s="1" t="inlineStr"/>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr">
-        <is>
-          <t>L317: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© l.21861</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L308: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bilodeau (Jeanne Mercier) rÃ©cemment</t>
-        </is>
-      </c>
+      <c r="J109" s="1" t="inlineStr"/>
+      <c r="K109" s="1" t="inlineStr"/>
       <c r="L109" s="1" t="inlineStr"/>
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L558: isolated marker/symbol line :: *</t>
+          <t>L556: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5451,21 +4679,13 @@
       <c r="G110" s="1" t="inlineStr"/>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr">
-        <is>
-          <t>L320: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Fabricants d 'Ã© tampes en caoutchouc</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mariÃ©s.</t>
-        </is>
-      </c>
+      <c r="J110" s="1" t="inlineStr"/>
+      <c r="K110" s="1" t="inlineStr"/>
       <c r="L110" s="1" t="inlineStr"/>
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L559: isolated marker/symbol line :: *</t>
+          <t>L557: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5490,21 +4710,13 @@
       <c r="G111" s="1" t="inlineStr"/>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr">
-        <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© phone 26927</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L316: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lefebvre Ã©pousera M. Arthur Laflamme</t>
-        </is>
-      </c>
+      <c r="J111" s="1" t="inlineStr"/>
+      <c r="K111" s="1" t="inlineStr"/>
       <c r="L111" s="1" t="inlineStr"/>
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: Ã·</t>
+          <t>L558: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5529,21 +4741,13 @@
       <c r="G112" s="1" t="inlineStr"/>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr">
-        <is>
-          <t>L323: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e Ã© stage) Edmonton</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L319: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La cÃ©rÃ©monie se fera Ã Saint-Joachim</t>
-        </is>
-      </c>
+      <c r="J112" s="1" t="inlineStr"/>
+      <c r="K112" s="1" t="inlineStr"/>
       <c r="L112" s="1" t="inlineStr"/>
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L561: isolated marker/symbol line :: Ã·</t>
+          <t>L559: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5568,21 +4772,13 @@
       <c r="G113" s="1" t="inlineStr"/>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr">
-        <is>
-          <t>L324: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 000 (404, 451, 000); tout bl Ã©, 358, 786, 000</t>
-        </is>
-      </c>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L325: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: de RÃ©millard), maintenant de Cold tions urgentes en vue de continuer leur prÃ©sidait ce pÃ¨lerinage avec l'aide de son</t>
-        </is>
-      </c>
+      <c r="J113" s="1" t="inlineStr"/>
+      <c r="K113" s="1" t="inlineStr"/>
       <c r="L113" s="1" t="inlineStr"/>
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L566: isolated marker/symbol line :: ***</t>
+          <t>L560: stray/suspicious non-ASCII glyph(s): U+00F7 DIVISION SIGN | isolated marker/symbol line :: ÷</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5607,21 +4803,13 @@
       <c r="G114" s="1" t="inlineStr"/>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr">
-        <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: m Ã© comme suit, en boisseaux, avec</t>
-        </is>
-      </c>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L326: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lake, ont fait baptiser leur premier-nÃ©</t>
-        </is>
-      </c>
+      <c r="J114" s="1" t="inlineStr"/>
+      <c r="K114" s="1" t="inlineStr"/>
       <c r="L114" s="1" t="inlineStr"/>
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L567: isolated marker/symbol line :: *</t>
+          <t>L561: stray/suspicious non-ASCII glyph(s): U+00F7 DIVISION SIGN | isolated marker/symbol line :: ÷</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5646,21 +4834,13 @@
       <c r="G115" s="1" t="inlineStr"/>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr">
-        <is>
-          <t>L333: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: moyenne de 1946 entre parenth: Bl Ã©</t>
-        </is>
-      </c>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L328: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Frank RÃ©millard ont Ã©tÃ© dans les hon-</t>
-        </is>
-      </c>
+      <c r="J115" s="1" t="inlineStr"/>
+      <c r="K115" s="1" t="inlineStr"/>
       <c r="L115" s="1" t="inlineStr"/>
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L568: isolated marker/symbol line :: *</t>
+          <t>L566: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5685,21 +4865,13 @@
       <c r="G116" s="1" t="inlineStr"/>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr"/>
-      <c r="J116" s="1" t="inlineStr">
-        <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'automne, 26.8 (29.8); blÃ© de printemps,</t>
-        </is>
-      </c>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>L332: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rendement rÃ©visÃ© de 17.5 boisseaux par</t>
-        </is>
-      </c>
+      <c r="J116" s="1" t="inlineStr"/>
+      <c r="K116" s="1" t="inlineStr"/>
       <c r="L116" s="1" t="inlineStr"/>
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L569: isolated marker/symbol line :: *</t>
+          <t>L567: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5724,21 +4896,13 @@
       <c r="G117" s="1" t="inlineStr"/>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr"/>
-      <c r="J117" s="1" t="inlineStr">
-        <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 14.7 (17.2);tout blÃ©, 15.0 (17.5); avoine,</t>
-        </is>
-      </c>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>L335: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: par acre. La rÃ©colte courante sera prise</t>
-        </is>
-      </c>
+      <c r="J117" s="1" t="inlineStr"/>
+      <c r="K117" s="1" t="inlineStr"/>
       <c r="L117" s="1" t="inlineStr"/>
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L579: isolated marker/symbol line :: **</t>
+          <t>L568: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5763,21 +4927,13 @@
       <c r="G118" s="1" t="inlineStr"/>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr"/>
-      <c r="J118" s="1" t="inlineStr">
-        <is>
-          <t>L361: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Place du MarchÃ©,</t>
-        </is>
-      </c>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>L336: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'une superficie ensemencÃ©e estimative</t>
-        </is>
-      </c>
+      <c r="J118" s="1" t="inlineStr"/>
+      <c r="K118" s="1" t="inlineStr"/>
       <c r="L118" s="1" t="inlineStr"/>
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L580: isolated marker/symbol line :: *</t>
+          <t>L569: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5802,21 +4958,13 @@
       <c r="G119" s="1" t="inlineStr"/>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr"/>
-      <c r="J119" s="1" t="inlineStr">
-        <is>
-          <t>L365: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Situ Ã© dans le centre des affaires</t>
-        </is>
-      </c>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. ElizÃ©e Ouellette et ses trois en-</t>
-        </is>
-      </c>
+      <c r="J119" s="1" t="inlineStr"/>
+      <c r="K119" s="1" t="inlineStr"/>
       <c r="L119" s="1" t="inlineStr"/>
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L581: isolated marker/symbol line :: *</t>
+          <t>L579: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5841,21 +4989,13 @@
       <c r="G120" s="1" t="inlineStr"/>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr"/>
-      <c r="J120" s="1" t="inlineStr">
-        <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
-        </is>
-      </c>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>L339: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: fants ont terminÃ© leurs vacances et sont</t>
-        </is>
-      </c>
+      <c r="J120" s="1" t="inlineStr"/>
+      <c r="K120" s="1" t="inlineStr"/>
       <c r="L120" s="1" t="inlineStr"/>
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L582: isolated marker/symbol line :: *</t>
+          <t>L580: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5880,21 +5020,13 @@
       <c r="G121" s="1" t="inlineStr"/>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr"/>
-      <c r="J121" s="1" t="inlineStr">
-        <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: derniÃ¨re, en voyage d'affaires.</t>
-        </is>
-      </c>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>L340: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: retournÃ©s Ã Vancouver. M. Ouellette</t>
-        </is>
-      </c>
+      <c r="J121" s="1" t="inlineStr"/>
+      <c r="K121" s="1" t="inlineStr"/>
       <c r="L121" s="1" t="inlineStr"/>
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L583: isolated marker/symbol line :: *</t>
+          <t>L581: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5919,21 +5051,13 @@
       <c r="G122" s="1" t="inlineStr"/>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr"/>
-      <c r="J122" s="1" t="inlineStr">
-        <is>
-          <t>L401: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: passÃ© la fin de semaine derniÃ¨re en vil-</t>
-        </is>
-      </c>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: amÃ¨ne avec lui sa vieille mÃ¨re pour pas-</t>
-        </is>
-      </c>
+      <c r="J122" s="1" t="inlineStr"/>
+      <c r="K122" s="1" t="inlineStr"/>
       <c r="L122" s="1" t="inlineStr"/>
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L589: isolated marker/symbol line :: ***</t>
+          <t>L582: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5958,21 +5082,13 @@
       <c r="G123" s="1" t="inlineStr"/>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr"/>
-      <c r="J123" s="1" t="inlineStr">
-        <is>
-          <t>L411: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Un hangar s'Ã©ve a l'est du village.</t>
-        </is>
-      </c>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans nos parages, est engagÃ©e pour faire</t>
-        </is>
-      </c>
+      <c r="J123" s="1" t="inlineStr"/>
+      <c r="K123" s="1" t="inlineStr"/>
       <c r="L123" s="1" t="inlineStr"/>
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L590: isolated marker/symbol line :: ***</t>
+          <t>L583: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5997,21 +5113,13 @@
       <c r="G124" s="1" t="inlineStr"/>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr"/>
-      <c r="J124" s="1" t="inlineStr">
-        <is>
-          <t>L412: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ce sera l'abri de l'avion Ã M. le cur Ã©</t>
-        </is>
-      </c>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: qui sera trÃ¨s bien pour les enfants d'Ã©-</t>
-        </is>
-      </c>
+      <c r="J124" s="1" t="inlineStr"/>
+      <c r="K124" s="1" t="inlineStr"/>
       <c r="L124" s="1" t="inlineStr"/>
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L613: isolated marker/symbol line :: *</t>
+          <t>L589: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -6036,21 +5144,13 @@
       <c r="G125" s="1" t="inlineStr"/>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr"/>
-      <c r="J125" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Une r Ã© union de J. E. C. f Ã© minine a</t>
-        </is>
-      </c>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>L352: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cole. EspÃ©rons qu'il sera rempli pour le</t>
-        </is>
-      </c>
+      <c r="J125" s="1" t="inlineStr"/>
+      <c r="K125" s="1" t="inlineStr"/>
       <c r="L125" s="1" t="inlineStr"/>
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L614: isolated marker/symbol line :: *</t>
+          <t>L590: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -6075,21 +5175,13 @@
       <c r="G126" s="1" t="inlineStr"/>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr"/>
-      <c r="J126" s="1" t="inlineStr">
-        <is>
-          <t>L425: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: amenÃ© plusieurs jeunes filles des pa-</t>
-        </is>
-      </c>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>L358: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: va prendre la direction de la paroisse de et Mme Paul Boisvert, baptisÃ©e le 10</t>
-        </is>
-      </c>
+      <c r="J126" s="1" t="inlineStr"/>
+      <c r="K126" s="1" t="inlineStr"/>
       <c r="L126" s="1" t="inlineStr"/>
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: *</t>
+          <t>L613: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6114,21 +5206,13 @@
       <c r="G127" s="1" t="inlineStr"/>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr"/>
-      <c r="J127" s="1" t="inlineStr">
-        <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: face de l'Ã©glise.</t>
-        </is>
-      </c>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>L360: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Falher. Nous n'hÃ©sitons pas a dire que aoÃ»t. Parrain et marraine: M. J.-H.</t>
-        </is>
-      </c>
+      <c r="J127" s="1" t="inlineStr"/>
+      <c r="K127" s="1" t="inlineStr"/>
       <c r="L127" s="1" t="inlineStr"/>
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L616: isolated marker/symbol line :: *</t>
+          <t>L614: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6153,21 +5237,13 @@
       <c r="G128" s="1" t="inlineStr"/>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr"/>
-      <c r="J128" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: berley, Ã© taient en visite d 'Ã© t Ã© chez</t>
-        </is>
-      </c>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>L364: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Dieu par son activitÃ© inlassable, par son</t>
-        </is>
-      </c>
+      <c r="J128" s="1" t="inlineStr"/>
+      <c r="K128" s="1" t="inlineStr"/>
       <c r="L128" s="1" t="inlineStr"/>
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L617: isolated marker/symbol line :: *</t>
+          <t>L615: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6192,21 +5268,13 @@
       <c r="G129" s="1" t="inlineStr"/>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr"/>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>L445: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: ç±³</t>
-        </is>
-      </c>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>L368: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Joseph-ClÃ©o-Edouard, enfant de M.</t>
-        </is>
-      </c>
+      <c r="J129" s="1" t="inlineStr"/>
+      <c r="K129" s="1" t="inlineStr"/>
       <c r="L129" s="1" t="inlineStr"/>
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L618: isolated marker/symbol line :: *</t>
+          <t>L616: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6231,21 +5299,13 @@
       <c r="G130" s="1" t="inlineStr"/>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr"/>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: framboise, M. et Mme AdÃ©lard De</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et Mme Emile Dumas, baptisÃ© le 17</t>
-        </is>
-      </c>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
       <c r="L130" s="1" t="inlineStr"/>
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L624: isolated marker/symbol line :: *</t>
+          <t>L617: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6270,21 +5330,13 @@
       <c r="G131" s="1" t="inlineStr"/>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr"/>
-      <c r="J131" s="1" t="inlineStr">
-        <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Bilodeau (Jeanne Mercier) r Ã© cemment</t>
-        </is>
-      </c>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>L371: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dÃ©vouement constant Ã la grande cause aoÃ»t. Parrain et marraine: M. et Mme</t>
-        </is>
-      </c>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
       <c r="L131" s="1" t="inlineStr"/>
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L625: isolated marker/symbol line :: *</t>
+          <t>L618: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6309,21 +5361,13 @@
       <c r="G132" s="1" t="inlineStr"/>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr"/>
-      <c r="J132" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: mari Ã© s.</t>
-        </is>
-      </c>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>L372: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: |de l'Ã©glise paroissiale, Ã celle de l'Ã©cole Edouard Nens, grands-parents de lâ€™en-</t>
-        </is>
-      </c>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
       <c r="L132" s="1" t="inlineStr"/>
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L626: isolated marker/symbol line :: *</t>
+          <t>L624: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6348,21 +5392,13 @@
       <c r="G133" s="1" t="inlineStr"/>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr"/>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>L458: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: On annonce dâ€™Edmonton un double</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et de tous les paroissiens confiÃ©s Ã sa fant, remplacÃ©s par M. et -Mme Paul</t>
-        </is>
-      </c>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
       <c r="L133" s="1" t="inlineStr"/>
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L627: isolated marker/symbol line :: *</t>
+          <t>L625: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6387,21 +5423,13 @@
       <c r="G134" s="1" t="inlineStr"/>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr"/>
-      <c r="J134" s="1" t="inlineStr">
-        <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La c Ã© r Ã© monie se fera Ã Saint-Joachim</t>
-        </is>
-      </c>
-      <c r="K134" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: juridiction. Tout cela, en dÃ©pit d'une Dumas,</t>
-        </is>
-      </c>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
       <c r="L134" s="1" t="inlineStr"/>
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L628: isolated marker/symbol line :: *</t>
+          <t>L626: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6426,21 +5454,13 @@
       <c r="G135" s="1" t="inlineStr"/>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr"/>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>L471: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de RÃ©millard), maintenant de Cold</t>
-        </is>
-      </c>
-      <c r="K135" s="1" t="inlineStr">
-        <is>
-          <t>L375: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: santÃ© fragile. Un Ã©vÃªque lui succÃ©dera : Marie-Rose-Ghislaine, enfant de M.</t>
-        </is>
-      </c>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
       <c r="L135" s="1" t="inlineStr"/>
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L629: isolated marker/symbol line :: *</t>
+          <t>L627: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6465,21 +5485,13 @@
       <c r="G136" s="1" t="inlineStr"/>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr"/>
-      <c r="J136" s="1" t="inlineStr">
-        <is>
-          <t>L472: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Lake, ont fait baptiser leur premier-n Ã©</t>
-        </is>
-      </c>
-      <c r="K136" s="1" t="inlineStr">
-        <is>
-          <t>L376: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et c'est beaucoup dire en sa faveur, et Mme LÃ©once Tremblay, baptisÃ©e le</t>
-        </is>
-      </c>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
       <c r="L136" s="1" t="inlineStr"/>
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L651: isolated marker/symbol line :: *</t>
+          <t>L628: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6504,21 +5516,13 @@
       <c r="G137" s="1" t="inlineStr"/>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr"/>
-      <c r="J137" s="1" t="inlineStr">
-        <is>
-          <t>L474: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Frank RÃ©millard ont etÃ© dans les hon-</t>
-        </is>
-      </c>
-      <c r="K137" s="1" t="inlineStr">
-        <is>
-          <t>L378: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: H. Routhier assumera maintenant ce Leclerc et Blanche RÃ©millard.</t>
-        </is>
-      </c>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
       <c r="L137" s="1" t="inlineStr"/>
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L667: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L629: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6543,21 +5547,13 @@
       <c r="G138" s="1" t="inlineStr"/>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr"/>
-      <c r="J138" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'ancien foyer toujours si cher de QuÃ©bec.</t>
-        </is>
-      </c>
-      <c r="K138" s="1" t="inlineStr">
-        <is>
-          <t>L380: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN, U+00A9 COPYRIGHT SIGN :: surcroÃ®t de responsabilitÃ© avec les vi-1</t>
-        </is>
-      </c>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
       <c r="L138" s="1" t="inlineStr"/>
       <c r="M138" s="1" t="inlineStr"/>
       <c r="N138" s="1" t="inlineStr">
         <is>
-          <t>L687: isolated marker/symbol line :: S</t>
+          <t>L651: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O138" s="1" t="inlineStr"/>
@@ -6582,21 +5578,13 @@
       <c r="G139" s="1" t="inlineStr"/>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr"/>
-      <c r="J139" s="1" t="inlineStr">
-        <is>
-          <t>L481: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Ils ont assist Ã© aussi au congr Ã¨ s marial</t>
-        </is>
-      </c>
-      <c r="K139" s="1" t="inlineStr">
-        <is>
-          <t>L386: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production prÃ©vue de blÃ© dans les</t>
-        </is>
-      </c>
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
       <c r="L139" s="1" t="inlineStr"/>
       <c r="M139" s="1" t="inlineStr"/>
       <c r="N139" s="1" t="inlineStr">
         <is>
-          <t>L691: isolated marker/symbol line :: _</t>
+          <t>L667: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O139" s="1" t="inlineStr"/>
@@ -6621,21 +5609,13 @@
       <c r="G140" s="1" t="inlineStr"/>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr"/>
-      <c r="J140" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ne et puis Ste-Anne-de-Beaupr Ã©, et</t>
-        </is>
-      </c>
-      <c r="K140" s="1" t="inlineStr">
-        <is>
-          <t>L389: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le rendement moyen prÃ©vu de blÃ© dans</t>
-        </is>
-      </c>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
       <c r="L140" s="1" t="inlineStr"/>
       <c r="M140" s="1" t="inlineStr"/>
       <c r="N140" s="1" t="inlineStr">
         <is>
-          <t>L722: symbol-only separator/garbage line :: 24606</t>
+          <t>L687: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O140" s="1" t="inlineStr"/>
@@ -6660,21 +5640,13 @@
       <c r="G141" s="1" t="inlineStr"/>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr"/>
-      <c r="J141" s="1" t="inlineStr">
-        <is>
-          <t>L490: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: jeune. Le voyage fut heureux et agr Ã© a-</t>
-        </is>
-      </c>
-      <c r="K141" s="1" t="inlineStr">
-        <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: les provinces des Prairies cette annÃ©e</t>
-        </is>
-      </c>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
       <c r="L141" s="1" t="inlineStr"/>
       <c r="M141" s="1" t="inlineStr"/>
       <c r="N141" s="1" t="inlineStr">
         <is>
-          <t>L727: isolated marker/symbol line :: -</t>
+          <t>L691: isolated marker/symbol line :: _</t>
         </is>
       </c>
       <c r="O141" s="1" t="inlineStr"/>
@@ -6699,21 +5671,13 @@
       <c r="G142" s="1" t="inlineStr"/>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr"/>
-      <c r="J142" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: jl'Ã©tÃ©, devient un peu inquiÃ©tante. Presque-</t>
-        </is>
-      </c>
-      <c r="K142" s="1" t="inlineStr">
-        <is>
-          <t>L396: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La production estimative de blÃ© dans</t>
-        </is>
-      </c>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
       <c r="L142" s="1" t="inlineStr"/>
       <c r="M142" s="1" t="inlineStr"/>
       <c r="N142" s="1" t="inlineStr">
         <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L722: symbol-only separator/garbage line :: 24606</t>
         </is>
       </c>
       <c r="O142" s="1" t="inlineStr"/>
@@ -6738,21 +5702,13 @@
       <c r="G143" s="1" t="inlineStr"/>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr"/>
-      <c r="J143" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s'il fallait? La r Ã© colte est probablement</t>
-        </is>
-      </c>
-      <c r="K143" s="1" t="inlineStr">
-        <is>
-          <t>L397: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: les autres provinces s'Ã©lÃ¨ve Ã 22,786,000</t>
-        </is>
-      </c>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
       <c r="L143" s="1" t="inlineStr"/>
       <c r="M143" s="1" t="inlineStr"/>
       <c r="N143" s="1" t="inlineStr">
         <is>
-          <t>L739: isolated marker/symbol line :: _</t>
+          <t>L727: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O143" s="1" t="inlineStr"/>
@@ -6777,21 +5733,13 @@
       <c r="G144" s="1" t="inlineStr"/>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr"/>
-      <c r="J144" s="1" t="inlineStr">
-        <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: toute sp Ã© ciale aux progr Ã¨ s r Ã© gionaux de</t>
-        </is>
-      </c>
-      <c r="K144" s="1" t="inlineStr">
-        <is>
-          <t>L399: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: soit 19,603,000, est prÃ©vue pour lâ€™Ontario.</t>
-        </is>
-      </c>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
       <c r="L144" s="1" t="inlineStr"/>
       <c r="M144" s="1" t="inlineStr"/>
       <c r="N144" s="1" t="inlineStr">
         <is>
-          <t>L783: symbol-only separator/garbage line :: ****</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O144" s="1" t="inlineStr"/>
@@ -6816,21 +5764,13 @@
       <c r="G145" s="1" t="inlineStr"/>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr"/>
-      <c r="J145" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la propri Ã© t Ã© appartenant a M. G.</t>
-        </is>
-      </c>
-      <c r="K145" s="1" t="inlineStr">
-        <is>
-          <t>L401: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ceptÃ© 513,000 boisseaux, est de blÃ© d'au-</t>
-        </is>
-      </c>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
       <c r="L145" s="1" t="inlineStr"/>
       <c r="M145" s="1" t="inlineStr"/>
       <c r="N145" s="1" t="inlineStr">
         <is>
-          <t>L784: isolated marker/symbol line :: *</t>
+          <t>L739: isolated marker/symbol line :: _</t>
         </is>
       </c>
       <c r="O145" s="1" t="inlineStr"/>
@@ -6855,21 +5795,13 @@
       <c r="G146" s="1" t="inlineStr"/>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr"/>
-      <c r="J146" s="1" t="inlineStr">
-        <is>
-          <t>L519: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©l'residence une maison de M. Steeve,</t>
-        </is>
-      </c>
-      <c r="K146" s="1" t="inlineStr">
-        <is>
-          <t>L407: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et Mme Rosario Corriveau, baptisÃ© le</t>
-        </is>
-      </c>
+      <c r="J146" s="1" t="inlineStr"/>
+      <c r="K146" s="1" t="inlineStr"/>
       <c r="L146" s="1" t="inlineStr"/>
       <c r="M146" s="1" t="inlineStr"/>
       <c r="N146" s="1" t="inlineStr">
         <is>
-          <t>L785: isolated marker/symbol line :: *</t>
+          <t>L783: symbol-only separator/garbage line :: ****</t>
         </is>
       </c>
       <c r="O146" s="1" t="inlineStr"/>
@@ -6894,21 +5826,13 @@
       <c r="G147" s="1" t="inlineStr"/>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr"/>
-      <c r="J147" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Board " en r Ã© compense de ses succ en</t>
-        </is>
-      </c>
-      <c r="K147" s="1" t="inlineStr">
-        <is>
-          <t>L410: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: sences, et le R. PÃ¨re Lessard. La paroisse Mme Etienne RÃ©millard.</t>
-        </is>
-      </c>
+      <c r="J147" s="1" t="inlineStr"/>
+      <c r="K147" s="1" t="inlineStr"/>
       <c r="L147" s="1" t="inlineStr"/>
       <c r="M147" s="1" t="inlineStr"/>
       <c r="N147" s="1" t="inlineStr">
         <is>
-          <t>L786: isolated marker/symbol line :: *</t>
+          <t>L784: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O147" s="1" t="inlineStr"/>
@@ -6933,21 +5857,13 @@
       <c r="G148" s="1" t="inlineStr"/>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
-      <c r="J148" s="1" t="inlineStr">
-        <is>
-          <t>L532: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le village est maintenant incorpor Ã©</t>
-        </is>
-      </c>
-      <c r="K148" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN :: A l'hÃ´pital du SacrÃ©-Coeur de Mc-</t>
-        </is>
-      </c>
+      <c r="J148" s="1" t="inlineStr"/>
+      <c r="K148" s="1" t="inlineStr"/>
       <c r="L148" s="1" t="inlineStr"/>
       <c r="M148" s="1" t="inlineStr"/>
       <c r="N148" s="1" t="inlineStr">
         <is>
-          <t>L792: isolated marker/symbol line :: ***</t>
+          <t>L785: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O148" s="1" t="inlineStr"/>
@@ -6972,21 +5888,13 @@
       <c r="G149" s="1" t="inlineStr"/>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr"/>
-      <c r="J149" s="1" t="inlineStr">
-        <is>
-          <t>L538: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç�«</t>
-        </is>
-      </c>
-      <c r="K149" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tÃ©e d'urgence Ã McLennan samedi soir,</t>
-        </is>
-      </c>
+      <c r="J149" s="1" t="inlineStr"/>
+      <c r="K149" s="1" t="inlineStr"/>
       <c r="L149" s="1" t="inlineStr"/>
       <c r="M149" s="1" t="inlineStr"/>
       <c r="N149" s="1" t="inlineStr">
         <is>
-          <t>L793: isolated marker/symbol line :: *</t>
+          <t>L786: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O149" s="1" t="inlineStr"/>
@@ -7011,21 +5919,13 @@
       <c r="G150" s="1" t="inlineStr"/>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr"/>
-      <c r="J150" s="1" t="inlineStr">
-        <is>
-          <t>L542: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le pique-nique au profit de l 'Ã© glise de</t>
-        </is>
-      </c>
-      <c r="K150" s="1" t="inlineStr">
-        <is>
-          <t>L428: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de retour d'une joyeuse promenade dÃ©</t>
-        </is>
-      </c>
+      <c r="J150" s="1" t="inlineStr"/>
+      <c r="K150" s="1" t="inlineStr"/>
       <c r="L150" s="1" t="inlineStr"/>
       <c r="M150" s="1" t="inlineStr"/>
       <c r="N150" s="1" t="inlineStr">
         <is>
-          <t>L794: isolated marker/symbol line :: **</t>
+          <t>L792: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O150" s="1" t="inlineStr"/>
@@ -7050,21 +5950,13 @@
       <c r="G151" s="1" t="inlineStr"/>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr"/>
-      <c r="J151" s="1" t="inlineStr">
-        <is>
-          <t>L543: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Donatville, dimanche dernier, fut trÃ¨s</t>
-        </is>
-      </c>
-      <c r="K151" s="1" t="inlineStr">
-        <is>
-          <t>L430: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: ner, Ontario et MontrÃ©al.</t>
-        </is>
-      </c>
+      <c r="J151" s="1" t="inlineStr"/>
+      <c r="K151" s="1" t="inlineStr"/>
       <c r="L151" s="1" t="inlineStr"/>
       <c r="M151" s="1" t="inlineStr"/>
       <c r="N151" s="1" t="inlineStr">
         <is>
-          <t>L798: isolated marker/symbol line :: ***</t>
+          <t>L793: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O151" s="1" t="inlineStr"/>
@@ -7089,21 +5981,13 @@
       <c r="G152" s="1" t="inlineStr"/>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
-      <c r="J152" s="1" t="inlineStr">
-        <is>
-          <t>L555: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: : Mme Etienne R Ã© millard.</t>
-        </is>
-      </c>
-      <c r="K152" s="1" t="inlineStr">
-        <is>
-          <t>L436: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: lentement les matÃ©riaux de la future</t>
-        </is>
-      </c>
+      <c r="J152" s="1" t="inlineStr"/>
+      <c r="K152" s="1" t="inlineStr"/>
       <c r="L152" s="1" t="inlineStr"/>
       <c r="M152" s="1" t="inlineStr"/>
       <c r="N152" s="1" t="inlineStr">
         <is>
-          <t>L799: isolated marker/symbol line :: *</t>
+          <t>L794: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O152" s="1" t="inlineStr"/>
@@ -7128,21 +6012,13 @@
       <c r="G153" s="1" t="inlineStr"/>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
-      <c r="J153" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: a Ã© t Ã© trÃ¨s bien suivie. Elle Ã© tait pr Ä“ ch Ã© e</t>
-        </is>
-      </c>
-      <c r="K153" s="1" t="inlineStr">
-        <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©cole de deux classes. Il va falloir se rÃ©-</t>
-        </is>
-      </c>
+      <c r="J153" s="1" t="inlineStr"/>
+      <c r="K153" s="1" t="inlineStr"/>
       <c r="L153" s="1" t="inlineStr"/>
       <c r="M153" s="1" t="inlineStr"/>
       <c r="N153" s="1" t="inlineStr">
         <is>
-          <t>L800: isolated marker/symbol line :: *</t>
+          <t>L798: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O153" s="1" t="inlineStr"/>
@@ -7167,21 +6043,13 @@
       <c r="G154" s="1" t="inlineStr"/>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
-      <c r="J154" s="1" t="inlineStr">
-        <is>
-          <t>L570: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: lerinage r Ã© gional</t>
-        </is>
-      </c>
-      <c r="K154" s="1" t="inlineStr">
-        <is>
-          <t>L438: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: signer Ã l'ouverture de l'Ã©cole avec les</t>
-        </is>
-      </c>
+      <c r="J154" s="1" t="inlineStr"/>
+      <c r="K154" s="1" t="inlineStr"/>
       <c r="L154" s="1" t="inlineStr"/>
       <c r="M154" s="1" t="inlineStr"/>
       <c r="N154" s="1" t="inlineStr">
         <is>
-          <t>L801: isolated marker/symbol line :: *</t>
+          <t>L799: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O154" s="1" t="inlineStr"/>
@@ -7206,21 +6074,13 @@
       <c r="G155" s="1" t="inlineStr"/>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
-      <c r="J155" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Malgr Ã© les menaces de la temp Ã© rature</t>
-        </is>
-      </c>
-      <c r="K155" s="1" t="inlineStr">
-        <is>
-          <t>L439: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: inconvÃ©nients du manque d'espace et les</t>
-        </is>
-      </c>
+      <c r="J155" s="1" t="inlineStr"/>
+      <c r="K155" s="1" t="inlineStr"/>
       <c r="L155" s="1" t="inlineStr"/>
       <c r="M155" s="1" t="inlineStr"/>
       <c r="N155" s="1" t="inlineStr">
         <is>
-          <t>L806: isolated marker/symbol line :: ***</t>
+          <t>L800: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O155" s="1" t="inlineStr"/>
@@ -7245,21 +6105,13 @@
       <c r="G156" s="1" t="inlineStr"/>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
-      <c r="J156" s="1" t="inlineStr">
-        <is>
-          <t>L573: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: 1, 000 p Ã¨ lerins sont venus f Ä“ ter Notre-</t>
-        </is>
-      </c>
-      <c r="K156" s="1" t="inlineStr">
-        <is>
-          <t>L441: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: si toutefois l'on commence bientÃ´t.</t>
-        </is>
-      </c>
+      <c r="J156" s="1" t="inlineStr"/>
+      <c r="K156" s="1" t="inlineStr"/>
       <c r="L156" s="1" t="inlineStr"/>
       <c r="M156" s="1" t="inlineStr"/>
       <c r="N156" s="1" t="inlineStr">
         <is>
-          <t>L807: isolated marker/symbol line :: *</t>
+          <t>L801: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O156" s="1" t="inlineStr"/>
@@ -7284,21 +6136,13 @@
       <c r="G157" s="1" t="inlineStr"/>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
-      <c r="J157" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: : pr Ã© sidait ce p Ã¨ lerinage avec l'aide de son</t>
-        </is>
-      </c>
-      <c r="K157" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: curÃ© tel que Son Excelelnce. Monsei-roissiale du 10 au soir du 13 aoÃ»t. Elle</t>
-        </is>
-      </c>
+      <c r="J157" s="1" t="inlineStr"/>
+      <c r="K157" s="1" t="inlineStr"/>
       <c r="L157" s="1" t="inlineStr"/>
       <c r="M157" s="1" t="inlineStr"/>
       <c r="N157" s="1" t="inlineStr">
         <is>
-          <t>L808: isolated marker/symbol line :: *</t>
+          <t>L806: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O157" s="1" t="inlineStr"/>
@@ -7323,21 +6167,13 @@
       <c r="G158" s="1" t="inlineStr"/>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
-      <c r="J158" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le chemin de croix fut prÃªchÃ© Ã© par le</t>
-        </is>
-      </c>
-      <c r="K158" s="1" t="inlineStr">
-        <is>
-          <t>L447: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: gneur exposait lui-mÃªme, dimanche der- a Ã©tÃ© trÃ¨s bien suivie. Elle Ã©tait prÃªchÃ©e</t>
-        </is>
-      </c>
+      <c r="J158" s="1" t="inlineStr"/>
+      <c r="K158" s="1" t="inlineStr"/>
       <c r="L158" s="1" t="inlineStr"/>
       <c r="M158" s="1" t="inlineStr"/>
       <c r="N158" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: *</t>
+          <t>L807: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O158" s="1" t="inlineStr"/>
@@ -7362,21 +6198,13 @@
       <c r="G159" s="1" t="inlineStr"/>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
-      <c r="J159" s="1" t="inlineStr">
-        <is>
-          <t>L585: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: riv Ã© ici, est en train de se bÃ¢tir une</t>
-        </is>
-      </c>
-      <c r="K159" s="1" t="inlineStr">
-        <is>
-          <t>L448: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: nier, un programme d'ampleur en ma- par le RÃ©vÃ©rend PÃ¨re Germain Dande-</t>
-        </is>
-      </c>
+      <c r="J159" s="1" t="inlineStr"/>
+      <c r="K159" s="1" t="inlineStr"/>
       <c r="L159" s="1" t="inlineStr"/>
       <c r="M159" s="1" t="inlineStr"/>
       <c r="N159" s="1" t="inlineStr">
         <is>
-          <t>L815: isolated marker/symbol line :: ***</t>
+          <t>L808: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O159" s="1" t="inlineStr"/>
@@ -7401,21 +6229,13 @@
       <c r="G160" s="1" t="inlineStr"/>
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr"/>
-      <c r="J160" s="1" t="inlineStr">
-        <is>
-          <t>L592: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©parations Ã son tel.</t>
-        </is>
-      </c>
-      <c r="K160" s="1" t="inlineStr">
-        <is>
-          <t>L449: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: tiÃ¨re d'Ã©tudes religieuses et sociales pour nualt, o.m.i., missionnaire de MontrÃ©al,</t>
-        </is>
-      </c>
+      <c r="J160" s="1" t="inlineStr"/>
+      <c r="K160" s="1" t="inlineStr"/>
       <c r="L160" s="1" t="inlineStr"/>
       <c r="M160" s="1" t="inlineStr"/>
       <c r="N160" s="1" t="inlineStr">
         <is>
-          <t>L816: isolated marker/symbol line :: *</t>
+          <t>L809: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O160" s="1" t="inlineStr"/>
@@ -7440,21 +6260,13 @@
       <c r="G161" s="1" t="inlineStr"/>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr"/>
-      <c r="J161" s="1" t="inlineStr">
-        <is>
-          <t>L593: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Rome. â€” Plus de 350 scouts italiens,</t>
-        </is>
-      </c>
-      <c r="K161" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: les enfants et pour les adultes. Il ma- : Le mÃªme PÃ¨re a fait un sermon trÃ¨s Ã©lo-</t>
-        </is>
-      </c>
+      <c r="J161" s="1" t="inlineStr"/>
+      <c r="K161" s="1" t="inlineStr"/>
       <c r="L161" s="1" t="inlineStr"/>
       <c r="M161" s="1" t="inlineStr"/>
       <c r="N161" s="1" t="inlineStr">
         <is>
-          <t>L817: isolated marker/symbol line :: *</t>
+          <t>L815: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O161" s="1" t="inlineStr"/>
@@ -7479,21 +6291,13 @@
       <c r="G162" s="1" t="inlineStr"/>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
-      <c r="J162" s="1" t="inlineStr">
-        <is>
-          <t>L595: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Scouts catholiques), ont assistÃ© au Jam-</t>
-        </is>
-      </c>
-      <c r="K162" s="1" t="inlineStr">
-        <is>
-          <t>L455: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: toute spÃ©ciale aux progrÃ¨s rÃ©gionaux de</t>
-        </is>
-      </c>
+      <c r="J162" s="1" t="inlineStr"/>
+      <c r="K162" s="1" t="inlineStr"/>
       <c r="L162" s="1" t="inlineStr"/>
       <c r="M162" s="1" t="inlineStr"/>
       <c r="N162" s="1" t="inlineStr">
         <is>
-          <t>L818: isolated marker/symbol line :: *</t>
+          <t>L816: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O162" s="1" t="inlineStr"/>
@@ -7518,21 +6322,13 @@
       <c r="G163" s="1" t="inlineStr"/>
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
-      <c r="J163" s="1" t="inlineStr">
-        <is>
-          <t>L597: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: prÃ¨s de Paris. Ces scouts italiens ont</t>
-        </is>
-      </c>
-      <c r="K163" s="1" t="inlineStr">
-        <is>
-          <t>L461: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de la propriÃ©tÃ© appartenant Ã M. G.</t>
-        </is>
-      </c>
+      <c r="J163" s="1" t="inlineStr"/>
+      <c r="K163" s="1" t="inlineStr"/>
       <c r="L163" s="1" t="inlineStr"/>
       <c r="M163" s="1" t="inlineStr"/>
       <c r="N163" s="1" t="inlineStr">
         <is>
-          <t>L822: symbol-only separator/garbage line :: ****</t>
+          <t>L817: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O163" s="1" t="inlineStr"/>
@@ -7557,21 +6353,13 @@
       <c r="G164" s="1" t="inlineStr"/>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr"/>
-      <c r="J164" s="1" t="inlineStr">
-        <is>
-          <t>L598: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: apportÃ© avec eux des rÃ©pliques d'une.</t>
-        </is>
-      </c>
-      <c r="K164" s="1" t="inlineStr">
-        <is>
-          <t>L462: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Stevenson. Ils sont Ã faire des rÃ©para-</t>
-        </is>
-      </c>
+      <c r="J164" s="1" t="inlineStr"/>
+      <c r="K164" s="1" t="inlineStr"/>
       <c r="L164" s="1" t="inlineStr"/>
       <c r="M164" s="1" t="inlineStr"/>
       <c r="N164" s="1" t="inlineStr">
         <is>
-          <t>L823: isolated marker/symbol line :: *</t>
+          <t>L818: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O164" s="1" t="inlineStr"/>
@@ -7596,21 +6384,13 @@
       <c r="G165" s="1" t="inlineStr"/>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr"/>
-      <c r="J165" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Scouts ". La statue originale a Ã© t Ã© b Ã© nie</t>
-        </is>
-      </c>
-      <c r="K165" s="1" t="inlineStr">
-        <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La rÃ©colte d'avoine en 1947 est estimÃ©e</t>
-        </is>
-      </c>
+      <c r="J165" s="1" t="inlineStr"/>
+      <c r="K165" s="1" t="inlineStr"/>
       <c r="L165" s="1" t="inlineStr"/>
       <c r="M165" s="1" t="inlineStr"/>
       <c r="N165" s="1" t="inlineStr">
         <is>
-          <t>L824: isolated marker/symbol line :: **</t>
+          <t>L822: symbol-only separator/garbage line :: ****</t>
         </is>
       </c>
       <c r="O165" s="1" t="inlineStr"/>
@@ -7635,21 +6415,13 @@
       <c r="G166" s="1" t="inlineStr"/>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr"/>
-      <c r="J166" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: derniÃ¨rement par par Sa Saintet Ã© le pape</t>
-        </is>
-      </c>
-      <c r="K166" s="1" t="inlineStr">
-        <is>
-          <t>L470: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'une diminution des acrÃ©ages ensemen-</t>
-        </is>
-      </c>
+      <c r="J166" s="1" t="inlineStr"/>
+      <c r="K166" s="1" t="inlineStr"/>
       <c r="L166" s="1" t="inlineStr"/>
       <c r="M166" s="1" t="inlineStr"/>
       <c r="N166" s="1" t="inlineStr">
         <is>
-          <t>L831: isolated marker/symbol line :: ***</t>
+          <t>L823: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O166" s="1" t="inlineStr"/>
@@ -7674,21 +6446,13 @@
       <c r="G167" s="1" t="inlineStr"/>
       <c r="H167" s="1" t="inlineStr"/>
       <c r="I167" s="1" t="inlineStr"/>
-      <c r="J167" s="1" t="inlineStr">
-        <is>
-          <t>L604: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: prÃ©sident et l'aumonier de l'Association.</t>
-        </is>
-      </c>
-      <c r="K167" s="1" t="inlineStr">
-        <is>
-          <t>L472: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: quent Ã la procession du grand pÃ¨leri-</t>
-        </is>
-      </c>
+      <c r="J167" s="1" t="inlineStr"/>
+      <c r="K167" s="1" t="inlineStr"/>
       <c r="L167" s="1" t="inlineStr"/>
       <c r="M167" s="1" t="inlineStr"/>
       <c r="N167" s="1" t="inlineStr">
         <is>
-          <t>L832: isolated marker/symbol line :: ***</t>
+          <t>L824: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O167" s="1" t="inlineStr"/>
@@ -7713,21 +6477,13 @@
       <c r="G168" s="1" t="inlineStr"/>
       <c r="H168" s="1" t="inlineStr"/>
       <c r="I168" s="1" t="inlineStr"/>
-      <c r="J168" s="1" t="inlineStr">
-        <is>
-          <t>L630: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Un brin d'espoir renait dans lâ€™esprit</t>
-        </is>
-      </c>
-      <c r="K168" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: PÃ¨lerinage rÃ©gional</t>
-        </is>
-      </c>
+      <c r="J168" s="1" t="inlineStr"/>
+      <c r="K168" s="1" t="inlineStr"/>
       <c r="L168" s="1" t="inlineStr"/>
       <c r="M168" s="1" t="inlineStr"/>
       <c r="N168" s="1" t="inlineStr">
         <is>
-          <t>L835: isolated marker/symbol line :: 2</t>
+          <t>L831: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O168" s="1" t="inlineStr"/>
@@ -7752,21 +6508,13 @@
       <c r="G169" s="1" t="inlineStr"/>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr"/>
-      <c r="J169" s="1" t="inlineStr">
-        <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã© cole de deux classes. Il va falloir se r Ã©-</t>
-        </is>
-      </c>
-      <c r="K169" s="1" t="inlineStr">
-        <is>
-          <t>L479: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: |MalgrÃ© les menaces de la tempÃ©rature</t>
-        </is>
-      </c>
+      <c r="J169" s="1" t="inlineStr"/>
+      <c r="K169" s="1" t="inlineStr"/>
       <c r="L169" s="1" t="inlineStr"/>
       <c r="M169" s="1" t="inlineStr"/>
       <c r="N169" s="1" t="inlineStr">
         <is>
-          <t>L837: isolated marker/symbol line :: ***</t>
+          <t>L832: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O169" s="1" t="inlineStr"/>
@@ -7791,21 +6539,13 @@
       <c r="G170" s="1" t="inlineStr"/>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr"/>
-      <c r="J170" s="1" t="inlineStr">
-        <is>
-          <t>L638: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lake-Success, N.- C.â€” Les nations de</t>
-        </is>
-      </c>
-      <c r="K170" s="1" t="inlineStr">
-        <is>
-          <t>L481: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: 1,000 pÃ¨lerins sont venus fÃªter Notre-</t>
-        </is>
-      </c>
+      <c r="J170" s="1" t="inlineStr"/>
+      <c r="K170" s="1" t="inlineStr"/>
       <c r="L170" s="1" t="inlineStr"/>
       <c r="M170" s="1" t="inlineStr"/>
       <c r="N170" s="1" t="inlineStr">
         <is>
-          <t>L838: isolated marker/symbol line :: *</t>
+          <t>L835: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O170" s="1" t="inlineStr"/>
@@ -7830,21 +6570,13 @@
       <c r="G171" s="1" t="inlineStr"/>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr"/>
-      <c r="J171" s="1" t="inlineStr">
-        <is>
-          <t>L640: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: cupe un des trois si Ã¨ ges non permanents</t>
-        </is>
-      </c>
-      <c r="K171" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: | Mgr Langlois, o.m.i., notre Ã©vÃªque,</t>
-        </is>
-      </c>
+      <c r="J171" s="1" t="inlineStr"/>
+      <c r="K171" s="1" t="inlineStr"/>
       <c r="L171" s="1" t="inlineStr"/>
       <c r="M171" s="1" t="inlineStr"/>
       <c r="N171" s="1" t="inlineStr">
         <is>
-          <t>L839: isolated marker/symbol line :: **</t>
+          <t>L837: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O171" s="1" t="inlineStr"/>
@@ -7869,21 +6601,13 @@
       <c r="G172" s="1" t="inlineStr"/>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr"/>
-      <c r="J172" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cur Ã© tel que Son Excelence. Monsei- roissiale du 10 au soir du 13 aout. Elle</t>
-        </is>
-      </c>
-      <c r="K172" s="1" t="inlineStr">
-        <is>
-          <t>L487: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: "Votre satisfaction est notre succÃ¨s"</t>
-        </is>
-      </c>
+      <c r="J172" s="1" t="inlineStr"/>
+      <c r="K172" s="1" t="inlineStr"/>
       <c r="L172" s="1" t="inlineStr"/>
       <c r="M172" s="1" t="inlineStr"/>
       <c r="N172" s="1" t="inlineStr">
         <is>
-          <t>L846: isolated marker/symbol line :: 4</t>
+          <t>L838: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O172" s="1" t="inlineStr"/>
@@ -7908,21 +6632,13 @@
       <c r="G173" s="1" t="inlineStr"/>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr"/>
-      <c r="J173" s="1" t="inlineStr">
-        <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: gneur exposait lui-m, dimanche der- a Ã© t Ã© trÃ¨s bien suivie. Elle Ã© tait prechee</t>
-        </is>
-      </c>
-      <c r="K173" s="1" t="inlineStr">
-        <is>
-          <t>L493: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le chemin de croix fut prÃªchÃ© par le</t>
-        </is>
-      </c>
+      <c r="J173" s="1" t="inlineStr"/>
+      <c r="K173" s="1" t="inlineStr"/>
       <c r="L173" s="1" t="inlineStr"/>
       <c r="M173" s="1" t="inlineStr"/>
       <c r="N173" s="1" t="inlineStr">
         <is>
-          <t>L847: isolated marker/symbol line :: ***</t>
+          <t>L839: isolated marker/symbol line :: **</t>
         </is>
       </c>
       <c r="O173" s="1" t="inlineStr"/>
@@ -7947,21 +6663,13 @@
       <c r="G174" s="1" t="inlineStr"/>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr"/>
-      <c r="J174" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nier, un programme d'ampleur en ma- par le R Ã© v Ã© rend Pere Germain Dande-</t>
-        </is>
-      </c>
-      <c r="K174" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | abbreviation/spacing may be garbled :: PÃ¨re Gabriel Morvan, o.m.i.</t>
-        </is>
-      </c>
+      <c r="J174" s="1" t="inlineStr"/>
+      <c r="K174" s="1" t="inlineStr"/>
       <c r="L174" s="1" t="inlineStr"/>
       <c r="M174" s="1" t="inlineStr"/>
       <c r="N174" s="1" t="inlineStr">
         <is>
-          <t>L848: isolated marker/symbol line :: ***</t>
+          <t>L845: stray/suspicious non-ASCII glyph(s): U+6211 CJK UNIFIED IDEOGRAPH-6211 | isolated marker/symbol line :: 我</t>
         </is>
       </c>
       <c r="O174" s="1" t="inlineStr"/>
@@ -7986,21 +6694,13 @@
       <c r="G175" s="1" t="inlineStr"/>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr"/>
-      <c r="J175" s="1" t="inlineStr">
-        <is>
-          <t>L655: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: tiÃ¨re d 'Ã© tudes religieuses et sociales pour, o. m. i, missionnaire de Montreal.</t>
-        </is>
-      </c>
-      <c r="K175" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: M. Alfred Cloutier, derniÃ¨rement ar-</t>
-        </is>
-      </c>
+      <c r="J175" s="1" t="inlineStr"/>
+      <c r="K175" s="1" t="inlineStr"/>
       <c r="L175" s="1" t="inlineStr"/>
       <c r="M175" s="1" t="inlineStr"/>
       <c r="N175" s="1" t="inlineStr">
         <is>
-          <t>L858: isolated marker/symbol line :: ***</t>
+          <t>L846: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O175" s="1" t="inlineStr"/>
@@ -8025,21 +6725,13 @@
       <c r="G176" s="1" t="inlineStr"/>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr"/>
-      <c r="J176" s="1" t="inlineStr">
-        <is>
-          <t>L656: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: les enfants et pour les adultes. Il ma- Le me Pere a fait un sermon tr Ã¨ s Ã© lo-</t>
-        </is>
-      </c>
-      <c r="K176" s="1" t="inlineStr">
-        <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: rivÃ© ici, est en train de se bÃ¢tir une</t>
-        </is>
-      </c>
+      <c r="J176" s="1" t="inlineStr"/>
+      <c r="K176" s="1" t="inlineStr"/>
       <c r="L176" s="1" t="inlineStr"/>
       <c r="M176" s="1" t="inlineStr"/>
       <c r="N176" s="1" t="inlineStr">
         <is>
-          <t>L859: isolated marker/symbol line :: *</t>
+          <t>L847: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O176" s="1" t="inlineStr"/>
@@ -8064,21 +6756,13 @@
       <c r="G177" s="1" t="inlineStr"/>
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr"/>
-      <c r="J177" s="1" t="inlineStr">
-        <is>
-          <t>L661: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Stevenson. Ils sont a faire des para Mgr Langlois, o. m. i., notre Ã© Ã©vÃªque,</t>
-        </is>
-      </c>
-      <c r="K177" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: rÃ©parations Ã son hÃ´tel.</t>
-        </is>
-      </c>
+      <c r="J177" s="1" t="inlineStr"/>
+      <c r="K177" s="1" t="inlineStr"/>
       <c r="L177" s="1" t="inlineStr"/>
       <c r="M177" s="1" t="inlineStr"/>
       <c r="N177" s="1" t="inlineStr">
         <is>
-          <t>L860: isolated marker/symbol line :: *</t>
+          <t>L848: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O177" s="1" t="inlineStr"/>
@@ -8103,21 +6787,13 @@
       <c r="G178" s="1" t="inlineStr"/>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr"/>
-      <c r="J178" s="1" t="inlineStr">
-        <is>
-          <t>L662: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: tions urgentes en vue de continuer leur i pr Ã© sidait ce lerinage avec l'aide de son</t>
-        </is>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: commerce d'hÃ´tel, pour accommoder les</t>
-        </is>
-      </c>
+      <c r="J178" s="1" t="inlineStr"/>
+      <c r="K178" s="1" t="inlineStr"/>
       <c r="L178" s="1" t="inlineStr"/>
       <c r="M178" s="1" t="inlineStr"/>
       <c r="N178" s="1" t="inlineStr">
         <is>
-          <t>L861: isolated marker/symbol line :: *</t>
+          <t>L858: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O178" s="1" t="inlineStr"/>
@@ -8142,21 +6818,13 @@
       <c r="G179" s="1" t="inlineStr"/>
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr"/>
-      <c r="J179" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: voyageurs. Ils ont aussi achet Ã© comme la messe et fit le sermon en anglais et</t>
-        </is>
-      </c>
-      <c r="K179" s="1" t="inlineStr">
-        <is>
-          <t>L511: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: voyageurs. Ils ont aussi achetÃ© comme</t>
-        </is>
-      </c>
+      <c r="J179" s="1" t="inlineStr"/>
+      <c r="K179" s="1" t="inlineStr"/>
       <c r="L179" s="1" t="inlineStr"/>
       <c r="M179" s="1" t="inlineStr"/>
       <c r="N179" s="1" t="inlineStr">
         <is>
-          <t>L868: isolated marker/symbol line :: ***</t>
+          <t>L859: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O179" s="1" t="inlineStr"/>
@@ -8181,21 +6849,13 @@
       <c r="G180" s="1" t="inlineStr"/>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr"/>
-      <c r="J180" s="1" t="inlineStr">
-        <is>
-          <t>L667: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K180" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: rÃ©sidence une maison de M. Steeve,</t>
-        </is>
-      </c>
+      <c r="J180" s="1" t="inlineStr"/>
+      <c r="K180" s="1" t="inlineStr"/>
       <c r="L180" s="1" t="inlineStr"/>
       <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="inlineStr">
         <is>
-          <t>L869: isolated marker/symbol line :: *</t>
+          <t>L860: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O180" s="1" t="inlineStr"/>
@@ -8220,21 +6880,13 @@
       <c r="G181" s="1" t="inlineStr"/>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr"/>
-      <c r="J181" s="1" t="inlineStr">
-        <is>
-          <t>L670: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: chez sa fille, Mme Arthur Mageau, aprÃ¨s revenus tout ragaillardis.</t>
-        </is>
-      </c>
-      <c r="K181" s="1" t="inlineStr">
-        <is>
-          <t>L517: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN, U+00A9 COPYRIGHT SIGN :: Florence Frey, Ã¢gÃ©e de neuf ans, en-</t>
-        </is>
-      </c>
+      <c r="J181" s="1" t="inlineStr"/>
+      <c r="K181" s="1" t="inlineStr"/>
       <c r="L181" s="1" t="inlineStr"/>
       <c r="M181" s="1" t="inlineStr"/>
       <c r="N181" s="1" t="inlineStr">
         <is>
-          <t>L870: isolated marker/symbol line :: *</t>
+          <t>L861: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O181" s="1" t="inlineStr"/>
@@ -8259,21 +6911,13 @@
       <c r="G182" s="1" t="inlineStr"/>
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr"/>
-      <c r="J182" s="1" t="inlineStr">
-        <is>
-          <t>L680: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Aim Ã©- R. Bernier</t>
-        </is>
-      </c>
-      <c r="K182" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Board" en rÃ©compense de ses succÃ¨s en</t>
-        </is>
-      </c>
+      <c r="J182" s="1" t="inlineStr"/>
+      <c r="K182" s="1" t="inlineStr"/>
       <c r="L182" s="1" t="inlineStr"/>
       <c r="M182" s="1" t="inlineStr"/>
       <c r="N182" s="1" t="inlineStr">
         <is>
-          <t>L871: isolated marker/symbol line :: *</t>
+          <t>L868: isolated marker/symbol line :: ***</t>
         </is>
       </c>
       <c r="O182" s="1" t="inlineStr"/>
@@ -8298,21 +6942,13 @@
       <c r="G183" s="1" t="inlineStr"/>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr"/>
-      <c r="J183" s="1" t="inlineStr">
-        <is>
-          <t>L683: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tel.: Bureau: 27365 â€” Res.: 24017</t>
-        </is>
-      </c>
-      <c r="K183" s="1" t="inlineStr">
-        <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: fÃ©licitations Ã la petite.</t>
-        </is>
-      </c>
+      <c r="J183" s="1" t="inlineStr"/>
+      <c r="K183" s="1" t="inlineStr"/>
       <c r="L183" s="1" t="inlineStr"/>
       <c r="M183" s="1" t="inlineStr"/>
       <c r="N183" s="1" t="inlineStr">
         <is>
-          <t>L907: symbol-only separator/garbage line :: 3977</t>
+          <t>L869: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O183" s="1" t="inlineStr"/>
@@ -8337,21 +6973,13 @@
       <c r="G184" s="1" t="inlineStr"/>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr"/>
-      <c r="J184" s="1" t="inlineStr">
-        <is>
-          <t>L692: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© l.: 25935</t>
-        </is>
-      </c>
-      <c r="K184" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Morin &amp; FrÃ¨res</t>
-        </is>
-      </c>
+      <c r="J184" s="1" t="inlineStr"/>
+      <c r="K184" s="1" t="inlineStr"/>
       <c r="L184" s="1" t="inlineStr"/>
       <c r="M184" s="1" t="inlineStr"/>
       <c r="N184" s="1" t="inlineStr">
         <is>
-          <t>L911: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
+          <t>L870: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O184" s="1" t="inlineStr"/>
@@ -8376,21 +7004,13 @@
       <c r="G185" s="1" t="inlineStr"/>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr"/>
-      <c r="J185" s="1" t="inlineStr">
-        <is>
-          <t>L695: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: L Ã© o Belhumeur</t>
-        </is>
-      </c>
-      <c r="K185" s="1" t="inlineStr">
-        <is>
-          <t>L531: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: maison. Un autre coin aura bientÃ´t em-</t>
-        </is>
-      </c>
+      <c r="J185" s="1" t="inlineStr"/>
+      <c r="K185" s="1" t="inlineStr"/>
       <c r="L185" s="1" t="inlineStr"/>
       <c r="M185" s="1" t="inlineStr"/>
       <c r="N185" s="1" t="inlineStr">
         <is>
-          <t>L914: isolated marker/symbol line :: 2</t>
+          <t>L871: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O185" s="1" t="inlineStr"/>
@@ -8415,21 +7035,13 @@
       <c r="G186" s="1" t="inlineStr"/>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr"/>
-      <c r="J186" s="1" t="inlineStr">
-        <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Vie â€” Feu - Auto â€” GrÃªle</t>
-        </is>
-      </c>
-      <c r="K186" s="1" t="inlineStr">
-        <is>
-          <t>L536: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | abbreviation/spacing may be garbled :: Une rÃ©union de J.E.C. fÃ©minine a</t>
-        </is>
-      </c>
+      <c r="J186" s="1" t="inlineStr"/>
+      <c r="K186" s="1" t="inlineStr"/>
       <c r="L186" s="1" t="inlineStr"/>
       <c r="M186" s="1" t="inlineStr"/>
       <c r="N186" s="1" t="inlineStr">
         <is>
-          <t>L918: isolated marker/symbol line :: 0</t>
+          <t>L907: symbol-only separator/garbage line :: 3977</t>
         </is>
       </c>
       <c r="O186" s="1" t="inlineStr"/>
@@ -8454,21 +7066,13 @@
       <c r="G187" s="1" t="inlineStr"/>
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr"/>
-      <c r="J187" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© l.: 26</t>
-        </is>
-      </c>
-      <c r="K187" s="1" t="inlineStr">
-        <is>
-          <t>L537: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: amenÃ© plusieurs jeunes filles des pa-</t>
-        </is>
-      </c>
+      <c r="J187" s="1" t="inlineStr"/>
+      <c r="K187" s="1" t="inlineStr"/>
       <c r="L187" s="1" t="inlineStr"/>
       <c r="M187" s="1" t="inlineStr"/>
       <c r="N187" s="1" t="inlineStr">
         <is>
-          <t>L920: symbol-only separator/garbage line :: $3975</t>
+          <t>L911: stray/suspicious non-ASCII glyph(s): U+54C1 CJK UNIFIED IDEOGRAPH-54C1 | isolated marker/symbol line :: 品</t>
         </is>
       </c>
       <c r="O187" s="1" t="inlineStr"/>
@@ -8493,21 +7097,13 @@
       <c r="G188" s="1" t="inlineStr"/>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr"/>
-      <c r="J188" s="1" t="inlineStr">
-        <is>
-          <t>L703: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: genres de propriÃ©tes par toutes les pro-</t>
-        </is>
-      </c>
-      <c r="K188" s="1" t="inlineStr">
-        <is>
-          <t>L541: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©lÃ©phone 26405</t>
-        </is>
-      </c>
+      <c r="J188" s="1" t="inlineStr"/>
+      <c r="K188" s="1" t="inlineStr"/>
       <c r="L188" s="1" t="inlineStr"/>
       <c r="M188" s="1" t="inlineStr"/>
       <c r="N188" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: *</t>
+          <t>L914: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O188" s="1" t="inlineStr"/>
@@ -8532,21 +7128,13 @@
       <c r="G189" s="1" t="inlineStr"/>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr"/>
-      <c r="J189" s="1" t="inlineStr">
-        <is>
-          <t>L708: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: R Ã© parages, Redoublage, Remodelage</t>
-        </is>
-      </c>
-      <c r="K189" s="1" t="inlineStr">
-        <is>
-          <t>L547: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l. 24344 721, Ã©difice Tegler</t>
-        </is>
-      </c>
+      <c r="J189" s="1" t="inlineStr"/>
+      <c r="K189" s="1" t="inlineStr"/>
       <c r="L189" s="1" t="inlineStr"/>
       <c r="M189" s="1" t="inlineStr"/>
       <c r="N189" s="1" t="inlineStr">
         <is>
-          <t>L922: isolated marker/symbol line :: *</t>
+          <t>L918: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O189" s="1" t="inlineStr"/>
@@ -8571,21 +7159,13 @@
       <c r="G190" s="1" t="inlineStr"/>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr"/>
-      <c r="J190" s="1" t="inlineStr">
-        <is>
-          <t>L712: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: T Ã© l. 22213</t>
-        </is>
-      </c>
-      <c r="K190" s="1" t="inlineStr">
-        <is>
-          <t>L549: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Lake-Success, N.-C. â€” Les nations de</t>
-        </is>
-      </c>
+      <c r="J190" s="1" t="inlineStr"/>
+      <c r="K190" s="1" t="inlineStr"/>
       <c r="L190" s="1" t="inlineStr"/>
       <c r="M190" s="1" t="inlineStr"/>
       <c r="N190" s="1" t="inlineStr">
         <is>
-          <t>L923: isolated marker/symbol line :: *</t>
+          <t>L920: symbol-only separator/garbage line :: $3975</t>
         </is>
       </c>
       <c r="O190" s="1" t="inlineStr"/>
@@ -8610,21 +7190,13 @@
       <c r="G191" s="1" t="inlineStr"/>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr"/>
-      <c r="J191" s="1" t="inlineStr">
-        <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: en tal.â€”Syst de classements,</t>
-        </is>
-      </c>
-      <c r="K191" s="1" t="inlineStr">
-        <is>
-          <t>L551: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: cupe un des trois siÃ¨ges non permanents</t>
-        </is>
-      </c>
+      <c r="J191" s="1" t="inlineStr"/>
+      <c r="K191" s="1" t="inlineStr"/>
       <c r="L191" s="1" t="inlineStr"/>
       <c r="M191" s="1" t="inlineStr"/>
       <c r="N191" s="1" t="inlineStr">
         <is>
-          <t>L926: symbol-only separator/garbage line :: $25.00</t>
+          <t>L921: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O191" s="1" t="inlineStr"/>
@@ -8649,21 +7221,13 @@
       <c r="G192" s="1" t="inlineStr"/>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr"/>
-      <c r="J192" s="1" t="inlineStr">
-        <is>
-          <t>L716: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: le tout fabriqu Ã© su Canada.</t>
-        </is>
-      </c>
-      <c r="K192" s="1" t="inlineStr">
-        <is>
-          <t>L552: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: du Conseil de SÃ©curitÃ© des Nations-</t>
-        </is>
-      </c>
+      <c r="J192" s="1" t="inlineStr"/>
+      <c r="K192" s="1" t="inlineStr"/>
       <c r="L192" s="1" t="inlineStr"/>
       <c r="M192" s="1" t="inlineStr"/>
       <c r="N192" s="1" t="inlineStr">
         <is>
-          <t>L927: symbol-only separator/garbage line :: $6.25</t>
+          <t>L922: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O192" s="1" t="inlineStr"/>
@@ -8688,21 +7252,13 @@
       <c r="G193" s="1" t="inlineStr"/>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr"/>
-      <c r="J193" s="1" t="inlineStr">
-        <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: - R Ã© para-</t>
-        </is>
-      </c>
-      <c r="K193" s="1" t="inlineStr">
-        <is>
-          <t>L553: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Unies, Ã l'occasion de l'Ã©lection de nou-</t>
-        </is>
-      </c>
+      <c r="J193" s="1" t="inlineStr"/>
+      <c r="K193" s="1" t="inlineStr"/>
       <c r="L193" s="1" t="inlineStr"/>
       <c r="M193" s="1" t="inlineStr"/>
       <c r="N193" s="1" t="inlineStr">
         <is>
-          <t>L928: isolated marker/symbol line :: 1</t>
+          <t>L923: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O193" s="1" t="inlineStr"/>
@@ -8727,21 +7283,13 @@
       <c r="G194" s="1" t="inlineStr"/>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr"/>
-      <c r="J194" s="1" t="inlineStr">
-        <is>
-          <t>L734: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Sp Ã© clairit de Vie</t>
-        </is>
-      </c>
-      <c r="K194" s="1" t="inlineStr">
-        <is>
-          <t>L554: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: veaux membres par l'AssemblÃ©e gÃ©nÃ©rale</t>
-        </is>
-      </c>
+      <c r="J194" s="1" t="inlineStr"/>
+      <c r="K194" s="1" t="inlineStr"/>
       <c r="L194" s="1" t="inlineStr"/>
       <c r="M194" s="1" t="inlineStr"/>
       <c r="N194" s="1" t="inlineStr">
         <is>
-          <t>L931: symbol-only separator/garbage line :: 10115</t>
+          <t>L926: symbol-only separator/garbage line :: $25.00</t>
         </is>
       </c>
       <c r="O194" s="1" t="inlineStr"/>
@@ -8766,19 +7314,15 @@
       <c r="G195" s="1" t="inlineStr"/>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr"/>
-      <c r="J195" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tel.: Bureau: 26573 â€” Res.:</t>
-        </is>
-      </c>
-      <c r="K195" s="1" t="inlineStr">
-        <is>
-          <t>L557: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J195" s="1" t="inlineStr"/>
+      <c r="K195" s="1" t="inlineStr"/>
       <c r="L195" s="1" t="inlineStr"/>
       <c r="M195" s="1" t="inlineStr"/>
-      <c r="N195" s="1" t="inlineStr"/>
+      <c r="N195" s="1" t="inlineStr">
+        <is>
+          <t>L927: symbol-only separator/garbage line :: $6.25</t>
+        </is>
+      </c>
       <c r="O195" s="1" t="inlineStr"/>
       <c r="P195" s="1" t="inlineStr"/>
       <c r="Q195" s="1" t="inlineStr"/>
@@ -8801,19 +7345,15 @@
       <c r="G196" s="1" t="inlineStr"/>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="1" t="inlineStr"/>
-      <c r="J196" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K196" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: SpÃ©cialitÃ© de produits franÃ§ais</t>
-        </is>
-      </c>
+      <c r="J196" s="1" t="inlineStr"/>
+      <c r="K196" s="1" t="inlineStr"/>
       <c r="L196" s="1" t="inlineStr"/>
       <c r="M196" s="1" t="inlineStr"/>
-      <c r="N196" s="1" t="inlineStr"/>
+      <c r="N196" s="1" t="inlineStr">
+        <is>
+          <t>L928: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="O196" s="1" t="inlineStr"/>
       <c r="P196" s="1" t="inlineStr"/>
       <c r="Q196" s="1" t="inlineStr"/>
@@ -8836,19 +7376,15 @@
       <c r="G197" s="1" t="inlineStr"/>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr"/>
-      <c r="J197" s="1" t="inlineStr">
-        <is>
-          <t>L747: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Tel. r Ã© s.: 23686</t>
-        </is>
-      </c>
-      <c r="K197" s="1" t="inlineStr">
-        <is>
-          <t>L571: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: longue promenade en machine Ã lâ€™an-</t>
-        </is>
-      </c>
+      <c r="J197" s="1" t="inlineStr"/>
+      <c r="K197" s="1" t="inlineStr"/>
       <c r="L197" s="1" t="inlineStr"/>
       <c r="M197" s="1" t="inlineStr"/>
-      <c r="N197" s="1" t="inlineStr"/>
+      <c r="N197" s="1" t="inlineStr">
+        <is>
+          <t>L931: symbol-only separator/garbage line :: 10115</t>
+        </is>
+      </c>
       <c r="O197" s="1" t="inlineStr"/>
       <c r="P197" s="1" t="inlineStr"/>
       <c r="Q197" s="1" t="inlineStr"/>
@@ -8861,3322 +7397,6 @@
       <c r="X197" s="1" t="inlineStr"/>
       <c r="Y197" s="1" t="inlineStr"/>
     </row>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr"/>
-      <c r="B198" s="1" t="inlineStr"/>
-      <c r="C198" s="1" t="inlineStr"/>
-      <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr"/>
-      <c r="F198" s="1" t="inlineStr"/>
-      <c r="G198" s="1" t="inlineStr"/>
-      <c r="H198" s="1" t="inlineStr"/>
-      <c r="I198" s="1" t="inlineStr"/>
-      <c r="J198" s="1" t="inlineStr">
-        <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: EATON pour lâ€™automne</t>
-        </is>
-      </c>
-      <c r="K198" s="1" t="inlineStr">
-        <is>
-          <t>L572: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: cien foyer toujours si cher de QuÃ©bec.</t>
-        </is>
-      </c>
-      <c r="L198" s="1" t="inlineStr"/>
-      <c r="M198" s="1" t="inlineStr"/>
-      <c r="N198" s="1" t="inlineStr"/>
-      <c r="O198" s="1" t="inlineStr"/>
-      <c r="P198" s="1" t="inlineStr"/>
-      <c r="Q198" s="1" t="inlineStr"/>
-      <c r="R198" s="1" t="inlineStr"/>
-      <c r="S198" s="1" t="inlineStr"/>
-      <c r="T198" s="1" t="inlineStr"/>
-      <c r="U198" s="1" t="inlineStr"/>
-      <c r="V198" s="1" t="inlineStr"/>
-      <c r="W198" s="1" t="inlineStr"/>
-      <c r="X198" s="1" t="inlineStr"/>
-      <c r="Y198" s="1" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr"/>
-      <c r="B199" s="1" t="inlineStr"/>
-      <c r="C199" s="1" t="inlineStr"/>
-      <c r="D199" s="1" t="inlineStr"/>
-      <c r="E199" s="1" t="inlineStr"/>
-      <c r="F199" s="1" t="inlineStr"/>
-      <c r="G199" s="1" t="inlineStr"/>
-      <c r="H199" s="1" t="inlineStr"/>
-      <c r="I199" s="1" t="inlineStr"/>
-      <c r="J199" s="1" t="inlineStr">
-        <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 548 pages intÃ©ressantes!</t>
-        </is>
-      </c>
-      <c r="K199" s="1" t="inlineStr">
-        <is>
-          <t>L574: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Ils ont assistÃ© aussi au congrÃ¨s marial</t>
-        </is>
-      </c>
-      <c r="L199" s="1" t="inlineStr"/>
-      <c r="M199" s="1" t="inlineStr"/>
-      <c r="N199" s="1" t="inlineStr"/>
-      <c r="O199" s="1" t="inlineStr"/>
-      <c r="P199" s="1" t="inlineStr"/>
-      <c r="Q199" s="1" t="inlineStr"/>
-      <c r="R199" s="1" t="inlineStr"/>
-      <c r="S199" s="1" t="inlineStr"/>
-      <c r="T199" s="1" t="inlineStr"/>
-      <c r="U199" s="1" t="inlineStr"/>
-      <c r="V199" s="1" t="inlineStr"/>
-      <c r="W199" s="1" t="inlineStr"/>
-      <c r="X199" s="1" t="inlineStr"/>
-      <c r="Y199" s="1" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="inlineStr"/>
-      <c r="B200" s="1" t="inlineStr"/>
-      <c r="C200" s="1" t="inlineStr"/>
-      <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr"/>
-      <c r="F200" s="1" t="inlineStr"/>
-      <c r="G200" s="1" t="inlineStr"/>
-      <c r="H200" s="1" t="inlineStr"/>
-      <c r="I200" s="1" t="inlineStr"/>
-      <c r="J200" s="1" t="inlineStr">
-        <is>
-          <t>L777: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: plus rapproch Ã©. Si leur r Ã© serve est</t>
-        </is>
-      </c>
-      <c r="K200" s="1" t="inlineStr">
-        <is>
-          <t>L575: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: d'Ottawa, visitÃ© l'oratoire Saint-Joseph,</t>
-        </is>
-      </c>
-      <c r="L200" s="1" t="inlineStr"/>
-      <c r="M200" s="1" t="inlineStr"/>
-      <c r="N200" s="1" t="inlineStr"/>
-      <c r="O200" s="1" t="inlineStr"/>
-      <c r="P200" s="1" t="inlineStr"/>
-      <c r="Q200" s="1" t="inlineStr"/>
-      <c r="R200" s="1" t="inlineStr"/>
-      <c r="S200" s="1" t="inlineStr"/>
-      <c r="T200" s="1" t="inlineStr"/>
-      <c r="U200" s="1" t="inlineStr"/>
-      <c r="V200" s="1" t="inlineStr"/>
-      <c r="W200" s="1" t="inlineStr"/>
-      <c r="X200" s="1" t="inlineStr"/>
-      <c r="Y200" s="1" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="inlineStr"/>
-      <c r="B201" s="1" t="inlineStr"/>
-      <c r="C201" s="1" t="inlineStr"/>
-      <c r="D201" s="1" t="inlineStr"/>
-      <c r="E201" s="1" t="inlineStr"/>
-      <c r="F201" s="1" t="inlineStr"/>
-      <c r="G201" s="1" t="inlineStr"/>
-      <c r="H201" s="1" t="inlineStr"/>
-      <c r="I201" s="1" t="inlineStr"/>
-      <c r="J201" s="1" t="inlineStr">
-        <is>
-          <t>L778: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: puis Ã© e, Ã© crivez a: The Circula-</t>
-        </is>
-      </c>
-      <c r="K201" s="1" t="inlineStr">
-        <is>
-          <t>L576: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de MontrÃ©al, le foyer des jumelles Dion-</t>
-        </is>
-      </c>
-      <c r="L201" s="1" t="inlineStr"/>
-      <c r="M201" s="1" t="inlineStr"/>
-      <c r="N201" s="1" t="inlineStr"/>
-      <c r="O201" s="1" t="inlineStr"/>
-      <c r="P201" s="1" t="inlineStr"/>
-      <c r="Q201" s="1" t="inlineStr"/>
-      <c r="R201" s="1" t="inlineStr"/>
-      <c r="S201" s="1" t="inlineStr"/>
-      <c r="T201" s="1" t="inlineStr"/>
-      <c r="U201" s="1" t="inlineStr"/>
-      <c r="V201" s="1" t="inlineStr"/>
-      <c r="W201" s="1" t="inlineStr"/>
-      <c r="X201" s="1" t="inlineStr"/>
-      <c r="Y201" s="1" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="inlineStr"/>
-      <c r="B202" s="1" t="inlineStr"/>
-      <c r="C202" s="1" t="inlineStr"/>
-      <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr"/>
-      <c r="F202" s="1" t="inlineStr"/>
-      <c r="G202" s="1" t="inlineStr"/>
-      <c r="H202" s="1" t="inlineStr"/>
-      <c r="I202" s="1" t="inlineStr"/>
-      <c r="J202" s="1" t="inlineStr">
-        <is>
-          <t>L788: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Toronto, sont recommenc Ã© s selon de</t>
-        </is>
-      </c>
-      <c r="K202" s="1" t="inlineStr">
-        <is>
-          <t>L602: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l. 21861</t>
-        </is>
-      </c>
-      <c r="L202" s="1" t="inlineStr"/>
-      <c r="M202" s="1" t="inlineStr"/>
-      <c r="N202" s="1" t="inlineStr"/>
-      <c r="O202" s="1" t="inlineStr"/>
-      <c r="P202" s="1" t="inlineStr"/>
-      <c r="Q202" s="1" t="inlineStr"/>
-      <c r="R202" s="1" t="inlineStr"/>
-      <c r="S202" s="1" t="inlineStr"/>
-      <c r="T202" s="1" t="inlineStr"/>
-      <c r="U202" s="1" t="inlineStr"/>
-      <c r="V202" s="1" t="inlineStr"/>
-      <c r="W202" s="1" t="inlineStr"/>
-      <c r="X202" s="1" t="inlineStr"/>
-      <c r="Y202" s="1" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="1" t="inlineStr"/>
-      <c r="B203" s="1" t="inlineStr"/>
-      <c r="C203" s="1" t="inlineStr"/>
-      <c r="D203" s="1" t="inlineStr"/>
-      <c r="E203" s="1" t="inlineStr"/>
-      <c r="F203" s="1" t="inlineStr"/>
-      <c r="G203" s="1" t="inlineStr"/>
-      <c r="H203" s="1" t="inlineStr"/>
-      <c r="I203" s="1" t="inlineStr"/>
-      <c r="J203" s="1" t="inlineStr">
-        <is>
-          <t>L795: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les mariÃ©s, M. et Mme RenÃ© Lefebvre,</t>
-        </is>
-      </c>
-      <c r="K203" s="1" t="inlineStr">
-        <is>
-          <t>L608: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: re construire un magnifique couvent en :ne et puis Ste-Anne-de-BeauprÃ©, et</t>
-        </is>
-      </c>
-      <c r="L203" s="1" t="inlineStr"/>
-      <c r="M203" s="1" t="inlineStr"/>
-      <c r="N203" s="1" t="inlineStr"/>
-      <c r="O203" s="1" t="inlineStr"/>
-      <c r="P203" s="1" t="inlineStr"/>
-      <c r="Q203" s="1" t="inlineStr"/>
-      <c r="R203" s="1" t="inlineStr"/>
-      <c r="S203" s="1" t="inlineStr"/>
-      <c r="T203" s="1" t="inlineStr"/>
-      <c r="U203" s="1" t="inlineStr"/>
-      <c r="V203" s="1" t="inlineStr"/>
-      <c r="W203" s="1" t="inlineStr"/>
-      <c r="X203" s="1" t="inlineStr"/>
-      <c r="Y203" s="1" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="inlineStr"/>
-      <c r="B204" s="1" t="inlineStr"/>
-      <c r="C204" s="1" t="inlineStr"/>
-      <c r="D204" s="1" t="inlineStr"/>
-      <c r="E204" s="1" t="inlineStr"/>
-      <c r="F204" s="1" t="inlineStr"/>
-      <c r="G204" s="1" t="inlineStr"/>
-      <c r="H204" s="1" t="inlineStr"/>
-      <c r="I204" s="1" t="inlineStr"/>
-      <c r="J204" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et machines de Lionel Baril; une r Ã© si-</t>
-        </is>
-      </c>
-      <c r="K204" s="1" t="inlineStr">
-        <is>
-          <t>L609: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: face de l'Ã©glise. surtout St-Raymond, l'ancienne patrie</t>
-        </is>
-      </c>
-      <c r="L204" s="1" t="inlineStr"/>
-      <c r="M204" s="1" t="inlineStr"/>
-      <c r="N204" s="1" t="inlineStr"/>
-      <c r="O204" s="1" t="inlineStr"/>
-      <c r="P204" s="1" t="inlineStr"/>
-      <c r="Q204" s="1" t="inlineStr"/>
-      <c r="R204" s="1" t="inlineStr"/>
-      <c r="S204" s="1" t="inlineStr"/>
-      <c r="T204" s="1" t="inlineStr"/>
-      <c r="U204" s="1" t="inlineStr"/>
-      <c r="V204" s="1" t="inlineStr"/>
-      <c r="W204" s="1" t="inlineStr"/>
-      <c r="X204" s="1" t="inlineStr"/>
-      <c r="Y204" s="1" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="inlineStr"/>
-      <c r="B205" s="1" t="inlineStr"/>
-      <c r="C205" s="1" t="inlineStr"/>
-      <c r="D205" s="1" t="inlineStr"/>
-      <c r="E205" s="1" t="inlineStr"/>
-      <c r="F205" s="1" t="inlineStr"/>
-      <c r="G205" s="1" t="inlineStr"/>
-      <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr"/>
-      <c r="J205" s="1" t="inlineStr">
-        <is>
-          <t>L813: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dence de Aim Ã© Drouin; et une nouvelle</t>
-        </is>
-      </c>
-      <c r="K205" s="1" t="inlineStr">
-        <is>
-          <t>L613: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00A9 COPYRIGHT SIGN :: M. Louis Dalalire ouvrira son hÃ´tel au chauffeur, Lucille, Ã©tudiante en Cali-</t>
-        </is>
-      </c>
-      <c r="L205" s="1" t="inlineStr"/>
-      <c r="M205" s="1" t="inlineStr"/>
-      <c r="N205" s="1" t="inlineStr"/>
-      <c r="O205" s="1" t="inlineStr"/>
-      <c r="P205" s="1" t="inlineStr"/>
-      <c r="Q205" s="1" t="inlineStr"/>
-      <c r="R205" s="1" t="inlineStr"/>
-      <c r="S205" s="1" t="inlineStr"/>
-      <c r="T205" s="1" t="inlineStr"/>
-      <c r="U205" s="1" t="inlineStr"/>
-      <c r="V205" s="1" t="inlineStr"/>
-      <c r="W205" s="1" t="inlineStr"/>
-      <c r="X205" s="1" t="inlineStr"/>
-      <c r="Y205" s="1" t="inlineStr"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="inlineStr"/>
-      <c r="B206" s="1" t="inlineStr"/>
-      <c r="C206" s="1" t="inlineStr"/>
-      <c r="D206" s="1" t="inlineStr"/>
-      <c r="E206" s="1" t="inlineStr"/>
-      <c r="F206" s="1" t="inlineStr"/>
-      <c r="G206" s="1" t="inlineStr"/>
-      <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr"/>
-      <c r="J206" s="1" t="inlineStr">
-        <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La convalescence de notre curÃ© se pro-</t>
-        </is>
-      </c>
-      <c r="K206" s="1" t="inlineStr">
-        <is>
-          <t>L615: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vis et les chambres louÃ©es. i jeune. Le voyage fut heureux et agrÃ©a-</t>
-        </is>
-      </c>
-      <c r="L206" s="1" t="inlineStr"/>
-      <c r="M206" s="1" t="inlineStr"/>
-      <c r="N206" s="1" t="inlineStr"/>
-      <c r="O206" s="1" t="inlineStr"/>
-      <c r="P206" s="1" t="inlineStr"/>
-      <c r="Q206" s="1" t="inlineStr"/>
-      <c r="R206" s="1" t="inlineStr"/>
-      <c r="S206" s="1" t="inlineStr"/>
-      <c r="T206" s="1" t="inlineStr"/>
-      <c r="U206" s="1" t="inlineStr"/>
-      <c r="V206" s="1" t="inlineStr"/>
-      <c r="W206" s="1" t="inlineStr"/>
-      <c r="X206" s="1" t="inlineStr"/>
-      <c r="Y206" s="1" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="inlineStr"/>
-      <c r="B207" s="1" t="inlineStr"/>
-      <c r="C207" s="1" t="inlineStr"/>
-      <c r="D207" s="1" t="inlineStr"/>
-      <c r="E207" s="1" t="inlineStr"/>
-      <c r="F207" s="1" t="inlineStr"/>
-      <c r="G207" s="1" t="inlineStr"/>
-      <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr"/>
-      <c r="J207" s="1" t="inlineStr">
-        <is>
-          <t>L841: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: : frÃ¨re l l'abb Ã© J.- A. Normandeau, Ã© taient</t>
-        </is>
-      </c>
-      <c r="K207" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: chez sa fille, Mme Arthur Mageau, aprÃ¨s revenus tout ragaillardis.</t>
-        </is>
-      </c>
-      <c r="L207" s="1" t="inlineStr"/>
-      <c r="M207" s="1" t="inlineStr"/>
-      <c r="N207" s="1" t="inlineStr"/>
-      <c r="O207" s="1" t="inlineStr"/>
-      <c r="P207" s="1" t="inlineStr"/>
-      <c r="Q207" s="1" t="inlineStr"/>
-      <c r="R207" s="1" t="inlineStr"/>
-      <c r="S207" s="1" t="inlineStr"/>
-      <c r="T207" s="1" t="inlineStr"/>
-      <c r="U207" s="1" t="inlineStr"/>
-      <c r="V207" s="1" t="inlineStr"/>
-      <c r="W207" s="1" t="inlineStr"/>
-      <c r="X207" s="1" t="inlineStr"/>
-      <c r="Y207" s="1" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr"/>
-      <c r="B208" s="1" t="inlineStr"/>
-      <c r="C208" s="1" t="inlineStr"/>
-      <c r="D208" s="1" t="inlineStr"/>
-      <c r="E208" s="1" t="inlineStr"/>
-      <c r="F208" s="1" t="inlineStr"/>
-      <c r="G208" s="1" t="inlineStr"/>
-      <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr"/>
-      <c r="J208" s="1" t="inlineStr">
-        <is>
-          <t>L843: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Bougie est arrivante de MontrÃ©al,</t>
-        </is>
-      </c>
-      <c r="K208" s="1" t="inlineStr">
-        <is>
-          <t>L623: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: l'Ã©tÃ©, devient un peu inquiÃ©tante. Pres-</t>
-        </is>
-      </c>
-      <c r="L208" s="1" t="inlineStr"/>
-      <c r="M208" s="1" t="inlineStr"/>
-      <c r="N208" s="1" t="inlineStr"/>
-      <c r="O208" s="1" t="inlineStr"/>
-      <c r="P208" s="1" t="inlineStr"/>
-      <c r="Q208" s="1" t="inlineStr"/>
-      <c r="R208" s="1" t="inlineStr"/>
-      <c r="S208" s="1" t="inlineStr"/>
-      <c r="T208" s="1" t="inlineStr"/>
-      <c r="U208" s="1" t="inlineStr"/>
-      <c r="V208" s="1" t="inlineStr"/>
-      <c r="W208" s="1" t="inlineStr"/>
-      <c r="X208" s="1" t="inlineStr"/>
-      <c r="Y208" s="1" t="inlineStr"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="inlineStr"/>
-      <c r="B209" s="1" t="inlineStr"/>
-      <c r="C209" s="1" t="inlineStr"/>
-      <c r="D209" s="1" t="inlineStr"/>
-      <c r="E209" s="1" t="inlineStr"/>
-      <c r="F209" s="1" t="inlineStr"/>
-      <c r="G209" s="1" t="inlineStr"/>
-      <c r="H209" s="1" t="inlineStr"/>
-      <c r="I209" s="1" t="inlineStr"/>
-      <c r="J209" s="1" t="inlineStr">
-        <is>
-          <t>L849: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. lard Roberge a pass Ã© ses va-</t>
-        </is>
-      </c>
-      <c r="K209" s="1" t="inlineStr">
-        <is>
-          <t>L625: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: s'il fallait? La rÃ©colte est probablement</t>
-        </is>
-      </c>
-      <c r="L209" s="1" t="inlineStr"/>
-      <c r="M209" s="1" t="inlineStr"/>
-      <c r="N209" s="1" t="inlineStr"/>
-      <c r="O209" s="1" t="inlineStr"/>
-      <c r="P209" s="1" t="inlineStr"/>
-      <c r="Q209" s="1" t="inlineStr"/>
-      <c r="R209" s="1" t="inlineStr"/>
-      <c r="S209" s="1" t="inlineStr"/>
-      <c r="T209" s="1" t="inlineStr"/>
-      <c r="U209" s="1" t="inlineStr"/>
-      <c r="V209" s="1" t="inlineStr"/>
-      <c r="W209" s="1" t="inlineStr"/>
-      <c r="X209" s="1" t="inlineStr"/>
-      <c r="Y209" s="1" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="inlineStr"/>
-      <c r="B210" s="1" t="inlineStr"/>
-      <c r="C210" s="1" t="inlineStr"/>
-      <c r="D210" s="1" t="inlineStr"/>
-      <c r="E210" s="1" t="inlineStr"/>
-      <c r="F210" s="1" t="inlineStr"/>
-      <c r="G210" s="1" t="inlineStr"/>
-      <c r="H210" s="1" t="inlineStr"/>
-      <c r="I210" s="1" t="inlineStr"/>
-      <c r="J210" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: haitons bon voyage. La grand'm Ã¨ re a</t>
-        </is>
-      </c>
-      <c r="K210" s="1" t="inlineStr">
-        <is>
-          <t>L628: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le village est maintenant incorporÃ©</t>
-        </is>
-      </c>
-      <c r="L210" s="1" t="inlineStr"/>
-      <c r="M210" s="1" t="inlineStr"/>
-      <c r="N210" s="1" t="inlineStr"/>
-      <c r="O210" s="1" t="inlineStr"/>
-      <c r="P210" s="1" t="inlineStr"/>
-      <c r="Q210" s="1" t="inlineStr"/>
-      <c r="R210" s="1" t="inlineStr"/>
-      <c r="S210" s="1" t="inlineStr"/>
-      <c r="T210" s="1" t="inlineStr"/>
-      <c r="U210" s="1" t="inlineStr"/>
-      <c r="V210" s="1" t="inlineStr"/>
-      <c r="W210" s="1" t="inlineStr"/>
-      <c r="X210" s="1" t="inlineStr"/>
-      <c r="Y210" s="1" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="inlineStr"/>
-      <c r="B211" s="1" t="inlineStr"/>
-      <c r="C211" s="1" t="inlineStr"/>
-      <c r="D211" s="1" t="inlineStr"/>
-      <c r="E211" s="1" t="inlineStr"/>
-      <c r="F211" s="1" t="inlineStr"/>
-      <c r="G211" s="1" t="inlineStr"/>
-      <c r="H211" s="1" t="inlineStr"/>
-      <c r="I211" s="1" t="inlineStr"/>
-      <c r="J211" s="1" t="inlineStr">
-        <is>
-          <t>L872: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. Roland PagÃ©, aviateur civil, ater-</t>
-        </is>
-      </c>
-      <c r="K211" s="1" t="inlineStr">
-        <is>
-          <t>L629: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et notre conseiller, M. Dan SadomÃ©, tra-</t>
-        </is>
-      </c>
-      <c r="L211" s="1" t="inlineStr"/>
-      <c r="M211" s="1" t="inlineStr"/>
-      <c r="N211" s="1" t="inlineStr"/>
-      <c r="O211" s="1" t="inlineStr"/>
-      <c r="P211" s="1" t="inlineStr"/>
-      <c r="Q211" s="1" t="inlineStr"/>
-      <c r="R211" s="1" t="inlineStr"/>
-      <c r="S211" s="1" t="inlineStr"/>
-      <c r="T211" s="1" t="inlineStr"/>
-      <c r="U211" s="1" t="inlineStr"/>
-      <c r="V211" s="1" t="inlineStr"/>
-      <c r="W211" s="1" t="inlineStr"/>
-      <c r="X211" s="1" t="inlineStr"/>
-      <c r="Y211" s="1" t="inlineStr"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="inlineStr"/>
-      <c r="B212" s="1" t="inlineStr"/>
-      <c r="C212" s="1" t="inlineStr"/>
-      <c r="D212" s="1" t="inlineStr"/>
-      <c r="E212" s="1" t="inlineStr"/>
-      <c r="F212" s="1" t="inlineStr"/>
-      <c r="G212" s="1" t="inlineStr"/>
-      <c r="H212" s="1" t="inlineStr"/>
-      <c r="I212" s="1" t="inlineStr"/>
-      <c r="J212" s="1" t="inlineStr">
-        <is>
-          <t>L874: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans un champ de blÃ© de M. Dan Mc-</t>
-        </is>
-      </c>
-      <c r="K212" s="1" t="inlineStr">
-        <is>
-          <t>L630: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: vaille de son mieux pour faire des amÃ©-</t>
-        </is>
-      </c>
-      <c r="L212" s="1" t="inlineStr"/>
-      <c r="M212" s="1" t="inlineStr"/>
-      <c r="N212" s="1" t="inlineStr"/>
-      <c r="O212" s="1" t="inlineStr"/>
-      <c r="P212" s="1" t="inlineStr"/>
-      <c r="Q212" s="1" t="inlineStr"/>
-      <c r="R212" s="1" t="inlineStr"/>
-      <c r="S212" s="1" t="inlineStr"/>
-      <c r="T212" s="1" t="inlineStr"/>
-      <c r="U212" s="1" t="inlineStr"/>
-      <c r="V212" s="1" t="inlineStr"/>
-      <c r="W212" s="1" t="inlineStr"/>
-      <c r="X212" s="1" t="inlineStr"/>
-      <c r="Y212" s="1" t="inlineStr"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="inlineStr"/>
-      <c r="B213" s="1" t="inlineStr"/>
-      <c r="C213" s="1" t="inlineStr"/>
-      <c r="D213" s="1" t="inlineStr"/>
-      <c r="E213" s="1" t="inlineStr"/>
-      <c r="F213" s="1" t="inlineStr"/>
-      <c r="G213" s="1" t="inlineStr"/>
-      <c r="H213" s="1" t="inlineStr"/>
-      <c r="I213" s="1" t="inlineStr"/>
-      <c r="J213" s="1" t="inlineStr">
-        <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Kenzie pour venir rencontrer son Ã© pouse</t>
-        </is>
-      </c>
-      <c r="K213" s="1" t="inlineStr">
-        <is>
-          <t>L633: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: aussi d'un hÃ´pital Ã Boyle.</t>
-        </is>
-      </c>
-      <c r="L213" s="1" t="inlineStr"/>
-      <c r="M213" s="1" t="inlineStr"/>
-      <c r="N213" s="1" t="inlineStr"/>
-      <c r="O213" s="1" t="inlineStr"/>
-      <c r="P213" s="1" t="inlineStr"/>
-      <c r="Q213" s="1" t="inlineStr"/>
-      <c r="R213" s="1" t="inlineStr"/>
-      <c r="S213" s="1" t="inlineStr"/>
-      <c r="T213" s="1" t="inlineStr"/>
-      <c r="U213" s="1" t="inlineStr"/>
-      <c r="V213" s="1" t="inlineStr"/>
-      <c r="W213" s="1" t="inlineStr"/>
-      <c r="X213" s="1" t="inlineStr"/>
-      <c r="Y213" s="1" t="inlineStr"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="inlineStr"/>
-      <c r="B214" s="1" t="inlineStr"/>
-      <c r="C214" s="1" t="inlineStr"/>
-      <c r="D214" s="1" t="inlineStr"/>
-      <c r="E214" s="1" t="inlineStr"/>
-      <c r="F214" s="1" t="inlineStr"/>
-      <c r="G214" s="1" t="inlineStr"/>
-      <c r="H214" s="1" t="inlineStr"/>
-      <c r="I214" s="1" t="inlineStr"/>
-      <c r="J214" s="1" t="inlineStr">
-        <is>
-          <t>L876: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et son b Ã© b Ã© qui sont en visite de trois</t>
-        </is>
-      </c>
-      <c r="K214" s="1" t="inlineStr">
-        <is>
-          <t>L637: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Le pique-nique au profit de l'Ã©glise de</t>
-        </is>
-      </c>
-      <c r="L214" s="1" t="inlineStr"/>
-      <c r="M214" s="1" t="inlineStr"/>
-      <c r="N214" s="1" t="inlineStr"/>
-      <c r="O214" s="1" t="inlineStr"/>
-      <c r="P214" s="1" t="inlineStr"/>
-      <c r="Q214" s="1" t="inlineStr"/>
-      <c r="R214" s="1" t="inlineStr"/>
-      <c r="S214" s="1" t="inlineStr"/>
-      <c r="T214" s="1" t="inlineStr"/>
-      <c r="U214" s="1" t="inlineStr"/>
-      <c r="V214" s="1" t="inlineStr"/>
-      <c r="W214" s="1" t="inlineStr"/>
-      <c r="X214" s="1" t="inlineStr"/>
-      <c r="Y214" s="1" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="inlineStr"/>
-      <c r="B215" s="1" t="inlineStr"/>
-      <c r="C215" s="1" t="inlineStr"/>
-      <c r="D215" s="1" t="inlineStr"/>
-      <c r="E215" s="1" t="inlineStr"/>
-      <c r="F215" s="1" t="inlineStr"/>
-      <c r="G215" s="1" t="inlineStr"/>
-      <c r="H215" s="1" t="inlineStr"/>
-      <c r="I215" s="1" t="inlineStr"/>
-      <c r="J215" s="1" t="inlineStr">
-        <is>
-          <t>L883: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Rom Ã© o Hurtubise, grand'mere Pat</t>
-        </is>
-      </c>
-      <c r="K215" s="1" t="inlineStr">
-        <is>
-          <t>L638: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: Donatville, dimanche dernier, fut trÃ¨s</t>
-        </is>
-      </c>
-      <c r="L215" s="1" t="inlineStr"/>
-      <c r="M215" s="1" t="inlineStr"/>
-      <c r="N215" s="1" t="inlineStr"/>
-      <c r="O215" s="1" t="inlineStr"/>
-      <c r="P215" s="1" t="inlineStr"/>
-      <c r="Q215" s="1" t="inlineStr"/>
-      <c r="R215" s="1" t="inlineStr"/>
-      <c r="S215" s="1" t="inlineStr"/>
-      <c r="T215" s="1" t="inlineStr"/>
-      <c r="U215" s="1" t="inlineStr"/>
-      <c r="V215" s="1" t="inlineStr"/>
-      <c r="W215" s="1" t="inlineStr"/>
-      <c r="X215" s="1" t="inlineStr"/>
-      <c r="Y215" s="1" t="inlineStr"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="inlineStr"/>
-      <c r="B216" s="1" t="inlineStr"/>
-      <c r="C216" s="1" t="inlineStr"/>
-      <c r="D216" s="1" t="inlineStr"/>
-      <c r="E216" s="1" t="inlineStr"/>
-      <c r="F216" s="1" t="inlineStr"/>
-      <c r="G216" s="1" t="inlineStr"/>
-      <c r="H216" s="1" t="inlineStr"/>
-      <c r="I216" s="1" t="inlineStr"/>
-      <c r="J216" s="1" t="inlineStr">
-        <is>
-          <t>L884: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: McKenzie, tante CÃ©cile et Roland Page,</t>
-        </is>
-      </c>
-      <c r="K216" s="1" t="inlineStr">
-        <is>
-          <t>L639: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: achalandÃ©. L'autre pique-nique d'il ya</t>
-        </is>
-      </c>
-      <c r="L216" s="1" t="inlineStr"/>
-      <c r="M216" s="1" t="inlineStr"/>
-      <c r="N216" s="1" t="inlineStr"/>
-      <c r="O216" s="1" t="inlineStr"/>
-      <c r="P216" s="1" t="inlineStr"/>
-      <c r="Q216" s="1" t="inlineStr"/>
-      <c r="R216" s="1" t="inlineStr"/>
-      <c r="S216" s="1" t="inlineStr"/>
-      <c r="T216" s="1" t="inlineStr"/>
-      <c r="U216" s="1" t="inlineStr"/>
-      <c r="V216" s="1" t="inlineStr"/>
-      <c r="W216" s="1" t="inlineStr"/>
-      <c r="X216" s="1" t="inlineStr"/>
-      <c r="Y216" s="1" t="inlineStr"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="inlineStr"/>
-      <c r="B217" s="1" t="inlineStr"/>
-      <c r="C217" s="1" t="inlineStr"/>
-      <c r="D217" s="1" t="inlineStr"/>
-      <c r="E217" s="1" t="inlineStr"/>
-      <c r="F217" s="1" t="inlineStr"/>
-      <c r="G217" s="1" t="inlineStr"/>
-      <c r="H217" s="1" t="inlineStr"/>
-      <c r="I217" s="1" t="inlineStr"/>
-      <c r="J217" s="1" t="inlineStr">
-        <is>
-          <t>L888: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: gnie Eldorado, et notre hÃ´te, le jeune</t>
-        </is>
-      </c>
-      <c r="K217" s="1" t="inlineStr">
-        <is>
-          <t>L650: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: qui s'enrÃ´la l'un des premiers Ã Ed-</t>
-        </is>
-      </c>
-      <c r="L217" s="1" t="inlineStr"/>
-      <c r="M217" s="1" t="inlineStr"/>
-      <c r="N217" s="1" t="inlineStr"/>
-      <c r="O217" s="1" t="inlineStr"/>
-      <c r="P217" s="1" t="inlineStr"/>
-      <c r="Q217" s="1" t="inlineStr"/>
-      <c r="R217" s="1" t="inlineStr"/>
-      <c r="S217" s="1" t="inlineStr"/>
-      <c r="T217" s="1" t="inlineStr"/>
-      <c r="U217" s="1" t="inlineStr"/>
-      <c r="V217" s="1" t="inlineStr"/>
-      <c r="W217" s="1" t="inlineStr"/>
-      <c r="X217" s="1" t="inlineStr"/>
-      <c r="Y217" s="1" t="inlineStr"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="inlineStr"/>
-      <c r="B218" s="1" t="inlineStr"/>
-      <c r="C218" s="1" t="inlineStr"/>
-      <c r="D218" s="1" t="inlineStr"/>
-      <c r="E218" s="1" t="inlineStr"/>
-      <c r="F218" s="1" t="inlineStr"/>
-      <c r="G218" s="1" t="inlineStr"/>
-      <c r="H218" s="1" t="inlineStr"/>
-      <c r="I218" s="1" t="inlineStr"/>
-      <c r="J218" s="1" t="inlineStr">
-        <is>
-          <t>L897: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: hild, est en d Ã© cision d'acheter un hÃ´tel</t>
-        </is>
-      </c>
-      <c r="K218" s="1" t="inlineStr">
-        <is>
-          <t>L655: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: M. et Mme Floyd , Richard et grandâ€™-</t>
-        </is>
-      </c>
-      <c r="L218" s="1" t="inlineStr"/>
-      <c r="M218" s="1" t="inlineStr"/>
-      <c r="N218" s="1" t="inlineStr"/>
-      <c r="O218" s="1" t="inlineStr"/>
-      <c r="P218" s="1" t="inlineStr"/>
-      <c r="Q218" s="1" t="inlineStr"/>
-      <c r="R218" s="1" t="inlineStr"/>
-      <c r="S218" s="1" t="inlineStr"/>
-      <c r="T218" s="1" t="inlineStr"/>
-      <c r="U218" s="1" t="inlineStr"/>
-      <c r="V218" s="1" t="inlineStr"/>
-      <c r="W218" s="1" t="inlineStr"/>
-      <c r="X218" s="1" t="inlineStr"/>
-      <c r="Y218" s="1" t="inlineStr"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="inlineStr"/>
-      <c r="B219" s="1" t="inlineStr"/>
-      <c r="C219" s="1" t="inlineStr"/>
-      <c r="D219" s="1" t="inlineStr"/>
-      <c r="E219" s="1" t="inlineStr"/>
-      <c r="F219" s="1" t="inlineStr"/>
-      <c r="G219" s="1" t="inlineStr"/>
-      <c r="H219" s="1" t="inlineStr"/>
-      <c r="I219" s="1" t="inlineStr"/>
-      <c r="J219" s="1" t="inlineStr">
-        <is>
-          <t>L911: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: å“�</t>
-        </is>
-      </c>
-      <c r="K219" s="1" t="inlineStr">
-        <is>
-          <t>L656: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: mÃ¨re Melvin sont partis pour des vacan-</t>
-        </is>
-      </c>
-      <c r="L219" s="1" t="inlineStr"/>
-      <c r="M219" s="1" t="inlineStr"/>
-      <c r="N219" s="1" t="inlineStr"/>
-      <c r="O219" s="1" t="inlineStr"/>
-      <c r="P219" s="1" t="inlineStr"/>
-      <c r="Q219" s="1" t="inlineStr"/>
-      <c r="R219" s="1" t="inlineStr"/>
-      <c r="S219" s="1" t="inlineStr"/>
-      <c r="T219" s="1" t="inlineStr"/>
-      <c r="U219" s="1" t="inlineStr"/>
-      <c r="V219" s="1" t="inlineStr"/>
-      <c r="W219" s="1" t="inlineStr"/>
-      <c r="X219" s="1" t="inlineStr"/>
-      <c r="Y219" s="1" t="inlineStr"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="inlineStr"/>
-      <c r="B220" s="1" t="inlineStr"/>
-      <c r="C220" s="1" t="inlineStr"/>
-      <c r="D220" s="1" t="inlineStr"/>
-      <c r="E220" s="1" t="inlineStr"/>
-      <c r="F220" s="1" t="inlineStr"/>
-      <c r="G220" s="1" t="inlineStr"/>
-      <c r="H220" s="1" t="inlineStr"/>
-      <c r="I220" s="1" t="inlineStr"/>
-      <c r="J220" s="1" t="inlineStr">
-        <is>
-          <t>L930: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bijoutier â€” Horloger</t>
-        </is>
-      </c>
-      <c r="K220" s="1" t="inlineStr">
-        <is>
-          <t>L658: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: de la RiviÃ¨re-la-Paix. Nous leur sou-</t>
-        </is>
-      </c>
-      <c r="L220" s="1" t="inlineStr"/>
-      <c r="M220" s="1" t="inlineStr"/>
-      <c r="N220" s="1" t="inlineStr"/>
-      <c r="O220" s="1" t="inlineStr"/>
-      <c r="P220" s="1" t="inlineStr"/>
-      <c r="Q220" s="1" t="inlineStr"/>
-      <c r="R220" s="1" t="inlineStr"/>
-      <c r="S220" s="1" t="inlineStr"/>
-      <c r="T220" s="1" t="inlineStr"/>
-      <c r="U220" s="1" t="inlineStr"/>
-      <c r="V220" s="1" t="inlineStr"/>
-      <c r="W220" s="1" t="inlineStr"/>
-      <c r="X220" s="1" t="inlineStr"/>
-      <c r="Y220" s="1" t="inlineStr"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="inlineStr"/>
-      <c r="B221" s="1" t="inlineStr"/>
-      <c r="C221" s="1" t="inlineStr"/>
-      <c r="D221" s="1" t="inlineStr"/>
-      <c r="E221" s="1" t="inlineStr"/>
-      <c r="F221" s="1" t="inlineStr"/>
-      <c r="G221" s="1" t="inlineStr"/>
-      <c r="H221" s="1" t="inlineStr"/>
-      <c r="I221" s="1" t="inlineStr"/>
-      <c r="J221" s="1" t="inlineStr"/>
-      <c r="K221" s="1" t="inlineStr">
-        <is>
-          <t>L659: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: haitons bon voyage. La grand'mÃ¨re a</t>
-        </is>
-      </c>
-      <c r="L221" s="1" t="inlineStr"/>
-      <c r="M221" s="1" t="inlineStr"/>
-      <c r="N221" s="1" t="inlineStr"/>
-      <c r="O221" s="1" t="inlineStr"/>
-      <c r="P221" s="1" t="inlineStr"/>
-      <c r="Q221" s="1" t="inlineStr"/>
-      <c r="R221" s="1" t="inlineStr"/>
-      <c r="S221" s="1" t="inlineStr"/>
-      <c r="T221" s="1" t="inlineStr"/>
-      <c r="U221" s="1" t="inlineStr"/>
-      <c r="V221" s="1" t="inlineStr"/>
-      <c r="W221" s="1" t="inlineStr"/>
-      <c r="X221" s="1" t="inlineStr"/>
-      <c r="Y221" s="1" t="inlineStr"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="inlineStr"/>
-      <c r="B222" s="1" t="inlineStr"/>
-      <c r="C222" s="1" t="inlineStr"/>
-      <c r="D222" s="1" t="inlineStr"/>
-      <c r="E222" s="1" t="inlineStr"/>
-      <c r="F222" s="1" t="inlineStr"/>
-      <c r="G222" s="1" t="inlineStr"/>
-      <c r="H222" s="1" t="inlineStr"/>
-      <c r="I222" s="1" t="inlineStr"/>
-      <c r="J222" s="1" t="inlineStr"/>
-      <c r="K222" s="1" t="inlineStr">
-        <is>
-          <t>L664: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. Roland PagÃ©, aviateur civil, ater-</t>
-        </is>
-      </c>
-      <c r="L222" s="1" t="inlineStr"/>
-      <c r="M222" s="1" t="inlineStr"/>
-      <c r="N222" s="1" t="inlineStr"/>
-      <c r="O222" s="1" t="inlineStr"/>
-      <c r="P222" s="1" t="inlineStr"/>
-      <c r="Q222" s="1" t="inlineStr"/>
-      <c r="R222" s="1" t="inlineStr"/>
-      <c r="S222" s="1" t="inlineStr"/>
-      <c r="T222" s="1" t="inlineStr"/>
-      <c r="U222" s="1" t="inlineStr"/>
-      <c r="V222" s="1" t="inlineStr"/>
-      <c r="W222" s="1" t="inlineStr"/>
-      <c r="X222" s="1" t="inlineStr"/>
-      <c r="Y222" s="1" t="inlineStr"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="1" t="inlineStr"/>
-      <c r="B223" s="1" t="inlineStr"/>
-      <c r="C223" s="1" t="inlineStr"/>
-      <c r="D223" s="1" t="inlineStr"/>
-      <c r="E223" s="1" t="inlineStr"/>
-      <c r="F223" s="1" t="inlineStr"/>
-      <c r="G223" s="1" t="inlineStr"/>
-      <c r="H223" s="1" t="inlineStr"/>
-      <c r="I223" s="1" t="inlineStr"/>
-      <c r="J223" s="1" t="inlineStr"/>
-      <c r="K223" s="1" t="inlineStr">
-        <is>
-          <t>L666: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dans un champ de blÃ© de M. Dan Mc-</t>
-        </is>
-      </c>
-      <c r="L223" s="1" t="inlineStr"/>
-      <c r="M223" s="1" t="inlineStr"/>
-      <c r="N223" s="1" t="inlineStr"/>
-      <c r="O223" s="1" t="inlineStr"/>
-      <c r="P223" s="1" t="inlineStr"/>
-      <c r="Q223" s="1" t="inlineStr"/>
-      <c r="R223" s="1" t="inlineStr"/>
-      <c r="S223" s="1" t="inlineStr"/>
-      <c r="T223" s="1" t="inlineStr"/>
-      <c r="U223" s="1" t="inlineStr"/>
-      <c r="V223" s="1" t="inlineStr"/>
-      <c r="W223" s="1" t="inlineStr"/>
-      <c r="X223" s="1" t="inlineStr"/>
-      <c r="Y223" s="1" t="inlineStr"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="inlineStr"/>
-      <c r="B224" s="1" t="inlineStr"/>
-      <c r="C224" s="1" t="inlineStr"/>
-      <c r="D224" s="1" t="inlineStr"/>
-      <c r="E224" s="1" t="inlineStr"/>
-      <c r="F224" s="1" t="inlineStr"/>
-      <c r="G224" s="1" t="inlineStr"/>
-      <c r="H224" s="1" t="inlineStr"/>
-      <c r="I224" s="1" t="inlineStr"/>
-      <c r="J224" s="1" t="inlineStr"/>
-      <c r="K224" s="1" t="inlineStr">
-        <is>
-          <t>L667: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Kenzie pour venir rencontrer son Ã©pouse</t>
-        </is>
-      </c>
-      <c r="L224" s="1" t="inlineStr"/>
-      <c r="M224" s="1" t="inlineStr"/>
-      <c r="N224" s="1" t="inlineStr"/>
-      <c r="O224" s="1" t="inlineStr"/>
-      <c r="P224" s="1" t="inlineStr"/>
-      <c r="Q224" s="1" t="inlineStr"/>
-      <c r="R224" s="1" t="inlineStr"/>
-      <c r="S224" s="1" t="inlineStr"/>
-      <c r="T224" s="1" t="inlineStr"/>
-      <c r="U224" s="1" t="inlineStr"/>
-      <c r="V224" s="1" t="inlineStr"/>
-      <c r="W224" s="1" t="inlineStr"/>
-      <c r="X224" s="1" t="inlineStr"/>
-      <c r="Y224" s="1" t="inlineStr"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="inlineStr"/>
-      <c r="B225" s="1" t="inlineStr"/>
-      <c r="C225" s="1" t="inlineStr"/>
-      <c r="D225" s="1" t="inlineStr"/>
-      <c r="E225" s="1" t="inlineStr"/>
-      <c r="F225" s="1" t="inlineStr"/>
-      <c r="G225" s="1" t="inlineStr"/>
-      <c r="H225" s="1" t="inlineStr"/>
-      <c r="I225" s="1" t="inlineStr"/>
-      <c r="J225" s="1" t="inlineStr"/>
-      <c r="K225" s="1" t="inlineStr">
-        <is>
-          <t>L668: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et son bÃ©bÃ© qui sont en visite de trois</t>
-        </is>
-      </c>
-      <c r="L225" s="1" t="inlineStr"/>
-      <c r="M225" s="1" t="inlineStr"/>
-      <c r="N225" s="1" t="inlineStr"/>
-      <c r="O225" s="1" t="inlineStr"/>
-      <c r="P225" s="1" t="inlineStr"/>
-      <c r="Q225" s="1" t="inlineStr"/>
-      <c r="R225" s="1" t="inlineStr"/>
-      <c r="S225" s="1" t="inlineStr"/>
-      <c r="T225" s="1" t="inlineStr"/>
-      <c r="U225" s="1" t="inlineStr"/>
-      <c r="V225" s="1" t="inlineStr"/>
-      <c r="W225" s="1" t="inlineStr"/>
-      <c r="X225" s="1" t="inlineStr"/>
-      <c r="Y225" s="1" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="inlineStr"/>
-      <c r="B226" s="1" t="inlineStr"/>
-      <c r="C226" s="1" t="inlineStr"/>
-      <c r="D226" s="1" t="inlineStr"/>
-      <c r="E226" s="1" t="inlineStr"/>
-      <c r="F226" s="1" t="inlineStr"/>
-      <c r="G226" s="1" t="inlineStr"/>
-      <c r="H226" s="1" t="inlineStr"/>
-      <c r="I226" s="1" t="inlineStr"/>
-      <c r="J226" s="1" t="inlineStr"/>
-      <c r="K226" s="1" t="inlineStr">
-        <is>
-          <t>L672: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: Un grand dÃ®ner avait lieu dimanche Ã</t>
-        </is>
-      </c>
-      <c r="L226" s="1" t="inlineStr"/>
-      <c r="M226" s="1" t="inlineStr"/>
-      <c r="N226" s="1" t="inlineStr"/>
-      <c r="O226" s="1" t="inlineStr"/>
-      <c r="P226" s="1" t="inlineStr"/>
-      <c r="Q226" s="1" t="inlineStr"/>
-      <c r="R226" s="1" t="inlineStr"/>
-      <c r="S226" s="1" t="inlineStr"/>
-      <c r="T226" s="1" t="inlineStr"/>
-      <c r="U226" s="1" t="inlineStr"/>
-      <c r="V226" s="1" t="inlineStr"/>
-      <c r="W226" s="1" t="inlineStr"/>
-      <c r="X226" s="1" t="inlineStr"/>
-      <c r="Y226" s="1" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="inlineStr"/>
-      <c r="B227" s="1" t="inlineStr"/>
-      <c r="C227" s="1" t="inlineStr"/>
-      <c r="D227" s="1" t="inlineStr"/>
-      <c r="E227" s="1" t="inlineStr"/>
-      <c r="F227" s="1" t="inlineStr"/>
-      <c r="G227" s="1" t="inlineStr"/>
-      <c r="H227" s="1" t="inlineStr"/>
-      <c r="I227" s="1" t="inlineStr"/>
-      <c r="J227" s="1" t="inlineStr"/>
-      <c r="K227" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sistaient: ses parents, M. etâ€™ Mme IrÃ</t>
-        </is>
-      </c>
-      <c r="L227" s="1" t="inlineStr"/>
-      <c r="M227" s="1" t="inlineStr"/>
-      <c r="N227" s="1" t="inlineStr"/>
-      <c r="O227" s="1" t="inlineStr"/>
-      <c r="P227" s="1" t="inlineStr"/>
-      <c r="Q227" s="1" t="inlineStr"/>
-      <c r="R227" s="1" t="inlineStr"/>
-      <c r="S227" s="1" t="inlineStr"/>
-      <c r="T227" s="1" t="inlineStr"/>
-      <c r="U227" s="1" t="inlineStr"/>
-      <c r="V227" s="1" t="inlineStr"/>
-      <c r="W227" s="1" t="inlineStr"/>
-      <c r="X227" s="1" t="inlineStr"/>
-      <c r="Y227" s="1" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="inlineStr"/>
-      <c r="B228" s="1" t="inlineStr"/>
-      <c r="C228" s="1" t="inlineStr"/>
-      <c r="D228" s="1" t="inlineStr"/>
-      <c r="E228" s="1" t="inlineStr"/>
-      <c r="F228" s="1" t="inlineStr"/>
-      <c r="G228" s="1" t="inlineStr"/>
-      <c r="H228" s="1" t="inlineStr"/>
-      <c r="I228" s="1" t="inlineStr"/>
-      <c r="J228" s="1" t="inlineStr"/>
-      <c r="K228" s="1" t="inlineStr">
-        <is>
-          <t>L677: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A8 DIAERESIS :: Mme RomÃ©o Hurtubise, grand'mÃ¨re Pat</t>
-        </is>
-      </c>
-      <c r="L228" s="1" t="inlineStr"/>
-      <c r="M228" s="1" t="inlineStr"/>
-      <c r="N228" s="1" t="inlineStr"/>
-      <c r="O228" s="1" t="inlineStr"/>
-      <c r="P228" s="1" t="inlineStr"/>
-      <c r="Q228" s="1" t="inlineStr"/>
-      <c r="R228" s="1" t="inlineStr"/>
-      <c r="S228" s="1" t="inlineStr"/>
-      <c r="T228" s="1" t="inlineStr"/>
-      <c r="U228" s="1" t="inlineStr"/>
-      <c r="V228" s="1" t="inlineStr"/>
-      <c r="W228" s="1" t="inlineStr"/>
-      <c r="X228" s="1" t="inlineStr"/>
-      <c r="Y228" s="1" t="inlineStr"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="1" t="inlineStr"/>
-      <c r="B229" s="1" t="inlineStr"/>
-      <c r="C229" s="1" t="inlineStr"/>
-      <c r="D229" s="1" t="inlineStr"/>
-      <c r="E229" s="1" t="inlineStr"/>
-      <c r="F229" s="1" t="inlineStr"/>
-      <c r="G229" s="1" t="inlineStr"/>
-      <c r="H229" s="1" t="inlineStr"/>
-      <c r="I229" s="1" t="inlineStr"/>
-      <c r="J229" s="1" t="inlineStr"/>
-      <c r="K229" s="1" t="inlineStr">
-        <is>
-          <t>L678: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: McKenzie, tante CÃ©cile et Roland PagÃ©,</t>
-        </is>
-      </c>
-      <c r="L229" s="1" t="inlineStr"/>
-      <c r="M229" s="1" t="inlineStr"/>
-      <c r="N229" s="1" t="inlineStr"/>
-      <c r="O229" s="1" t="inlineStr"/>
-      <c r="P229" s="1" t="inlineStr"/>
-      <c r="Q229" s="1" t="inlineStr"/>
-      <c r="R229" s="1" t="inlineStr"/>
-      <c r="S229" s="1" t="inlineStr"/>
-      <c r="T229" s="1" t="inlineStr"/>
-      <c r="U229" s="1" t="inlineStr"/>
-      <c r="V229" s="1" t="inlineStr"/>
-      <c r="W229" s="1" t="inlineStr"/>
-      <c r="X229" s="1" t="inlineStr"/>
-      <c r="Y229" s="1" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="1" t="inlineStr"/>
-      <c r="B230" s="1" t="inlineStr"/>
-      <c r="C230" s="1" t="inlineStr"/>
-      <c r="D230" s="1" t="inlineStr"/>
-      <c r="E230" s="1" t="inlineStr"/>
-      <c r="F230" s="1" t="inlineStr"/>
-      <c r="G230" s="1" t="inlineStr"/>
-      <c r="H230" s="1" t="inlineStr"/>
-      <c r="I230" s="1" t="inlineStr"/>
-      <c r="J230" s="1" t="inlineStr"/>
-      <c r="K230" s="1" t="inlineStr">
-        <is>
-          <t>L679: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: M. Amos Chambers et IrÃ¨ne White, de</t>
-        </is>
-      </c>
-      <c r="L230" s="1" t="inlineStr"/>
-      <c r="M230" s="1" t="inlineStr"/>
-      <c r="N230" s="1" t="inlineStr"/>
-      <c r="O230" s="1" t="inlineStr"/>
-      <c r="P230" s="1" t="inlineStr"/>
-      <c r="Q230" s="1" t="inlineStr"/>
-      <c r="R230" s="1" t="inlineStr"/>
-      <c r="S230" s="1" t="inlineStr"/>
-      <c r="T230" s="1" t="inlineStr"/>
-      <c r="U230" s="1" t="inlineStr"/>
-      <c r="V230" s="1" t="inlineStr"/>
-      <c r="W230" s="1" t="inlineStr"/>
-      <c r="X230" s="1" t="inlineStr"/>
-      <c r="Y230" s="1" t="inlineStr"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="1" t="inlineStr"/>
-      <c r="B231" s="1" t="inlineStr"/>
-      <c r="C231" s="1" t="inlineStr"/>
-      <c r="D231" s="1" t="inlineStr"/>
-      <c r="E231" s="1" t="inlineStr"/>
-      <c r="F231" s="1" t="inlineStr"/>
-      <c r="G231" s="1" t="inlineStr"/>
-      <c r="H231" s="1" t="inlineStr"/>
-      <c r="I231" s="1" t="inlineStr"/>
-      <c r="J231" s="1" t="inlineStr"/>
-      <c r="K231" s="1" t="inlineStr">
-        <is>
-          <t>L682: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: gnie Eldorado, et notre hÃ´te, le jeune</t>
-        </is>
-      </c>
-      <c r="L231" s="1" t="inlineStr"/>
-      <c r="M231" s="1" t="inlineStr"/>
-      <c r="N231" s="1" t="inlineStr"/>
-      <c r="O231" s="1" t="inlineStr"/>
-      <c r="P231" s="1" t="inlineStr"/>
-      <c r="Q231" s="1" t="inlineStr"/>
-      <c r="R231" s="1" t="inlineStr"/>
-      <c r="S231" s="1" t="inlineStr"/>
-      <c r="T231" s="1" t="inlineStr"/>
-      <c r="U231" s="1" t="inlineStr"/>
-      <c r="V231" s="1" t="inlineStr"/>
-      <c r="W231" s="1" t="inlineStr"/>
-      <c r="X231" s="1" t="inlineStr"/>
-      <c r="Y231" s="1" t="inlineStr"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="1" t="inlineStr"/>
-      <c r="B232" s="1" t="inlineStr"/>
-      <c r="C232" s="1" t="inlineStr"/>
-      <c r="D232" s="1" t="inlineStr"/>
-      <c r="E232" s="1" t="inlineStr"/>
-      <c r="F232" s="1" t="inlineStr"/>
-      <c r="G232" s="1" t="inlineStr"/>
-      <c r="H232" s="1" t="inlineStr"/>
-      <c r="I232" s="1" t="inlineStr"/>
-      <c r="J232" s="1" t="inlineStr"/>
-      <c r="K232" s="1" t="inlineStr">
-        <is>
-          <t>L688: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: prendre ses classes aprÃ¨s un repos de six</t>
-        </is>
-      </c>
-      <c r="L232" s="1" t="inlineStr"/>
-      <c r="M232" s="1" t="inlineStr"/>
-      <c r="N232" s="1" t="inlineStr"/>
-      <c r="O232" s="1" t="inlineStr"/>
-      <c r="P232" s="1" t="inlineStr"/>
-      <c r="Q232" s="1" t="inlineStr"/>
-      <c r="R232" s="1" t="inlineStr"/>
-      <c r="S232" s="1" t="inlineStr"/>
-      <c r="T232" s="1" t="inlineStr"/>
-      <c r="U232" s="1" t="inlineStr"/>
-      <c r="V232" s="1" t="inlineStr"/>
-      <c r="W232" s="1" t="inlineStr"/>
-      <c r="X232" s="1" t="inlineStr"/>
-      <c r="Y232" s="1" t="inlineStr"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="1" t="inlineStr"/>
-      <c r="B233" s="1" t="inlineStr"/>
-      <c r="C233" s="1" t="inlineStr"/>
-      <c r="D233" s="1" t="inlineStr"/>
-      <c r="E233" s="1" t="inlineStr"/>
-      <c r="F233" s="1" t="inlineStr"/>
-      <c r="G233" s="1" t="inlineStr"/>
-      <c r="H233" s="1" t="inlineStr"/>
-      <c r="I233" s="1" t="inlineStr"/>
-      <c r="J233" s="1" t="inlineStr"/>
-      <c r="K233" s="1" t="inlineStr">
-        <is>
-          <t>L689: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: - semaines Ã la plage et chez les parentÃ©s</t>
-        </is>
-      </c>
-      <c r="L233" s="1" t="inlineStr"/>
-      <c r="M233" s="1" t="inlineStr"/>
-      <c r="N233" s="1" t="inlineStr"/>
-      <c r="O233" s="1" t="inlineStr"/>
-      <c r="P233" s="1" t="inlineStr"/>
-      <c r="Q233" s="1" t="inlineStr"/>
-      <c r="R233" s="1" t="inlineStr"/>
-      <c r="S233" s="1" t="inlineStr"/>
-      <c r="T233" s="1" t="inlineStr"/>
-      <c r="U233" s="1" t="inlineStr"/>
-      <c r="V233" s="1" t="inlineStr"/>
-      <c r="W233" s="1" t="inlineStr"/>
-      <c r="X233" s="1" t="inlineStr"/>
-      <c r="Y233" s="1" t="inlineStr"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="1" t="inlineStr"/>
-      <c r="B234" s="1" t="inlineStr"/>
-      <c r="C234" s="1" t="inlineStr"/>
-      <c r="D234" s="1" t="inlineStr"/>
-      <c r="E234" s="1" t="inlineStr"/>
-      <c r="F234" s="1" t="inlineStr"/>
-      <c r="G234" s="1" t="inlineStr"/>
-      <c r="H234" s="1" t="inlineStr"/>
-      <c r="I234" s="1" t="inlineStr"/>
-      <c r="J234" s="1" t="inlineStr"/>
-      <c r="K234" s="1" t="inlineStr">
-        <is>
-          <t>L694: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: hild, est en dÃ©cision d'acheter un hÃ´tel</t>
-        </is>
-      </c>
-      <c r="L234" s="1" t="inlineStr"/>
-      <c r="M234" s="1" t="inlineStr"/>
-      <c r="N234" s="1" t="inlineStr"/>
-      <c r="O234" s="1" t="inlineStr"/>
-      <c r="P234" s="1" t="inlineStr"/>
-      <c r="Q234" s="1" t="inlineStr"/>
-      <c r="R234" s="1" t="inlineStr"/>
-      <c r="S234" s="1" t="inlineStr"/>
-      <c r="T234" s="1" t="inlineStr"/>
-      <c r="U234" s="1" t="inlineStr"/>
-      <c r="V234" s="1" t="inlineStr"/>
-      <c r="W234" s="1" t="inlineStr"/>
-      <c r="X234" s="1" t="inlineStr"/>
-      <c r="Y234" s="1" t="inlineStr"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="1" t="inlineStr"/>
-      <c r="B235" s="1" t="inlineStr"/>
-      <c r="C235" s="1" t="inlineStr"/>
-      <c r="D235" s="1" t="inlineStr"/>
-      <c r="E235" s="1" t="inlineStr"/>
-      <c r="F235" s="1" t="inlineStr"/>
-      <c r="G235" s="1" t="inlineStr"/>
-      <c r="H235" s="1" t="inlineStr"/>
-      <c r="I235" s="1" t="inlineStr"/>
-      <c r="J235" s="1" t="inlineStr"/>
-      <c r="K235" s="1" t="inlineStr">
-        <is>
-          <t>L698: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: belles-soeurs, Mmes Dakin et PagÃ©,</t>
-        </is>
-      </c>
-      <c r="L235" s="1" t="inlineStr"/>
-      <c r="M235" s="1" t="inlineStr"/>
-      <c r="N235" s="1" t="inlineStr"/>
-      <c r="O235" s="1" t="inlineStr"/>
-      <c r="P235" s="1" t="inlineStr"/>
-      <c r="Q235" s="1" t="inlineStr"/>
-      <c r="R235" s="1" t="inlineStr"/>
-      <c r="S235" s="1" t="inlineStr"/>
-      <c r="T235" s="1" t="inlineStr"/>
-      <c r="U235" s="1" t="inlineStr"/>
-      <c r="V235" s="1" t="inlineStr"/>
-      <c r="W235" s="1" t="inlineStr"/>
-      <c r="X235" s="1" t="inlineStr"/>
-      <c r="Y235" s="1" t="inlineStr"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="1" t="inlineStr"/>
-      <c r="B236" s="1" t="inlineStr"/>
-      <c r="C236" s="1" t="inlineStr"/>
-      <c r="D236" s="1" t="inlineStr"/>
-      <c r="E236" s="1" t="inlineStr"/>
-      <c r="F236" s="1" t="inlineStr"/>
-      <c r="G236" s="1" t="inlineStr"/>
-      <c r="H236" s="1" t="inlineStr"/>
-      <c r="I236" s="1" t="inlineStr"/>
-      <c r="J236" s="1" t="inlineStr"/>
-      <c r="K236" s="1" t="inlineStr">
-        <is>
-          <t>L699: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©taient de passage au Lac-la-Biche la</t>
-        </is>
-      </c>
-      <c r="L236" s="1" t="inlineStr"/>
-      <c r="M236" s="1" t="inlineStr"/>
-      <c r="N236" s="1" t="inlineStr"/>
-      <c r="O236" s="1" t="inlineStr"/>
-      <c r="P236" s="1" t="inlineStr"/>
-      <c r="Q236" s="1" t="inlineStr"/>
-      <c r="R236" s="1" t="inlineStr"/>
-      <c r="S236" s="1" t="inlineStr"/>
-      <c r="T236" s="1" t="inlineStr"/>
-      <c r="U236" s="1" t="inlineStr"/>
-      <c r="V236" s="1" t="inlineStr"/>
-      <c r="W236" s="1" t="inlineStr"/>
-      <c r="X236" s="1" t="inlineStr"/>
-      <c r="Y236" s="1" t="inlineStr"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="1" t="inlineStr"/>
-      <c r="B237" s="1" t="inlineStr"/>
-      <c r="C237" s="1" t="inlineStr"/>
-      <c r="D237" s="1" t="inlineStr"/>
-      <c r="E237" s="1" t="inlineStr"/>
-      <c r="F237" s="1" t="inlineStr"/>
-      <c r="G237" s="1" t="inlineStr"/>
-      <c r="H237" s="1" t="inlineStr"/>
-      <c r="I237" s="1" t="inlineStr"/>
-      <c r="J237" s="1" t="inlineStr"/>
-      <c r="K237" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: semaine derniÃ¨re.</t>
-        </is>
-      </c>
-      <c r="L237" s="1" t="inlineStr"/>
-      <c r="M237" s="1" t="inlineStr"/>
-      <c r="N237" s="1" t="inlineStr"/>
-      <c r="O237" s="1" t="inlineStr"/>
-      <c r="P237" s="1" t="inlineStr"/>
-      <c r="Q237" s="1" t="inlineStr"/>
-      <c r="R237" s="1" t="inlineStr"/>
-      <c r="S237" s="1" t="inlineStr"/>
-      <c r="T237" s="1" t="inlineStr"/>
-      <c r="U237" s="1" t="inlineStr"/>
-      <c r="V237" s="1" t="inlineStr"/>
-      <c r="W237" s="1" t="inlineStr"/>
-      <c r="X237" s="1" t="inlineStr"/>
-      <c r="Y237" s="1" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="1" t="inlineStr"/>
-      <c r="B238" s="1" t="inlineStr"/>
-      <c r="C238" s="1" t="inlineStr"/>
-      <c r="D238" s="1" t="inlineStr"/>
-      <c r="E238" s="1" t="inlineStr"/>
-      <c r="F238" s="1" t="inlineStr"/>
-      <c r="G238" s="1" t="inlineStr"/>
-      <c r="H238" s="1" t="inlineStr"/>
-      <c r="I238" s="1" t="inlineStr"/>
-      <c r="J238" s="1" t="inlineStr"/>
-      <c r="K238" s="1" t="inlineStr">
-        <is>
-          <t>L711: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Place du MarchÃ©,</t>
-        </is>
-      </c>
-      <c r="L238" s="1" t="inlineStr"/>
-      <c r="M238" s="1" t="inlineStr"/>
-      <c r="N238" s="1" t="inlineStr"/>
-      <c r="O238" s="1" t="inlineStr"/>
-      <c r="P238" s="1" t="inlineStr"/>
-      <c r="Q238" s="1" t="inlineStr"/>
-      <c r="R238" s="1" t="inlineStr"/>
-      <c r="S238" s="1" t="inlineStr"/>
-      <c r="T238" s="1" t="inlineStr"/>
-      <c r="U238" s="1" t="inlineStr"/>
-      <c r="V238" s="1" t="inlineStr"/>
-      <c r="W238" s="1" t="inlineStr"/>
-      <c r="X238" s="1" t="inlineStr"/>
-      <c r="Y238" s="1" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="1" t="inlineStr"/>
-      <c r="B239" s="1" t="inlineStr"/>
-      <c r="C239" s="1" t="inlineStr"/>
-      <c r="D239" s="1" t="inlineStr"/>
-      <c r="E239" s="1" t="inlineStr"/>
-      <c r="F239" s="1" t="inlineStr"/>
-      <c r="G239" s="1" t="inlineStr"/>
-      <c r="H239" s="1" t="inlineStr"/>
-      <c r="I239" s="1" t="inlineStr"/>
-      <c r="J239" s="1" t="inlineStr"/>
-      <c r="K239" s="1" t="inlineStr">
-        <is>
-          <t>L715: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Fabricants d'Ã©tampes en caoutchouc</t>
-        </is>
-      </c>
-      <c r="L239" s="1" t="inlineStr"/>
-      <c r="M239" s="1" t="inlineStr"/>
-      <c r="N239" s="1" t="inlineStr"/>
-      <c r="O239" s="1" t="inlineStr"/>
-      <c r="P239" s="1" t="inlineStr"/>
-      <c r="Q239" s="1" t="inlineStr"/>
-      <c r="R239" s="1" t="inlineStr"/>
-      <c r="S239" s="1" t="inlineStr"/>
-      <c r="T239" s="1" t="inlineStr"/>
-      <c r="U239" s="1" t="inlineStr"/>
-      <c r="V239" s="1" t="inlineStr"/>
-      <c r="W239" s="1" t="inlineStr"/>
-      <c r="X239" s="1" t="inlineStr"/>
-      <c r="Y239" s="1" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="1" t="inlineStr"/>
-      <c r="B240" s="1" t="inlineStr"/>
-      <c r="C240" s="1" t="inlineStr"/>
-      <c r="D240" s="1" t="inlineStr"/>
-      <c r="E240" s="1" t="inlineStr"/>
-      <c r="F240" s="1" t="inlineStr"/>
-      <c r="G240" s="1" t="inlineStr"/>
-      <c r="H240" s="1" t="inlineStr"/>
-      <c r="I240" s="1" t="inlineStr"/>
-      <c r="J240" s="1" t="inlineStr"/>
-      <c r="K240" s="1" t="inlineStr">
-        <is>
-          <t>L718: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©lÃ©phone 26927</t>
-        </is>
-      </c>
-      <c r="L240" s="1" t="inlineStr"/>
-      <c r="M240" s="1" t="inlineStr"/>
-      <c r="N240" s="1" t="inlineStr"/>
-      <c r="O240" s="1" t="inlineStr"/>
-      <c r="P240" s="1" t="inlineStr"/>
-      <c r="Q240" s="1" t="inlineStr"/>
-      <c r="R240" s="1" t="inlineStr"/>
-      <c r="S240" s="1" t="inlineStr"/>
-      <c r="T240" s="1" t="inlineStr"/>
-      <c r="U240" s="1" t="inlineStr"/>
-      <c r="V240" s="1" t="inlineStr"/>
-      <c r="W240" s="1" t="inlineStr"/>
-      <c r="X240" s="1" t="inlineStr"/>
-      <c r="Y240" s="1" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="1" t="inlineStr"/>
-      <c r="B241" s="1" t="inlineStr"/>
-      <c r="C241" s="1" t="inlineStr"/>
-      <c r="D241" s="1" t="inlineStr"/>
-      <c r="E241" s="1" t="inlineStr"/>
-      <c r="F241" s="1" t="inlineStr"/>
-      <c r="G241" s="1" t="inlineStr"/>
-      <c r="H241" s="1" t="inlineStr"/>
-      <c r="I241" s="1" t="inlineStr"/>
-      <c r="J241" s="1" t="inlineStr"/>
-      <c r="K241" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 102e (letter/digit mix), 2e (letter/digit mix) :: 10127-102e rue (2e Ã©tage) Edmonton</t>
-        </is>
-      </c>
-      <c r="L241" s="1" t="inlineStr"/>
-      <c r="M241" s="1" t="inlineStr"/>
-      <c r="N241" s="1" t="inlineStr"/>
-      <c r="O241" s="1" t="inlineStr"/>
-      <c r="P241" s="1" t="inlineStr"/>
-      <c r="Q241" s="1" t="inlineStr"/>
-      <c r="R241" s="1" t="inlineStr"/>
-      <c r="S241" s="1" t="inlineStr"/>
-      <c r="T241" s="1" t="inlineStr"/>
-      <c r="U241" s="1" t="inlineStr"/>
-      <c r="V241" s="1" t="inlineStr"/>
-      <c r="W241" s="1" t="inlineStr"/>
-      <c r="X241" s="1" t="inlineStr"/>
-      <c r="Y241" s="1" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="1" t="inlineStr"/>
-      <c r="B242" s="1" t="inlineStr"/>
-      <c r="C242" s="1" t="inlineStr"/>
-      <c r="D242" s="1" t="inlineStr"/>
-      <c r="E242" s="1" t="inlineStr"/>
-      <c r="F242" s="1" t="inlineStr"/>
-      <c r="G242" s="1" t="inlineStr"/>
-      <c r="H242" s="1" t="inlineStr"/>
-      <c r="I242" s="1" t="inlineStr"/>
-      <c r="J242" s="1" t="inlineStr"/>
-      <c r="K242" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Rome. â€” Plus de 350 scouts italiens,</t>
-        </is>
-      </c>
-      <c r="L242" s="1" t="inlineStr"/>
-      <c r="M242" s="1" t="inlineStr"/>
-      <c r="N242" s="1" t="inlineStr"/>
-      <c r="O242" s="1" t="inlineStr"/>
-      <c r="P242" s="1" t="inlineStr"/>
-      <c r="Q242" s="1" t="inlineStr"/>
-      <c r="R242" s="1" t="inlineStr"/>
-      <c r="S242" s="1" t="inlineStr"/>
-      <c r="T242" s="1" t="inlineStr"/>
-      <c r="U242" s="1" t="inlineStr"/>
-      <c r="V242" s="1" t="inlineStr"/>
-      <c r="W242" s="1" t="inlineStr"/>
-      <c r="X242" s="1" t="inlineStr"/>
-      <c r="Y242" s="1" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="1" t="inlineStr"/>
-      <c r="B243" s="1" t="inlineStr"/>
-      <c r="C243" s="1" t="inlineStr"/>
-      <c r="D243" s="1" t="inlineStr"/>
-      <c r="E243" s="1" t="inlineStr"/>
-      <c r="F243" s="1" t="inlineStr"/>
-      <c r="G243" s="1" t="inlineStr"/>
-      <c r="H243" s="1" t="inlineStr"/>
-      <c r="I243" s="1" t="inlineStr"/>
-      <c r="J243" s="1" t="inlineStr"/>
-      <c r="K243" s="1" t="inlineStr">
-        <is>
-          <t>L724: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Scouts catholiques), ont assistÃ© au Jam-</t>
-        </is>
-      </c>
-      <c r="L243" s="1" t="inlineStr"/>
-      <c r="M243" s="1" t="inlineStr"/>
-      <c r="N243" s="1" t="inlineStr"/>
-      <c r="O243" s="1" t="inlineStr"/>
-      <c r="P243" s="1" t="inlineStr"/>
-      <c r="Q243" s="1" t="inlineStr"/>
-      <c r="R243" s="1" t="inlineStr"/>
-      <c r="S243" s="1" t="inlineStr"/>
-      <c r="T243" s="1" t="inlineStr"/>
-      <c r="U243" s="1" t="inlineStr"/>
-      <c r="V243" s="1" t="inlineStr"/>
-      <c r="W243" s="1" t="inlineStr"/>
-      <c r="X243" s="1" t="inlineStr"/>
-      <c r="Y243" s="1" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="1" t="inlineStr"/>
-      <c r="B244" s="1" t="inlineStr"/>
-      <c r="C244" s="1" t="inlineStr"/>
-      <c r="D244" s="1" t="inlineStr"/>
-      <c r="E244" s="1" t="inlineStr"/>
-      <c r="F244" s="1" t="inlineStr"/>
-      <c r="G244" s="1" t="inlineStr"/>
-      <c r="H244" s="1" t="inlineStr"/>
-      <c r="I244" s="1" t="inlineStr"/>
-      <c r="J244" s="1" t="inlineStr"/>
-      <c r="K244" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | suspicious token(s): ont1 (letter/digit mix) :: prÃ¨s de Paris. Ces scouts italiens ont1</t>
-        </is>
-      </c>
-      <c r="L244" s="1" t="inlineStr"/>
-      <c r="M244" s="1" t="inlineStr"/>
-      <c r="N244" s="1" t="inlineStr"/>
-      <c r="O244" s="1" t="inlineStr"/>
-      <c r="P244" s="1" t="inlineStr"/>
-      <c r="Q244" s="1" t="inlineStr"/>
-      <c r="R244" s="1" t="inlineStr"/>
-      <c r="S244" s="1" t="inlineStr"/>
-      <c r="T244" s="1" t="inlineStr"/>
-      <c r="U244" s="1" t="inlineStr"/>
-      <c r="V244" s="1" t="inlineStr"/>
-      <c r="W244" s="1" t="inlineStr"/>
-      <c r="X244" s="1" t="inlineStr"/>
-      <c r="Y244" s="1" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="1" t="inlineStr"/>
-      <c r="B245" s="1" t="inlineStr"/>
-      <c r="C245" s="1" t="inlineStr"/>
-      <c r="D245" s="1" t="inlineStr"/>
-      <c r="E245" s="1" t="inlineStr"/>
-      <c r="F245" s="1" t="inlineStr"/>
-      <c r="G245" s="1" t="inlineStr"/>
-      <c r="H245" s="1" t="inlineStr"/>
-      <c r="I245" s="1" t="inlineStr"/>
-      <c r="J245" s="1" t="inlineStr"/>
-      <c r="K245" s="1" t="inlineStr">
-        <is>
-          <t>L727: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: apportÃ© avec eux des rÃ©pliques dâ€™une</t>
-        </is>
-      </c>
-      <c r="L245" s="1" t="inlineStr"/>
-      <c r="M245" s="1" t="inlineStr"/>
-      <c r="N245" s="1" t="inlineStr"/>
-      <c r="O245" s="1" t="inlineStr"/>
-      <c r="P245" s="1" t="inlineStr"/>
-      <c r="Q245" s="1" t="inlineStr"/>
-      <c r="R245" s="1" t="inlineStr"/>
-      <c r="S245" s="1" t="inlineStr"/>
-      <c r="T245" s="1" t="inlineStr"/>
-      <c r="U245" s="1" t="inlineStr"/>
-      <c r="V245" s="1" t="inlineStr"/>
-      <c r="W245" s="1" t="inlineStr"/>
-      <c r="X245" s="1" t="inlineStr"/>
-      <c r="Y245" s="1" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="1" t="inlineStr"/>
-      <c r="B246" s="1" t="inlineStr"/>
-      <c r="C246" s="1" t="inlineStr"/>
-      <c r="D246" s="1" t="inlineStr"/>
-      <c r="E246" s="1" t="inlineStr"/>
-      <c r="F246" s="1" t="inlineStr"/>
-      <c r="G246" s="1" t="inlineStr"/>
-      <c r="H246" s="1" t="inlineStr"/>
-      <c r="I246" s="1" t="inlineStr"/>
-      <c r="J246" s="1" t="inlineStr"/>
-      <c r="K246" s="1" t="inlineStr">
-        <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: petite statue de la TrÃ¨s Sainte Vierge :</t>
-        </is>
-      </c>
-      <c r="L246" s="1" t="inlineStr"/>
-      <c r="M246" s="1" t="inlineStr"/>
-      <c r="N246" s="1" t="inlineStr"/>
-      <c r="O246" s="1" t="inlineStr"/>
-      <c r="P246" s="1" t="inlineStr"/>
-      <c r="Q246" s="1" t="inlineStr"/>
-      <c r="R246" s="1" t="inlineStr"/>
-      <c r="S246" s="1" t="inlineStr"/>
-      <c r="T246" s="1" t="inlineStr"/>
-      <c r="U246" s="1" t="inlineStr"/>
-      <c r="V246" s="1" t="inlineStr"/>
-      <c r="W246" s="1" t="inlineStr"/>
-      <c r="X246" s="1" t="inlineStr"/>
-      <c r="Y246" s="1" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="1" t="inlineStr"/>
-      <c r="B247" s="1" t="inlineStr"/>
-      <c r="C247" s="1" t="inlineStr"/>
-      <c r="D247" s="1" t="inlineStr"/>
-      <c r="E247" s="1" t="inlineStr"/>
-      <c r="F247" s="1" t="inlineStr"/>
-      <c r="G247" s="1" t="inlineStr"/>
-      <c r="H247" s="1" t="inlineStr"/>
-      <c r="I247" s="1" t="inlineStr"/>
-      <c r="J247" s="1" t="inlineStr"/>
-      <c r="K247" s="1" t="inlineStr">
-        <is>
-          <t>L730: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Scouts". La statue originale a Ã©tÃ© bÃ©nie 1</t>
-        </is>
-      </c>
-      <c r="L247" s="1" t="inlineStr"/>
-      <c r="M247" s="1" t="inlineStr"/>
-      <c r="N247" s="1" t="inlineStr"/>
-      <c r="O247" s="1" t="inlineStr"/>
-      <c r="P247" s="1" t="inlineStr"/>
-      <c r="Q247" s="1" t="inlineStr"/>
-      <c r="R247" s="1" t="inlineStr"/>
-      <c r="S247" s="1" t="inlineStr"/>
-      <c r="T247" s="1" t="inlineStr"/>
-      <c r="U247" s="1" t="inlineStr"/>
-      <c r="V247" s="1" t="inlineStr"/>
-      <c r="W247" s="1" t="inlineStr"/>
-      <c r="X247" s="1" t="inlineStr"/>
-      <c r="Y247" s="1" t="inlineStr"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="1" t="inlineStr"/>
-      <c r="B248" s="1" t="inlineStr"/>
-      <c r="C248" s="1" t="inlineStr"/>
-      <c r="D248" s="1" t="inlineStr"/>
-      <c r="E248" s="1" t="inlineStr"/>
-      <c r="F248" s="1" t="inlineStr"/>
-      <c r="G248" s="1" t="inlineStr"/>
-      <c r="H248" s="1" t="inlineStr"/>
-      <c r="I248" s="1" t="inlineStr"/>
-      <c r="J248" s="1" t="inlineStr"/>
-      <c r="K248" s="1" t="inlineStr">
-        <is>
-          <t>L731: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: derniÃ¨rement par Sa SaintetÃ© le pape</t>
-        </is>
-      </c>
-      <c r="L248" s="1" t="inlineStr"/>
-      <c r="M248" s="1" t="inlineStr"/>
-      <c r="N248" s="1" t="inlineStr"/>
-      <c r="O248" s="1" t="inlineStr"/>
-      <c r="P248" s="1" t="inlineStr"/>
-      <c r="Q248" s="1" t="inlineStr"/>
-      <c r="R248" s="1" t="inlineStr"/>
-      <c r="S248" s="1" t="inlineStr"/>
-      <c r="T248" s="1" t="inlineStr"/>
-      <c r="U248" s="1" t="inlineStr"/>
-      <c r="V248" s="1" t="inlineStr"/>
-      <c r="W248" s="1" t="inlineStr"/>
-      <c r="X248" s="1" t="inlineStr"/>
-      <c r="Y248" s="1" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="1" t="inlineStr"/>
-      <c r="B249" s="1" t="inlineStr"/>
-      <c r="C249" s="1" t="inlineStr"/>
-      <c r="D249" s="1" t="inlineStr"/>
-      <c r="E249" s="1" t="inlineStr"/>
-      <c r="F249" s="1" t="inlineStr"/>
-      <c r="G249" s="1" t="inlineStr"/>
-      <c r="H249" s="1" t="inlineStr"/>
-      <c r="I249" s="1" t="inlineStr"/>
-      <c r="J249" s="1" t="inlineStr"/>
-      <c r="K249" s="1" t="inlineStr">
-        <is>
-          <t>L733: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00B4 ACUTE ACCENT :: prÃ©sident et l'aumÃ´nier de l'Association.</t>
-        </is>
-      </c>
-      <c r="L249" s="1" t="inlineStr"/>
-      <c r="M249" s="1" t="inlineStr"/>
-      <c r="N249" s="1" t="inlineStr"/>
-      <c r="O249" s="1" t="inlineStr"/>
-      <c r="P249" s="1" t="inlineStr"/>
-      <c r="Q249" s="1" t="inlineStr"/>
-      <c r="R249" s="1" t="inlineStr"/>
-      <c r="S249" s="1" t="inlineStr"/>
-      <c r="T249" s="1" t="inlineStr"/>
-      <c r="U249" s="1" t="inlineStr"/>
-      <c r="V249" s="1" t="inlineStr"/>
-      <c r="W249" s="1" t="inlineStr"/>
-      <c r="X249" s="1" t="inlineStr"/>
-      <c r="Y249" s="1" t="inlineStr"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="1" t="inlineStr"/>
-      <c r="B250" s="1" t="inlineStr"/>
-      <c r="C250" s="1" t="inlineStr"/>
-      <c r="D250" s="1" t="inlineStr"/>
-      <c r="E250" s="1" t="inlineStr"/>
-      <c r="F250" s="1" t="inlineStr"/>
-      <c r="G250" s="1" t="inlineStr"/>
-      <c r="H250" s="1" t="inlineStr"/>
-      <c r="I250" s="1" t="inlineStr"/>
-      <c r="J250" s="1" t="inlineStr"/>
-      <c r="K250" s="1" t="inlineStr">
-        <is>
-          <t>L754: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: SituÃ© dans le centre des affaires</t>
-        </is>
-      </c>
-      <c r="L250" s="1" t="inlineStr"/>
-      <c r="M250" s="1" t="inlineStr"/>
-      <c r="N250" s="1" t="inlineStr"/>
-      <c r="O250" s="1" t="inlineStr"/>
-      <c r="P250" s="1" t="inlineStr"/>
-      <c r="Q250" s="1" t="inlineStr"/>
-      <c r="R250" s="1" t="inlineStr"/>
-      <c r="S250" s="1" t="inlineStr"/>
-      <c r="T250" s="1" t="inlineStr"/>
-      <c r="U250" s="1" t="inlineStr"/>
-      <c r="V250" s="1" t="inlineStr"/>
-      <c r="W250" s="1" t="inlineStr"/>
-      <c r="X250" s="1" t="inlineStr"/>
-      <c r="Y250" s="1" t="inlineStr"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="1" t="inlineStr"/>
-      <c r="B251" s="1" t="inlineStr"/>
-      <c r="C251" s="1" t="inlineStr"/>
-      <c r="D251" s="1" t="inlineStr"/>
-      <c r="E251" s="1" t="inlineStr"/>
-      <c r="F251" s="1" t="inlineStr"/>
-      <c r="G251" s="1" t="inlineStr"/>
-      <c r="H251" s="1" t="inlineStr"/>
-      <c r="I251" s="1" t="inlineStr"/>
-      <c r="J251" s="1" t="inlineStr"/>
-      <c r="K251" s="1" t="inlineStr">
-        <is>
-          <t>L755: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+00A2 CENT SIGN :: et des thÃ©Ã¢tres</t>
-        </is>
-      </c>
-      <c r="L251" s="1" t="inlineStr"/>
-      <c r="M251" s="1" t="inlineStr"/>
-      <c r="N251" s="1" t="inlineStr"/>
-      <c r="O251" s="1" t="inlineStr"/>
-      <c r="P251" s="1" t="inlineStr"/>
-      <c r="Q251" s="1" t="inlineStr"/>
-      <c r="R251" s="1" t="inlineStr"/>
-      <c r="S251" s="1" t="inlineStr"/>
-      <c r="T251" s="1" t="inlineStr"/>
-      <c r="U251" s="1" t="inlineStr"/>
-      <c r="V251" s="1" t="inlineStr"/>
-      <c r="W251" s="1" t="inlineStr"/>
-      <c r="X251" s="1" t="inlineStr"/>
-      <c r="Y251" s="1" t="inlineStr"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="1" t="inlineStr"/>
-      <c r="B252" s="1" t="inlineStr"/>
-      <c r="C252" s="1" t="inlineStr"/>
-      <c r="D252" s="1" t="inlineStr"/>
-      <c r="E252" s="1" t="inlineStr"/>
-      <c r="F252" s="1" t="inlineStr"/>
-      <c r="G252" s="1" t="inlineStr"/>
-      <c r="H252" s="1" t="inlineStr"/>
-      <c r="I252" s="1" t="inlineStr"/>
-      <c r="J252" s="1" t="inlineStr"/>
-      <c r="K252" s="1" t="inlineStr">
-        <is>
-          <t>L762: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Camions spÃ©ciaux pour meubles</t>
-        </is>
-      </c>
-      <c r="L252" s="1" t="inlineStr"/>
-      <c r="M252" s="1" t="inlineStr"/>
-      <c r="N252" s="1" t="inlineStr"/>
-      <c r="O252" s="1" t="inlineStr"/>
-      <c r="P252" s="1" t="inlineStr"/>
-      <c r="Q252" s="1" t="inlineStr"/>
-      <c r="R252" s="1" t="inlineStr"/>
-      <c r="S252" s="1" t="inlineStr"/>
-      <c r="T252" s="1" t="inlineStr"/>
-      <c r="U252" s="1" t="inlineStr"/>
-      <c r="V252" s="1" t="inlineStr"/>
-      <c r="W252" s="1" t="inlineStr"/>
-      <c r="X252" s="1" t="inlineStr"/>
-      <c r="Y252" s="1" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="inlineStr"/>
-      <c r="B253" s="1" t="inlineStr"/>
-      <c r="C253" s="1" t="inlineStr"/>
-      <c r="D253" s="1" t="inlineStr"/>
-      <c r="E253" s="1" t="inlineStr"/>
-      <c r="F253" s="1" t="inlineStr"/>
-      <c r="G253" s="1" t="inlineStr"/>
-      <c r="H253" s="1" t="inlineStr"/>
-      <c r="I253" s="1" t="inlineStr"/>
-      <c r="J253" s="1" t="inlineStr"/>
-      <c r="K253" s="1" t="inlineStr">
-        <is>
-          <t>L764: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l.: 26175</t>
-        </is>
-      </c>
-      <c r="L253" s="1" t="inlineStr"/>
-      <c r="M253" s="1" t="inlineStr"/>
-      <c r="N253" s="1" t="inlineStr"/>
-      <c r="O253" s="1" t="inlineStr"/>
-      <c r="P253" s="1" t="inlineStr"/>
-      <c r="Q253" s="1" t="inlineStr"/>
-      <c r="R253" s="1" t="inlineStr"/>
-      <c r="S253" s="1" t="inlineStr"/>
-      <c r="T253" s="1" t="inlineStr"/>
-      <c r="U253" s="1" t="inlineStr"/>
-      <c r="V253" s="1" t="inlineStr"/>
-      <c r="W253" s="1" t="inlineStr"/>
-      <c r="X253" s="1" t="inlineStr"/>
-      <c r="Y253" s="1" t="inlineStr"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="1" t="inlineStr"/>
-      <c r="B254" s="1" t="inlineStr"/>
-      <c r="C254" s="1" t="inlineStr"/>
-      <c r="D254" s="1" t="inlineStr"/>
-      <c r="E254" s="1" t="inlineStr"/>
-      <c r="F254" s="1" t="inlineStr"/>
-      <c r="G254" s="1" t="inlineStr"/>
-      <c r="H254" s="1" t="inlineStr"/>
-      <c r="I254" s="1" t="inlineStr"/>
-      <c r="J254" s="1" t="inlineStr"/>
-      <c r="K254" s="1" t="inlineStr">
-        <is>
-          <t>L775: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Toronto, sont recommencÃ©s selon de</t>
-        </is>
-      </c>
-      <c r="L254" s="1" t="inlineStr"/>
-      <c r="M254" s="1" t="inlineStr"/>
-      <c r="N254" s="1" t="inlineStr"/>
-      <c r="O254" s="1" t="inlineStr"/>
-      <c r="P254" s="1" t="inlineStr"/>
-      <c r="Q254" s="1" t="inlineStr"/>
-      <c r="R254" s="1" t="inlineStr"/>
-      <c r="S254" s="1" t="inlineStr"/>
-      <c r="T254" s="1" t="inlineStr"/>
-      <c r="U254" s="1" t="inlineStr"/>
-      <c r="V254" s="1" t="inlineStr"/>
-      <c r="W254" s="1" t="inlineStr"/>
-      <c r="X254" s="1" t="inlineStr"/>
-      <c r="Y254" s="1" t="inlineStr"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="1" t="inlineStr"/>
-      <c r="B255" s="1" t="inlineStr"/>
-      <c r="C255" s="1" t="inlineStr"/>
-      <c r="D255" s="1" t="inlineStr"/>
-      <c r="E255" s="1" t="inlineStr"/>
-      <c r="F255" s="1" t="inlineStr"/>
-      <c r="G255" s="1" t="inlineStr"/>
-      <c r="H255" s="1" t="inlineStr"/>
-      <c r="I255" s="1" t="inlineStr"/>
-      <c r="J255" s="1" t="inlineStr"/>
-      <c r="K255" s="1" t="inlineStr">
-        <is>
-          <t>L776: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: nouveaux plans Ã cause de l'excÃ¨s dans</t>
-        </is>
-      </c>
-      <c r="L255" s="1" t="inlineStr"/>
-      <c r="M255" s="1" t="inlineStr"/>
-      <c r="N255" s="1" t="inlineStr"/>
-      <c r="O255" s="1" t="inlineStr"/>
-      <c r="P255" s="1" t="inlineStr"/>
-      <c r="Q255" s="1" t="inlineStr"/>
-      <c r="R255" s="1" t="inlineStr"/>
-      <c r="S255" s="1" t="inlineStr"/>
-      <c r="T255" s="1" t="inlineStr"/>
-      <c r="U255" s="1" t="inlineStr"/>
-      <c r="V255" s="1" t="inlineStr"/>
-      <c r="W255" s="1" t="inlineStr"/>
-      <c r="X255" s="1" t="inlineStr"/>
-      <c r="Y255" s="1" t="inlineStr"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="1" t="inlineStr"/>
-      <c r="B256" s="1" t="inlineStr"/>
-      <c r="C256" s="1" t="inlineStr"/>
-      <c r="D256" s="1" t="inlineStr"/>
-      <c r="E256" s="1" t="inlineStr"/>
-      <c r="F256" s="1" t="inlineStr"/>
-      <c r="G256" s="1" t="inlineStr"/>
-      <c r="H256" s="1" t="inlineStr"/>
-      <c r="I256" s="1" t="inlineStr"/>
-      <c r="J256" s="1" t="inlineStr"/>
-      <c r="K256" s="1" t="inlineStr">
-        <is>
-          <t>L782: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Les mariÃ©s, M. et Mme RenÃ© Lefebvre,</t>
-        </is>
-      </c>
-      <c r="L256" s="1" t="inlineStr"/>
-      <c r="M256" s="1" t="inlineStr"/>
-      <c r="N256" s="1" t="inlineStr"/>
-      <c r="O256" s="1" t="inlineStr"/>
-      <c r="P256" s="1" t="inlineStr"/>
-      <c r="Q256" s="1" t="inlineStr"/>
-      <c r="R256" s="1" t="inlineStr"/>
-      <c r="S256" s="1" t="inlineStr"/>
-      <c r="T256" s="1" t="inlineStr"/>
-      <c r="U256" s="1" t="inlineStr"/>
-      <c r="V256" s="1" t="inlineStr"/>
-      <c r="W256" s="1" t="inlineStr"/>
-      <c r="X256" s="1" t="inlineStr"/>
-      <c r="Y256" s="1" t="inlineStr"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="1" t="inlineStr"/>
-      <c r="B257" s="1" t="inlineStr"/>
-      <c r="C257" s="1" t="inlineStr"/>
-      <c r="D257" s="1" t="inlineStr"/>
-      <c r="E257" s="1" t="inlineStr"/>
-      <c r="F257" s="1" t="inlineStr"/>
-      <c r="G257" s="1" t="inlineStr"/>
-      <c r="H257" s="1" t="inlineStr"/>
-      <c r="I257" s="1" t="inlineStr"/>
-      <c r="J257" s="1" t="inlineStr"/>
-      <c r="K257" s="1" t="inlineStr">
-        <is>
-          <t>L798: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: et machines de Lionel Baril; une rÃ©si-</t>
-        </is>
-      </c>
-      <c r="L257" s="1" t="inlineStr"/>
-      <c r="M257" s="1" t="inlineStr"/>
-      <c r="N257" s="1" t="inlineStr"/>
-      <c r="O257" s="1" t="inlineStr"/>
-      <c r="P257" s="1" t="inlineStr"/>
-      <c r="Q257" s="1" t="inlineStr"/>
-      <c r="R257" s="1" t="inlineStr"/>
-      <c r="S257" s="1" t="inlineStr"/>
-      <c r="T257" s="1" t="inlineStr"/>
-      <c r="U257" s="1" t="inlineStr"/>
-      <c r="V257" s="1" t="inlineStr"/>
-      <c r="W257" s="1" t="inlineStr"/>
-      <c r="X257" s="1" t="inlineStr"/>
-      <c r="Y257" s="1" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="1" t="inlineStr"/>
-      <c r="B258" s="1" t="inlineStr"/>
-      <c r="C258" s="1" t="inlineStr"/>
-      <c r="D258" s="1" t="inlineStr"/>
-      <c r="E258" s="1" t="inlineStr"/>
-      <c r="F258" s="1" t="inlineStr"/>
-      <c r="G258" s="1" t="inlineStr"/>
-      <c r="H258" s="1" t="inlineStr"/>
-      <c r="I258" s="1" t="inlineStr"/>
-      <c r="J258" s="1" t="inlineStr"/>
-      <c r="K258" s="1" t="inlineStr">
-        <is>
-          <t>L799: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: dence de AimÃ© Drouin; et une nouvelle</t>
-        </is>
-      </c>
-      <c r="L258" s="1" t="inlineStr"/>
-      <c r="M258" s="1" t="inlineStr"/>
-      <c r="N258" s="1" t="inlineStr"/>
-      <c r="O258" s="1" t="inlineStr"/>
-      <c r="P258" s="1" t="inlineStr"/>
-      <c r="Q258" s="1" t="inlineStr"/>
-      <c r="R258" s="1" t="inlineStr"/>
-      <c r="S258" s="1" t="inlineStr"/>
-      <c r="T258" s="1" t="inlineStr"/>
-      <c r="U258" s="1" t="inlineStr"/>
-      <c r="V258" s="1" t="inlineStr"/>
-      <c r="W258" s="1" t="inlineStr"/>
-      <c r="X258" s="1" t="inlineStr"/>
-      <c r="Y258" s="1" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="1" t="inlineStr"/>
-      <c r="B259" s="1" t="inlineStr"/>
-      <c r="C259" s="1" t="inlineStr"/>
-      <c r="D259" s="1" t="inlineStr"/>
-      <c r="E259" s="1" t="inlineStr"/>
-      <c r="F259" s="1" t="inlineStr"/>
-      <c r="G259" s="1" t="inlineStr"/>
-      <c r="H259" s="1" t="inlineStr"/>
-      <c r="I259" s="1" t="inlineStr"/>
-      <c r="J259" s="1" t="inlineStr"/>
-      <c r="K259" s="1" t="inlineStr">
-        <is>
-          <t>L800: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: faÃ§ade au restaurant Strand CafÃ©.</t>
-        </is>
-      </c>
-      <c r="L259" s="1" t="inlineStr"/>
-      <c r="M259" s="1" t="inlineStr"/>
-      <c r="N259" s="1" t="inlineStr"/>
-      <c r="O259" s="1" t="inlineStr"/>
-      <c r="P259" s="1" t="inlineStr"/>
-      <c r="Q259" s="1" t="inlineStr"/>
-      <c r="R259" s="1" t="inlineStr"/>
-      <c r="S259" s="1" t="inlineStr"/>
-      <c r="T259" s="1" t="inlineStr"/>
-      <c r="U259" s="1" t="inlineStr"/>
-      <c r="V259" s="1" t="inlineStr"/>
-      <c r="W259" s="1" t="inlineStr"/>
-      <c r="X259" s="1" t="inlineStr"/>
-      <c r="Y259" s="1" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="1" t="inlineStr"/>
-      <c r="B260" s="1" t="inlineStr"/>
-      <c r="C260" s="1" t="inlineStr"/>
-      <c r="D260" s="1" t="inlineStr"/>
-      <c r="E260" s="1" t="inlineStr"/>
-      <c r="F260" s="1" t="inlineStr"/>
-      <c r="G260" s="1" t="inlineStr"/>
-      <c r="H260" s="1" t="inlineStr"/>
-      <c r="I260" s="1" t="inlineStr"/>
-      <c r="J260" s="1" t="inlineStr"/>
-      <c r="K260" s="1" t="inlineStr">
-        <is>
-          <t>L805: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: achetÃ© la maison de Sylva Ouellette, sur</t>
-        </is>
-      </c>
-      <c r="L260" s="1" t="inlineStr"/>
-      <c r="M260" s="1" t="inlineStr"/>
-      <c r="N260" s="1" t="inlineStr"/>
-      <c r="O260" s="1" t="inlineStr"/>
-      <c r="P260" s="1" t="inlineStr"/>
-      <c r="Q260" s="1" t="inlineStr"/>
-      <c r="R260" s="1" t="inlineStr"/>
-      <c r="S260" s="1" t="inlineStr"/>
-      <c r="T260" s="1" t="inlineStr"/>
-      <c r="U260" s="1" t="inlineStr"/>
-      <c r="V260" s="1" t="inlineStr"/>
-      <c r="W260" s="1" t="inlineStr"/>
-      <c r="X260" s="1" t="inlineStr"/>
-      <c r="Y260" s="1" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="1" t="inlineStr"/>
-      <c r="B261" s="1" t="inlineStr"/>
-      <c r="C261" s="1" t="inlineStr"/>
-      <c r="D261" s="1" t="inlineStr"/>
-      <c r="E261" s="1" t="inlineStr"/>
-      <c r="F261" s="1" t="inlineStr"/>
-      <c r="G261" s="1" t="inlineStr"/>
-      <c r="H261" s="1" t="inlineStr"/>
-      <c r="I261" s="1" t="inlineStr"/>
-      <c r="J261" s="1" t="inlineStr"/>
-      <c r="K261" s="1" t="inlineStr">
-        <is>
-          <t>L812: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: fils. Elle est accompagnÃ©e de sa fille</t>
-        </is>
-      </c>
-      <c r="L261" s="1" t="inlineStr"/>
-      <c r="M261" s="1" t="inlineStr"/>
-      <c r="N261" s="1" t="inlineStr"/>
-      <c r="O261" s="1" t="inlineStr"/>
-      <c r="P261" s="1" t="inlineStr"/>
-      <c r="Q261" s="1" t="inlineStr"/>
-      <c r="R261" s="1" t="inlineStr"/>
-      <c r="S261" s="1" t="inlineStr"/>
-      <c r="T261" s="1" t="inlineStr"/>
-      <c r="U261" s="1" t="inlineStr"/>
-      <c r="V261" s="1" t="inlineStr"/>
-      <c r="W261" s="1" t="inlineStr"/>
-      <c r="X261" s="1" t="inlineStr"/>
-      <c r="Y261" s="1" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="1" t="inlineStr"/>
-      <c r="B262" s="1" t="inlineStr"/>
-      <c r="C262" s="1" t="inlineStr"/>
-      <c r="D262" s="1" t="inlineStr"/>
-      <c r="E262" s="1" t="inlineStr"/>
-      <c r="F262" s="1" t="inlineStr"/>
-      <c r="G262" s="1" t="inlineStr"/>
-      <c r="H262" s="1" t="inlineStr"/>
-      <c r="I262" s="1" t="inlineStr"/>
-      <c r="J262" s="1" t="inlineStr"/>
-      <c r="K262" s="1" t="inlineStr">
-        <is>
-          <t>L814: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS :: ve, de Grand'mÃ¨re et de son jeune fils</t>
-        </is>
-      </c>
-      <c r="L262" s="1" t="inlineStr"/>
-      <c r="M262" s="1" t="inlineStr"/>
-      <c r="N262" s="1" t="inlineStr"/>
-      <c r="O262" s="1" t="inlineStr"/>
-      <c r="P262" s="1" t="inlineStr"/>
-      <c r="Q262" s="1" t="inlineStr"/>
-      <c r="R262" s="1" t="inlineStr"/>
-      <c r="S262" s="1" t="inlineStr"/>
-      <c r="T262" s="1" t="inlineStr"/>
-      <c r="U262" s="1" t="inlineStr"/>
-      <c r="V262" s="1" t="inlineStr"/>
-      <c r="W262" s="1" t="inlineStr"/>
-      <c r="X262" s="1" t="inlineStr"/>
-      <c r="Y262" s="1" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="1" t="inlineStr"/>
-      <c r="B263" s="1" t="inlineStr"/>
-      <c r="C263" s="1" t="inlineStr"/>
-      <c r="D263" s="1" t="inlineStr"/>
-      <c r="E263" s="1" t="inlineStr"/>
-      <c r="F263" s="1" t="inlineStr"/>
-      <c r="G263" s="1" t="inlineStr"/>
-      <c r="H263" s="1" t="inlineStr"/>
-      <c r="I263" s="1" t="inlineStr"/>
-      <c r="J263" s="1" t="inlineStr"/>
-      <c r="K263" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: La convalescence de notre curÃ© se pro-</t>
-        </is>
-      </c>
-      <c r="L263" s="1" t="inlineStr"/>
-      <c r="M263" s="1" t="inlineStr"/>
-      <c r="N263" s="1" t="inlineStr"/>
-      <c r="O263" s="1" t="inlineStr"/>
-      <c r="P263" s="1" t="inlineStr"/>
-      <c r="Q263" s="1" t="inlineStr"/>
-      <c r="R263" s="1" t="inlineStr"/>
-      <c r="S263" s="1" t="inlineStr"/>
-      <c r="T263" s="1" t="inlineStr"/>
-      <c r="U263" s="1" t="inlineStr"/>
-      <c r="V263" s="1" t="inlineStr"/>
-      <c r="W263" s="1" t="inlineStr"/>
-      <c r="X263" s="1" t="inlineStr"/>
-      <c r="Y263" s="1" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="1" t="inlineStr"/>
-      <c r="B264" s="1" t="inlineStr"/>
-      <c r="C264" s="1" t="inlineStr"/>
-      <c r="D264" s="1" t="inlineStr"/>
-      <c r="E264" s="1" t="inlineStr"/>
-      <c r="F264" s="1" t="inlineStr"/>
-      <c r="G264" s="1" t="inlineStr"/>
-      <c r="H264" s="1" t="inlineStr"/>
-      <c r="I264" s="1" t="inlineStr"/>
-      <c r="J264" s="1" t="inlineStr"/>
-      <c r="K264" s="1" t="inlineStr">
-        <is>
-          <t>L820: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT :: longe toujours; il est encore Ã l'hÃ´pital</t>
-        </is>
-      </c>
-      <c r="L264" s="1" t="inlineStr"/>
-      <c r="M264" s="1" t="inlineStr"/>
-      <c r="N264" s="1" t="inlineStr"/>
-      <c r="O264" s="1" t="inlineStr"/>
-      <c r="P264" s="1" t="inlineStr"/>
-      <c r="Q264" s="1" t="inlineStr"/>
-      <c r="R264" s="1" t="inlineStr"/>
-      <c r="S264" s="1" t="inlineStr"/>
-      <c r="T264" s="1" t="inlineStr"/>
-      <c r="U264" s="1" t="inlineStr"/>
-      <c r="V264" s="1" t="inlineStr"/>
-      <c r="W264" s="1" t="inlineStr"/>
-      <c r="X264" s="1" t="inlineStr"/>
-      <c r="Y264" s="1" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="1" t="inlineStr"/>
-      <c r="B265" s="1" t="inlineStr"/>
-      <c r="C265" s="1" t="inlineStr"/>
-      <c r="D265" s="1" t="inlineStr"/>
-      <c r="E265" s="1" t="inlineStr"/>
-      <c r="F265" s="1" t="inlineStr"/>
-      <c r="G265" s="1" t="inlineStr"/>
-      <c r="H265" s="1" t="inlineStr"/>
-      <c r="I265" s="1" t="inlineStr"/>
-      <c r="J265" s="1" t="inlineStr"/>
-      <c r="K265" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+00A9 COPYRIGHT SIGN :: frÃ¨re l'abbÃ© J.-A. Normandeau, Ã©taient</t>
-        </is>
-      </c>
-      <c r="L265" s="1" t="inlineStr"/>
-      <c r="M265" s="1" t="inlineStr"/>
-      <c r="N265" s="1" t="inlineStr"/>
-      <c r="O265" s="1" t="inlineStr"/>
-      <c r="P265" s="1" t="inlineStr"/>
-      <c r="Q265" s="1" t="inlineStr"/>
-      <c r="R265" s="1" t="inlineStr"/>
-      <c r="S265" s="1" t="inlineStr"/>
-      <c r="T265" s="1" t="inlineStr"/>
-      <c r="U265" s="1" t="inlineStr"/>
-      <c r="V265" s="1" t="inlineStr"/>
-      <c r="W265" s="1" t="inlineStr"/>
-      <c r="X265" s="1" t="inlineStr"/>
-      <c r="Y265" s="1" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="1" t="inlineStr"/>
-      <c r="B266" s="1" t="inlineStr"/>
-      <c r="C266" s="1" t="inlineStr"/>
-      <c r="D266" s="1" t="inlineStr"/>
-      <c r="E266" s="1" t="inlineStr"/>
-      <c r="F266" s="1" t="inlineStr"/>
-      <c r="G266" s="1" t="inlineStr"/>
-      <c r="H266" s="1" t="inlineStr"/>
-      <c r="I266" s="1" t="inlineStr"/>
-      <c r="J266" s="1" t="inlineStr"/>
-      <c r="K266" s="1" t="inlineStr">
-        <is>
-          <t>L827: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: de passage chez M. LÃ©opaul Bougie.</t>
-        </is>
-      </c>
-      <c r="L266" s="1" t="inlineStr"/>
-      <c r="M266" s="1" t="inlineStr"/>
-      <c r="N266" s="1" t="inlineStr"/>
-      <c r="O266" s="1" t="inlineStr"/>
-      <c r="P266" s="1" t="inlineStr"/>
-      <c r="Q266" s="1" t="inlineStr"/>
-      <c r="R266" s="1" t="inlineStr"/>
-      <c r="S266" s="1" t="inlineStr"/>
-      <c r="T266" s="1" t="inlineStr"/>
-      <c r="U266" s="1" t="inlineStr"/>
-      <c r="V266" s="1" t="inlineStr"/>
-      <c r="W266" s="1" t="inlineStr"/>
-      <c r="X266" s="1" t="inlineStr"/>
-      <c r="Y266" s="1" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="1" t="inlineStr"/>
-      <c r="B267" s="1" t="inlineStr"/>
-      <c r="C267" s="1" t="inlineStr"/>
-      <c r="D267" s="1" t="inlineStr"/>
-      <c r="E267" s="1" t="inlineStr"/>
-      <c r="F267" s="1" t="inlineStr"/>
-      <c r="G267" s="1" t="inlineStr"/>
-      <c r="H267" s="1" t="inlineStr"/>
-      <c r="I267" s="1" t="inlineStr"/>
-      <c r="J267" s="1" t="inlineStr"/>
-      <c r="K267" s="1" t="inlineStr">
-        <is>
-          <t>L828: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Mme Bougie est arrivante de MontrÃ©al,</t>
-        </is>
-      </c>
-      <c r="L267" s="1" t="inlineStr"/>
-      <c r="M267" s="1" t="inlineStr"/>
-      <c r="N267" s="1" t="inlineStr"/>
-      <c r="O267" s="1" t="inlineStr"/>
-      <c r="P267" s="1" t="inlineStr"/>
-      <c r="Q267" s="1" t="inlineStr"/>
-      <c r="R267" s="1" t="inlineStr"/>
-      <c r="S267" s="1" t="inlineStr"/>
-      <c r="T267" s="1" t="inlineStr"/>
-      <c r="U267" s="1" t="inlineStr"/>
-      <c r="V267" s="1" t="inlineStr"/>
-      <c r="W267" s="1" t="inlineStr"/>
-      <c r="X267" s="1" t="inlineStr"/>
-      <c r="Y267" s="1" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="1" t="inlineStr"/>
-      <c r="B268" s="1" t="inlineStr"/>
-      <c r="C268" s="1" t="inlineStr"/>
-      <c r="D268" s="1" t="inlineStr"/>
-      <c r="E268" s="1" t="inlineStr"/>
-      <c r="F268" s="1" t="inlineStr"/>
-      <c r="G268" s="1" t="inlineStr"/>
-      <c r="H268" s="1" t="inlineStr"/>
-      <c r="I268" s="1" t="inlineStr"/>
-      <c r="J268" s="1" t="inlineStr"/>
-      <c r="K268" s="1" t="inlineStr">
-        <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: M. AdÃ©lard Roberge a passÃ© ses va-</t>
-        </is>
-      </c>
-      <c r="L268" s="1" t="inlineStr"/>
-      <c r="M268" s="1" t="inlineStr"/>
-      <c r="N268" s="1" t="inlineStr"/>
-      <c r="O268" s="1" t="inlineStr"/>
-      <c r="P268" s="1" t="inlineStr"/>
-      <c r="Q268" s="1" t="inlineStr"/>
-      <c r="R268" s="1" t="inlineStr"/>
-      <c r="S268" s="1" t="inlineStr"/>
-      <c r="T268" s="1" t="inlineStr"/>
-      <c r="U268" s="1" t="inlineStr"/>
-      <c r="V268" s="1" t="inlineStr"/>
-      <c r="W268" s="1" t="inlineStr"/>
-      <c r="X268" s="1" t="inlineStr"/>
-      <c r="Y268" s="1" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="1" t="inlineStr"/>
-      <c r="B269" s="1" t="inlineStr"/>
-      <c r="C269" s="1" t="inlineStr"/>
-      <c r="D269" s="1" t="inlineStr"/>
-      <c r="E269" s="1" t="inlineStr"/>
-      <c r="F269" s="1" t="inlineStr"/>
-      <c r="G269" s="1" t="inlineStr"/>
-      <c r="H269" s="1" t="inlineStr"/>
-      <c r="I269" s="1" t="inlineStr"/>
-      <c r="J269" s="1" t="inlineStr"/>
-      <c r="K269" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+00A8 DIAERESIS :: en mÃ©tal.â€”SystÃ¨mes de classements,</t>
-        </is>
-      </c>
-      <c r="L269" s="1" t="inlineStr"/>
-      <c r="M269" s="1" t="inlineStr"/>
-      <c r="N269" s="1" t="inlineStr"/>
-      <c r="O269" s="1" t="inlineStr"/>
-      <c r="P269" s="1" t="inlineStr"/>
-      <c r="Q269" s="1" t="inlineStr"/>
-      <c r="R269" s="1" t="inlineStr"/>
-      <c r="S269" s="1" t="inlineStr"/>
-      <c r="T269" s="1" t="inlineStr"/>
-      <c r="U269" s="1" t="inlineStr"/>
-      <c r="V269" s="1" t="inlineStr"/>
-      <c r="W269" s="1" t="inlineStr"/>
-      <c r="X269" s="1" t="inlineStr"/>
-      <c r="Y269" s="1" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="1" t="inlineStr"/>
-      <c r="B270" s="1" t="inlineStr"/>
-      <c r="C270" s="1" t="inlineStr"/>
-      <c r="D270" s="1" t="inlineStr"/>
-      <c r="E270" s="1" t="inlineStr"/>
-      <c r="F270" s="1" t="inlineStr"/>
-      <c r="G270" s="1" t="inlineStr"/>
-      <c r="H270" s="1" t="inlineStr"/>
-      <c r="I270" s="1" t="inlineStr"/>
-      <c r="J270" s="1" t="inlineStr"/>
-      <c r="K270" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: le tout fabriquÃ© au Canada.</t>
-        </is>
-      </c>
-      <c r="L270" s="1" t="inlineStr"/>
-      <c r="M270" s="1" t="inlineStr"/>
-      <c r="N270" s="1" t="inlineStr"/>
-      <c r="O270" s="1" t="inlineStr"/>
-      <c r="P270" s="1" t="inlineStr"/>
-      <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="inlineStr"/>
-      <c r="S270" s="1" t="inlineStr"/>
-      <c r="T270" s="1" t="inlineStr"/>
-      <c r="U270" s="1" t="inlineStr"/>
-      <c r="V270" s="1" t="inlineStr"/>
-      <c r="W270" s="1" t="inlineStr"/>
-      <c r="X270" s="1" t="inlineStr"/>
-      <c r="Y270" s="1" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="1" t="inlineStr"/>
-      <c r="B271" s="1" t="inlineStr"/>
-      <c r="C271" s="1" t="inlineStr"/>
-      <c r="D271" s="1" t="inlineStr"/>
-      <c r="E271" s="1" t="inlineStr"/>
-      <c r="F271" s="1" t="inlineStr"/>
-      <c r="G271" s="1" t="inlineStr"/>
-      <c r="H271" s="1" t="inlineStr"/>
-      <c r="I271" s="1" t="inlineStr"/>
-      <c r="J271" s="1" t="inlineStr"/>
-      <c r="K271" s="1" t="inlineStr">
-        <is>
-          <t>L845: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 10514 ,Ave Jasper TÃ©l.: 24636</t>
-        </is>
-      </c>
-      <c r="L271" s="1" t="inlineStr"/>
-      <c r="M271" s="1" t="inlineStr"/>
-      <c r="N271" s="1" t="inlineStr"/>
-      <c r="O271" s="1" t="inlineStr"/>
-      <c r="P271" s="1" t="inlineStr"/>
-      <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="inlineStr"/>
-      <c r="S271" s="1" t="inlineStr"/>
-      <c r="T271" s="1" t="inlineStr"/>
-      <c r="U271" s="1" t="inlineStr"/>
-      <c r="V271" s="1" t="inlineStr"/>
-      <c r="W271" s="1" t="inlineStr"/>
-      <c r="X271" s="1" t="inlineStr"/>
-      <c r="Y271" s="1" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="1" t="inlineStr"/>
-      <c r="B272" s="1" t="inlineStr"/>
-      <c r="C272" s="1" t="inlineStr"/>
-      <c r="D272" s="1" t="inlineStr"/>
-      <c r="E272" s="1" t="inlineStr"/>
-      <c r="F272" s="1" t="inlineStr"/>
-      <c r="G272" s="1" t="inlineStr"/>
-      <c r="H272" s="1" t="inlineStr"/>
-      <c r="I272" s="1" t="inlineStr"/>
-      <c r="J272" s="1" t="inlineStr"/>
-      <c r="K272" s="1" t="inlineStr">
-        <is>
-          <t>L853: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 109e (letter/digit mix) :: 10330 - 109e rue TÃ©l. 24165</t>
-        </is>
-      </c>
-      <c r="L272" s="1" t="inlineStr"/>
-      <c r="M272" s="1" t="inlineStr"/>
-      <c r="N272" s="1" t="inlineStr"/>
-      <c r="O272" s="1" t="inlineStr"/>
-      <c r="P272" s="1" t="inlineStr"/>
-      <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="inlineStr"/>
-      <c r="S272" s="1" t="inlineStr"/>
-      <c r="T272" s="1" t="inlineStr"/>
-      <c r="U272" s="1" t="inlineStr"/>
-      <c r="V272" s="1" t="inlineStr"/>
-      <c r="W272" s="1" t="inlineStr"/>
-      <c r="X272" s="1" t="inlineStr"/>
-      <c r="Y272" s="1" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="1" t="inlineStr"/>
-      <c r="B273" s="1" t="inlineStr"/>
-      <c r="C273" s="1" t="inlineStr"/>
-      <c r="D273" s="1" t="inlineStr"/>
-      <c r="E273" s="1" t="inlineStr"/>
-      <c r="F273" s="1" t="inlineStr"/>
-      <c r="G273" s="1" t="inlineStr"/>
-      <c r="H273" s="1" t="inlineStr"/>
-      <c r="I273" s="1" t="inlineStr"/>
-      <c r="J273" s="1" t="inlineStr"/>
-      <c r="K273" s="1" t="inlineStr">
-        <is>
-          <t>L857: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: EATONâ€™S</t>
-        </is>
-      </c>
-      <c r="L273" s="1" t="inlineStr"/>
-      <c r="M273" s="1" t="inlineStr"/>
-      <c r="N273" s="1" t="inlineStr"/>
-      <c r="O273" s="1" t="inlineStr"/>
-      <c r="P273" s="1" t="inlineStr"/>
-      <c r="Q273" s="1" t="inlineStr"/>
-      <c r="R273" s="1" t="inlineStr"/>
-      <c r="S273" s="1" t="inlineStr"/>
-      <c r="T273" s="1" t="inlineStr"/>
-      <c r="U273" s="1" t="inlineStr"/>
-      <c r="V273" s="1" t="inlineStr"/>
-      <c r="W273" s="1" t="inlineStr"/>
-      <c r="X273" s="1" t="inlineStr"/>
-      <c r="Y273" s="1" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="1" t="inlineStr"/>
-      <c r="B274" s="1" t="inlineStr"/>
-      <c r="C274" s="1" t="inlineStr"/>
-      <c r="D274" s="1" t="inlineStr"/>
-      <c r="E274" s="1" t="inlineStr"/>
-      <c r="F274" s="1" t="inlineStr"/>
-      <c r="G274" s="1" t="inlineStr"/>
-      <c r="H274" s="1" t="inlineStr"/>
-      <c r="I274" s="1" t="inlineStr"/>
-      <c r="J274" s="1" t="inlineStr"/>
-      <c r="K274" s="1" t="inlineStr">
-        <is>
-          <t>L863: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: AimÃ©-R. Bernier</t>
-        </is>
-      </c>
-      <c r="L274" s="1" t="inlineStr"/>
-      <c r="M274" s="1" t="inlineStr"/>
-      <c r="N274" s="1" t="inlineStr"/>
-      <c r="O274" s="1" t="inlineStr"/>
-      <c r="P274" s="1" t="inlineStr"/>
-      <c r="Q274" s="1" t="inlineStr"/>
-      <c r="R274" s="1" t="inlineStr"/>
-      <c r="S274" s="1" t="inlineStr"/>
-      <c r="T274" s="1" t="inlineStr"/>
-      <c r="U274" s="1" t="inlineStr"/>
-      <c r="V274" s="1" t="inlineStr"/>
-      <c r="W274" s="1" t="inlineStr"/>
-      <c r="X274" s="1" t="inlineStr"/>
-      <c r="Y274" s="1" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="1" t="inlineStr"/>
-      <c r="B275" s="1" t="inlineStr"/>
-      <c r="C275" s="1" t="inlineStr"/>
-      <c r="D275" s="1" t="inlineStr"/>
-      <c r="E275" s="1" t="inlineStr"/>
-      <c r="F275" s="1" t="inlineStr"/>
-      <c r="G275" s="1" t="inlineStr"/>
-      <c r="H275" s="1" t="inlineStr"/>
-      <c r="I275" s="1" t="inlineStr"/>
-      <c r="J275" s="1" t="inlineStr"/>
-      <c r="K275" s="1" t="inlineStr">
-        <is>
-          <t>L868: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN :: TÃ©l.: Bureau: 27365 â€” RÃ©s.: 24017</t>
-        </is>
-      </c>
-      <c r="L275" s="1" t="inlineStr"/>
-      <c r="M275" s="1" t="inlineStr"/>
-      <c r="N275" s="1" t="inlineStr"/>
-      <c r="O275" s="1" t="inlineStr"/>
-      <c r="P275" s="1" t="inlineStr"/>
-      <c r="Q275" s="1" t="inlineStr"/>
-      <c r="R275" s="1" t="inlineStr"/>
-      <c r="S275" s="1" t="inlineStr"/>
-      <c r="T275" s="1" t="inlineStr"/>
-      <c r="U275" s="1" t="inlineStr"/>
-      <c r="V275" s="1" t="inlineStr"/>
-      <c r="W275" s="1" t="inlineStr"/>
-      <c r="X275" s="1" t="inlineStr"/>
-      <c r="Y275" s="1" t="inlineStr"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="1" t="inlineStr"/>
-      <c r="B276" s="1" t="inlineStr"/>
-      <c r="C276" s="1" t="inlineStr"/>
-      <c r="D276" s="1" t="inlineStr"/>
-      <c r="E276" s="1" t="inlineStr"/>
-      <c r="F276" s="1" t="inlineStr"/>
-      <c r="G276" s="1" t="inlineStr"/>
-      <c r="H276" s="1" t="inlineStr"/>
-      <c r="I276" s="1" t="inlineStr"/>
-      <c r="J276" s="1" t="inlineStr"/>
-      <c r="K276" s="1" t="inlineStr">
-        <is>
-          <t>L870: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS, U+20AC EURO SIGN :: 114 Edifice La FlÃ¨che â€” Edmonton</t>
-        </is>
-      </c>
-      <c r="L276" s="1" t="inlineStr"/>
-      <c r="M276" s="1" t="inlineStr"/>
-      <c r="N276" s="1" t="inlineStr"/>
-      <c r="O276" s="1" t="inlineStr"/>
-      <c r="P276" s="1" t="inlineStr"/>
-      <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="inlineStr"/>
-      <c r="S276" s="1" t="inlineStr"/>
-      <c r="T276" s="1" t="inlineStr"/>
-      <c r="U276" s="1" t="inlineStr"/>
-      <c r="V276" s="1" t="inlineStr"/>
-      <c r="W276" s="1" t="inlineStr"/>
-      <c r="X276" s="1" t="inlineStr"/>
-      <c r="Y276" s="1" t="inlineStr"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="1" t="inlineStr"/>
-      <c r="B277" s="1" t="inlineStr"/>
-      <c r="C277" s="1" t="inlineStr"/>
-      <c r="D277" s="1" t="inlineStr"/>
-      <c r="E277" s="1" t="inlineStr"/>
-      <c r="F277" s="1" t="inlineStr"/>
-      <c r="G277" s="1" t="inlineStr"/>
-      <c r="H277" s="1" t="inlineStr"/>
-      <c r="I277" s="1" t="inlineStr"/>
-      <c r="J277" s="1" t="inlineStr"/>
-      <c r="K277" s="1" t="inlineStr">
-        <is>
-          <t>L875: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN :: EbÃ©nisterie â€” Boiseries â€” RÃ©para-</t>
-        </is>
-      </c>
-      <c r="L277" s="1" t="inlineStr"/>
-      <c r="M277" s="1" t="inlineStr"/>
-      <c r="N277" s="1" t="inlineStr"/>
-      <c r="O277" s="1" t="inlineStr"/>
-      <c r="P277" s="1" t="inlineStr"/>
-      <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="inlineStr"/>
-      <c r="S277" s="1" t="inlineStr"/>
-      <c r="T277" s="1" t="inlineStr"/>
-      <c r="U277" s="1" t="inlineStr"/>
-      <c r="V277" s="1" t="inlineStr"/>
-      <c r="W277" s="1" t="inlineStr"/>
-      <c r="X277" s="1" t="inlineStr"/>
-      <c r="Y277" s="1" t="inlineStr"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="1" t="inlineStr"/>
-      <c r="B278" s="1" t="inlineStr"/>
-      <c r="C278" s="1" t="inlineStr"/>
-      <c r="D278" s="1" t="inlineStr"/>
-      <c r="E278" s="1" t="inlineStr"/>
-      <c r="F278" s="1" t="inlineStr"/>
-      <c r="G278" s="1" t="inlineStr"/>
-      <c r="H278" s="1" t="inlineStr"/>
-      <c r="I278" s="1" t="inlineStr"/>
-      <c r="J278" s="1" t="inlineStr"/>
-      <c r="K278" s="1" t="inlineStr">
-        <is>
-          <t>L886: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l.: 33777</t>
-        </is>
-      </c>
-      <c r="L278" s="1" t="inlineStr"/>
-      <c r="M278" s="1" t="inlineStr"/>
-      <c r="N278" s="1" t="inlineStr"/>
-      <c r="O278" s="1" t="inlineStr"/>
-      <c r="P278" s="1" t="inlineStr"/>
-      <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="inlineStr"/>
-      <c r="S278" s="1" t="inlineStr"/>
-      <c r="T278" s="1" t="inlineStr"/>
-      <c r="U278" s="1" t="inlineStr"/>
-      <c r="V278" s="1" t="inlineStr"/>
-      <c r="W278" s="1" t="inlineStr"/>
-      <c r="X278" s="1" t="inlineStr"/>
-      <c r="Y278" s="1" t="inlineStr"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="1" t="inlineStr"/>
-      <c r="B279" s="1" t="inlineStr"/>
-      <c r="C279" s="1" t="inlineStr"/>
-      <c r="D279" s="1" t="inlineStr"/>
-      <c r="E279" s="1" t="inlineStr"/>
-      <c r="F279" s="1" t="inlineStr"/>
-      <c r="G279" s="1" t="inlineStr"/>
-      <c r="H279" s="1" t="inlineStr"/>
-      <c r="I279" s="1" t="inlineStr"/>
-      <c r="J279" s="1" t="inlineStr"/>
-      <c r="K279" s="1" t="inlineStr">
-        <is>
-          <t>L895: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 548 pages intÃ©ressantes!</t>
-        </is>
-      </c>
-      <c r="L279" s="1" t="inlineStr"/>
-      <c r="M279" s="1" t="inlineStr"/>
-      <c r="N279" s="1" t="inlineStr"/>
-      <c r="O279" s="1" t="inlineStr"/>
-      <c r="P279" s="1" t="inlineStr"/>
-      <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="inlineStr"/>
-      <c r="S279" s="1" t="inlineStr"/>
-      <c r="T279" s="1" t="inlineStr"/>
-      <c r="U279" s="1" t="inlineStr"/>
-      <c r="V279" s="1" t="inlineStr"/>
-      <c r="W279" s="1" t="inlineStr"/>
-      <c r="X279" s="1" t="inlineStr"/>
-      <c r="Y279" s="1" t="inlineStr"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="1" t="inlineStr"/>
-      <c r="B280" s="1" t="inlineStr"/>
-      <c r="C280" s="1" t="inlineStr"/>
-      <c r="D280" s="1" t="inlineStr"/>
-      <c r="E280" s="1" t="inlineStr"/>
-      <c r="F280" s="1" t="inlineStr"/>
-      <c r="G280" s="1" t="inlineStr"/>
-      <c r="H280" s="1" t="inlineStr"/>
-      <c r="I280" s="1" t="inlineStr"/>
-      <c r="J280" s="1" t="inlineStr"/>
-      <c r="K280" s="1" t="inlineStr">
-        <is>
-          <t>L903: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: EATONâ€”</t>
-        </is>
-      </c>
-      <c r="L280" s="1" t="inlineStr"/>
-      <c r="M280" s="1" t="inlineStr"/>
-      <c r="N280" s="1" t="inlineStr"/>
-      <c r="O280" s="1" t="inlineStr"/>
-      <c r="P280" s="1" t="inlineStr"/>
-      <c r="Q280" s="1" t="inlineStr"/>
-      <c r="R280" s="1" t="inlineStr"/>
-      <c r="S280" s="1" t="inlineStr"/>
-      <c r="T280" s="1" t="inlineStr"/>
-      <c r="U280" s="1" t="inlineStr"/>
-      <c r="V280" s="1" t="inlineStr"/>
-      <c r="W280" s="1" t="inlineStr"/>
-      <c r="X280" s="1" t="inlineStr"/>
-      <c r="Y280" s="1" t="inlineStr"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="1" t="inlineStr"/>
-      <c r="B281" s="1" t="inlineStr"/>
-      <c r="C281" s="1" t="inlineStr"/>
-      <c r="D281" s="1" t="inlineStr"/>
-      <c r="E281" s="1" t="inlineStr"/>
-      <c r="F281" s="1" t="inlineStr"/>
-      <c r="G281" s="1" t="inlineStr"/>
-      <c r="H281" s="1" t="inlineStr"/>
-      <c r="I281" s="1" t="inlineStr"/>
-      <c r="J281" s="1" t="inlineStr"/>
-      <c r="K281" s="1" t="inlineStr">
-        <is>
-          <t>L909: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Si vous nâ€™avez pas encore reÃ§u vo-</t>
-        </is>
-      </c>
-      <c r="L281" s="1" t="inlineStr"/>
-      <c r="M281" s="1" t="inlineStr"/>
-      <c r="N281" s="1" t="inlineStr"/>
-      <c r="O281" s="1" t="inlineStr"/>
-      <c r="P281" s="1" t="inlineStr"/>
-      <c r="Q281" s="1" t="inlineStr"/>
-      <c r="R281" s="1" t="inlineStr"/>
-      <c r="S281" s="1" t="inlineStr"/>
-      <c r="T281" s="1" t="inlineStr"/>
-      <c r="U281" s="1" t="inlineStr"/>
-      <c r="V281" s="1" t="inlineStr"/>
-      <c r="W281" s="1" t="inlineStr"/>
-      <c r="X281" s="1" t="inlineStr"/>
-      <c r="Y281" s="1" t="inlineStr"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="1" t="inlineStr"/>
-      <c r="B282" s="1" t="inlineStr"/>
-      <c r="C282" s="1" t="inlineStr"/>
-      <c r="D282" s="1" t="inlineStr"/>
-      <c r="E282" s="1" t="inlineStr"/>
-      <c r="F282" s="1" t="inlineStr"/>
-      <c r="G282" s="1" t="inlineStr"/>
-      <c r="H282" s="1" t="inlineStr"/>
-      <c r="I282" s="1" t="inlineStr"/>
-      <c r="J282" s="1" t="inlineStr"/>
-      <c r="K282" s="1" t="inlineStr">
-        <is>
-          <t>L913: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: plus rapprochÃ©. Si leur rÃ©serve est</t>
-        </is>
-      </c>
-      <c r="L282" s="1" t="inlineStr"/>
-      <c r="M282" s="1" t="inlineStr"/>
-      <c r="N282" s="1" t="inlineStr"/>
-      <c r="O282" s="1" t="inlineStr"/>
-      <c r="P282" s="1" t="inlineStr"/>
-      <c r="Q282" s="1" t="inlineStr"/>
-      <c r="R282" s="1" t="inlineStr"/>
-      <c r="S282" s="1" t="inlineStr"/>
-      <c r="T282" s="1" t="inlineStr"/>
-      <c r="U282" s="1" t="inlineStr"/>
-      <c r="V282" s="1" t="inlineStr"/>
-      <c r="W282" s="1" t="inlineStr"/>
-      <c r="X282" s="1" t="inlineStr"/>
-      <c r="Y282" s="1" t="inlineStr"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="1" t="inlineStr"/>
-      <c r="B283" s="1" t="inlineStr"/>
-      <c r="C283" s="1" t="inlineStr"/>
-      <c r="D283" s="1" t="inlineStr"/>
-      <c r="E283" s="1" t="inlineStr"/>
-      <c r="F283" s="1" t="inlineStr"/>
-      <c r="G283" s="1" t="inlineStr"/>
-      <c r="H283" s="1" t="inlineStr"/>
-      <c r="I283" s="1" t="inlineStr"/>
-      <c r="J283" s="1" t="inlineStr"/>
-      <c r="K283" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Ã©puisÃ©e, Ã©crivez Ã : The Circula-</t>
-        </is>
-      </c>
-      <c r="L283" s="1" t="inlineStr"/>
-      <c r="M283" s="1" t="inlineStr"/>
-      <c r="N283" s="1" t="inlineStr"/>
-      <c r="O283" s="1" t="inlineStr"/>
-      <c r="P283" s="1" t="inlineStr"/>
-      <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="inlineStr"/>
-      <c r="S283" s="1" t="inlineStr"/>
-      <c r="T283" s="1" t="inlineStr"/>
-      <c r="U283" s="1" t="inlineStr"/>
-      <c r="V283" s="1" t="inlineStr"/>
-      <c r="W283" s="1" t="inlineStr"/>
-      <c r="X283" s="1" t="inlineStr"/>
-      <c r="Y283" s="1" t="inlineStr"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="1" t="inlineStr"/>
-      <c r="B284" s="1" t="inlineStr"/>
-      <c r="C284" s="1" t="inlineStr"/>
-      <c r="D284" s="1" t="inlineStr"/>
-      <c r="E284" s="1" t="inlineStr"/>
-      <c r="F284" s="1" t="inlineStr"/>
-      <c r="G284" s="1" t="inlineStr"/>
-      <c r="H284" s="1" t="inlineStr"/>
-      <c r="I284" s="1" t="inlineStr"/>
-      <c r="J284" s="1" t="inlineStr"/>
-      <c r="K284" s="1" t="inlineStr">
-        <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 10043, ave Jasper TÃ©l.: 25935</t>
-        </is>
-      </c>
-      <c r="L284" s="1" t="inlineStr"/>
-      <c r="M284" s="1" t="inlineStr"/>
-      <c r="N284" s="1" t="inlineStr"/>
-      <c r="O284" s="1" t="inlineStr"/>
-      <c r="P284" s="1" t="inlineStr"/>
-      <c r="Q284" s="1" t="inlineStr"/>
-      <c r="R284" s="1" t="inlineStr"/>
-      <c r="S284" s="1" t="inlineStr"/>
-      <c r="T284" s="1" t="inlineStr"/>
-      <c r="U284" s="1" t="inlineStr"/>
-      <c r="V284" s="1" t="inlineStr"/>
-      <c r="W284" s="1" t="inlineStr"/>
-      <c r="X284" s="1" t="inlineStr"/>
-      <c r="Y284" s="1" t="inlineStr"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="1" t="inlineStr"/>
-      <c r="B285" s="1" t="inlineStr"/>
-      <c r="C285" s="1" t="inlineStr"/>
-      <c r="D285" s="1" t="inlineStr"/>
-      <c r="E285" s="1" t="inlineStr"/>
-      <c r="F285" s="1" t="inlineStr"/>
-      <c r="G285" s="1" t="inlineStr"/>
-      <c r="H285" s="1" t="inlineStr"/>
-      <c r="I285" s="1" t="inlineStr"/>
-      <c r="J285" s="1" t="inlineStr"/>
-      <c r="K285" s="1" t="inlineStr">
-        <is>
-          <t>L936: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): 124e (letter/digit mix) :: RÃ©sidence 10248-124e rue TÃ©l. 84691</t>
-        </is>
-      </c>
-      <c r="L285" s="1" t="inlineStr"/>
-      <c r="M285" s="1" t="inlineStr"/>
-      <c r="N285" s="1" t="inlineStr"/>
-      <c r="O285" s="1" t="inlineStr"/>
-      <c r="P285" s="1" t="inlineStr"/>
-      <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="inlineStr"/>
-      <c r="S285" s="1" t="inlineStr"/>
-      <c r="T285" s="1" t="inlineStr"/>
-      <c r="U285" s="1" t="inlineStr"/>
-      <c r="V285" s="1" t="inlineStr"/>
-      <c r="W285" s="1" t="inlineStr"/>
-      <c r="X285" s="1" t="inlineStr"/>
-      <c r="Y285" s="1" t="inlineStr"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="1" t="inlineStr"/>
-      <c r="B286" s="1" t="inlineStr"/>
-      <c r="C286" s="1" t="inlineStr"/>
-      <c r="D286" s="1" t="inlineStr"/>
-      <c r="E286" s="1" t="inlineStr"/>
-      <c r="F286" s="1" t="inlineStr"/>
-      <c r="G286" s="1" t="inlineStr"/>
-      <c r="H286" s="1" t="inlineStr"/>
-      <c r="I286" s="1" t="inlineStr"/>
-      <c r="J286" s="1" t="inlineStr"/>
-      <c r="K286" s="1" t="inlineStr">
-        <is>
-          <t>L941: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: SpÃ©cialitÃ© de Vie</t>
-        </is>
-      </c>
-      <c r="L286" s="1" t="inlineStr"/>
-      <c r="M286" s="1" t="inlineStr"/>
-      <c r="N286" s="1" t="inlineStr"/>
-      <c r="O286" s="1" t="inlineStr"/>
-      <c r="P286" s="1" t="inlineStr"/>
-      <c r="Q286" s="1" t="inlineStr"/>
-      <c r="R286" s="1" t="inlineStr"/>
-      <c r="S286" s="1" t="inlineStr"/>
-      <c r="T286" s="1" t="inlineStr"/>
-      <c r="U286" s="1" t="inlineStr"/>
-      <c r="V286" s="1" t="inlineStr"/>
-      <c r="W286" s="1" t="inlineStr"/>
-      <c r="X286" s="1" t="inlineStr"/>
-      <c r="Y286" s="1" t="inlineStr"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="1" t="inlineStr"/>
-      <c r="B287" s="1" t="inlineStr"/>
-      <c r="C287" s="1" t="inlineStr"/>
-      <c r="D287" s="1" t="inlineStr"/>
-      <c r="E287" s="1" t="inlineStr"/>
-      <c r="F287" s="1" t="inlineStr"/>
-      <c r="G287" s="1" t="inlineStr"/>
-      <c r="H287" s="1" t="inlineStr"/>
-      <c r="I287" s="1" t="inlineStr"/>
-      <c r="J287" s="1" t="inlineStr"/>
-      <c r="K287" s="1" t="inlineStr">
-        <is>
-          <t>L943: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN :: TÃ©l.: Bureau: 26573 â€” RÃ©s.: 26693</t>
-        </is>
-      </c>
-      <c r="L287" s="1" t="inlineStr"/>
-      <c r="M287" s="1" t="inlineStr"/>
-      <c r="N287" s="1" t="inlineStr"/>
-      <c r="O287" s="1" t="inlineStr"/>
-      <c r="P287" s="1" t="inlineStr"/>
-      <c r="Q287" s="1" t="inlineStr"/>
-      <c r="R287" s="1" t="inlineStr"/>
-      <c r="S287" s="1" t="inlineStr"/>
-      <c r="T287" s="1" t="inlineStr"/>
-      <c r="U287" s="1" t="inlineStr"/>
-      <c r="V287" s="1" t="inlineStr"/>
-      <c r="W287" s="1" t="inlineStr"/>
-      <c r="X287" s="1" t="inlineStr"/>
-      <c r="Y287" s="1" t="inlineStr"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="1" t="inlineStr"/>
-      <c r="B288" s="1" t="inlineStr"/>
-      <c r="C288" s="1" t="inlineStr"/>
-      <c r="D288" s="1" t="inlineStr"/>
-      <c r="E288" s="1" t="inlineStr"/>
-      <c r="F288" s="1" t="inlineStr"/>
-      <c r="G288" s="1" t="inlineStr"/>
-      <c r="H288" s="1" t="inlineStr"/>
-      <c r="I288" s="1" t="inlineStr"/>
-      <c r="J288" s="1" t="inlineStr"/>
-      <c r="K288" s="1" t="inlineStr">
-        <is>
-          <t>L947: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: LÃ©o Belhumeur</t>
-        </is>
-      </c>
-      <c r="L288" s="1" t="inlineStr"/>
-      <c r="M288" s="1" t="inlineStr"/>
-      <c r="N288" s="1" t="inlineStr"/>
-      <c r="O288" s="1" t="inlineStr"/>
-      <c r="P288" s="1" t="inlineStr"/>
-      <c r="Q288" s="1" t="inlineStr"/>
-      <c r="R288" s="1" t="inlineStr"/>
-      <c r="S288" s="1" t="inlineStr"/>
-      <c r="T288" s="1" t="inlineStr"/>
-      <c r="U288" s="1" t="inlineStr"/>
-      <c r="V288" s="1" t="inlineStr"/>
-      <c r="W288" s="1" t="inlineStr"/>
-      <c r="X288" s="1" t="inlineStr"/>
-      <c r="Y288" s="1" t="inlineStr"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="1" t="inlineStr"/>
-      <c r="B289" s="1" t="inlineStr"/>
-      <c r="C289" s="1" t="inlineStr"/>
-      <c r="D289" s="1" t="inlineStr"/>
-      <c r="E289" s="1" t="inlineStr"/>
-      <c r="F289" s="1" t="inlineStr"/>
-      <c r="G289" s="1" t="inlineStr"/>
-      <c r="H289" s="1" t="inlineStr"/>
-      <c r="I289" s="1" t="inlineStr"/>
-      <c r="J289" s="1" t="inlineStr"/>
-      <c r="K289" s="1" t="inlineStr">
-        <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Vie â€” Feu â€” Auto â€” GrÃªle</t>
-        </is>
-      </c>
-      <c r="L289" s="1" t="inlineStr"/>
-      <c r="M289" s="1" t="inlineStr"/>
-      <c r="N289" s="1" t="inlineStr"/>
-      <c r="O289" s="1" t="inlineStr"/>
-      <c r="P289" s="1" t="inlineStr"/>
-      <c r="Q289" s="1" t="inlineStr"/>
-      <c r="R289" s="1" t="inlineStr"/>
-      <c r="S289" s="1" t="inlineStr"/>
-      <c r="T289" s="1" t="inlineStr"/>
-      <c r="U289" s="1" t="inlineStr"/>
-      <c r="V289" s="1" t="inlineStr"/>
-      <c r="W289" s="1" t="inlineStr"/>
-      <c r="X289" s="1" t="inlineStr"/>
-      <c r="Y289" s="1" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="1" t="inlineStr"/>
-      <c r="B290" s="1" t="inlineStr"/>
-      <c r="C290" s="1" t="inlineStr"/>
-      <c r="D290" s="1" t="inlineStr"/>
-      <c r="E290" s="1" t="inlineStr"/>
-      <c r="F290" s="1" t="inlineStr"/>
-      <c r="G290" s="1" t="inlineStr"/>
-      <c r="H290" s="1" t="inlineStr"/>
-      <c r="I290" s="1" t="inlineStr"/>
-      <c r="J290" s="1" t="inlineStr"/>
-      <c r="K290" s="1" t="inlineStr">
-        <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN, U+20AC EURO SIGN, U+2122 TRADE MARK SIGN, U+00B4 ACUTE ACCENT :: ComptabilitÃ©, rapports dâ€™impÃ´ts (In-</t>
-        </is>
-      </c>
-      <c r="L290" s="1" t="inlineStr"/>
-      <c r="M290" s="1" t="inlineStr"/>
-      <c r="N290" s="1" t="inlineStr"/>
-      <c r="O290" s="1" t="inlineStr"/>
-      <c r="P290" s="1" t="inlineStr"/>
-      <c r="Q290" s="1" t="inlineStr"/>
-      <c r="R290" s="1" t="inlineStr"/>
-      <c r="S290" s="1" t="inlineStr"/>
-      <c r="T290" s="1" t="inlineStr"/>
-      <c r="U290" s="1" t="inlineStr"/>
-      <c r="V290" s="1" t="inlineStr"/>
-      <c r="W290" s="1" t="inlineStr"/>
-      <c r="X290" s="1" t="inlineStr"/>
-      <c r="Y290" s="1" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="1" t="inlineStr"/>
-      <c r="B291" s="1" t="inlineStr"/>
-      <c r="C291" s="1" t="inlineStr"/>
-      <c r="D291" s="1" t="inlineStr"/>
-      <c r="E291" s="1" t="inlineStr"/>
-      <c r="F291" s="1" t="inlineStr"/>
-      <c r="G291" s="1" t="inlineStr"/>
-      <c r="H291" s="1" t="inlineStr"/>
-      <c r="I291" s="1" t="inlineStr"/>
-      <c r="J291" s="1" t="inlineStr"/>
-      <c r="K291" s="1" t="inlineStr">
-        <is>
-          <t>L964: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l.: 26</t>
-        </is>
-      </c>
-      <c r="L291" s="1" t="inlineStr"/>
-      <c r="M291" s="1" t="inlineStr"/>
-      <c r="N291" s="1" t="inlineStr"/>
-      <c r="O291" s="1" t="inlineStr"/>
-      <c r="P291" s="1" t="inlineStr"/>
-      <c r="Q291" s="1" t="inlineStr"/>
-      <c r="R291" s="1" t="inlineStr"/>
-      <c r="S291" s="1" t="inlineStr"/>
-      <c r="T291" s="1" t="inlineStr"/>
-      <c r="U291" s="1" t="inlineStr"/>
-      <c r="V291" s="1" t="inlineStr"/>
-      <c r="W291" s="1" t="inlineStr"/>
-      <c r="X291" s="1" t="inlineStr"/>
-      <c r="Y291" s="1" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="1" t="inlineStr"/>
-      <c r="B292" s="1" t="inlineStr"/>
-      <c r="C292" s="1" t="inlineStr"/>
-      <c r="D292" s="1" t="inlineStr"/>
-      <c r="E292" s="1" t="inlineStr"/>
-      <c r="F292" s="1" t="inlineStr"/>
-      <c r="G292" s="1" t="inlineStr"/>
-      <c r="H292" s="1" t="inlineStr"/>
-      <c r="I292" s="1" t="inlineStr"/>
-      <c r="J292" s="1" t="inlineStr"/>
-      <c r="K292" s="1" t="inlineStr">
-        <is>
-          <t>L970: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l.: 22912</t>
-        </is>
-      </c>
-      <c r="L292" s="1" t="inlineStr"/>
-      <c r="M292" s="1" t="inlineStr"/>
-      <c r="N292" s="1" t="inlineStr"/>
-      <c r="O292" s="1" t="inlineStr"/>
-      <c r="P292" s="1" t="inlineStr"/>
-      <c r="Q292" s="1" t="inlineStr"/>
-      <c r="R292" s="1" t="inlineStr"/>
-      <c r="S292" s="1" t="inlineStr"/>
-      <c r="T292" s="1" t="inlineStr"/>
-      <c r="U292" s="1" t="inlineStr"/>
-      <c r="V292" s="1" t="inlineStr"/>
-      <c r="W292" s="1" t="inlineStr"/>
-      <c r="X292" s="1" t="inlineStr"/>
-      <c r="Y292" s="1" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="inlineStr"/>
-      <c r="B293" s="1" t="inlineStr"/>
-      <c r="C293" s="1" t="inlineStr"/>
-      <c r="D293" s="1" t="inlineStr"/>
-      <c r="E293" s="1" t="inlineStr"/>
-      <c r="F293" s="1" t="inlineStr"/>
-      <c r="G293" s="1" t="inlineStr"/>
-      <c r="H293" s="1" t="inlineStr"/>
-      <c r="I293" s="1" t="inlineStr"/>
-      <c r="J293" s="1" t="inlineStr"/>
-      <c r="K293" s="1" t="inlineStr">
-        <is>
-          <t>L972: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l. rÃ©s.: 23686</t>
-        </is>
-      </c>
-      <c r="L293" s="1" t="inlineStr"/>
-      <c r="M293" s="1" t="inlineStr"/>
-      <c r="N293" s="1" t="inlineStr"/>
-      <c r="O293" s="1" t="inlineStr"/>
-      <c r="P293" s="1" t="inlineStr"/>
-      <c r="Q293" s="1" t="inlineStr"/>
-      <c r="R293" s="1" t="inlineStr"/>
-      <c r="S293" s="1" t="inlineStr"/>
-      <c r="T293" s="1" t="inlineStr"/>
-      <c r="U293" s="1" t="inlineStr"/>
-      <c r="V293" s="1" t="inlineStr"/>
-      <c r="W293" s="1" t="inlineStr"/>
-      <c r="X293" s="1" t="inlineStr"/>
-      <c r="Y293" s="1" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="inlineStr"/>
-      <c r="B294" s="1" t="inlineStr"/>
-      <c r="C294" s="1" t="inlineStr"/>
-      <c r="D294" s="1" t="inlineStr"/>
-      <c r="E294" s="1" t="inlineStr"/>
-      <c r="F294" s="1" t="inlineStr"/>
-      <c r="G294" s="1" t="inlineStr"/>
-      <c r="H294" s="1" t="inlineStr"/>
-      <c r="I294" s="1" t="inlineStr"/>
-      <c r="J294" s="1" t="inlineStr"/>
-      <c r="K294" s="1" t="inlineStr">
-        <is>
-          <t>L985: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A9 COPYRIGHT SIGN :: 10337-102 rue, Edmontonâ€”TÃ©l. 27806</t>
-        </is>
-      </c>
-      <c r="L294" s="1" t="inlineStr"/>
-      <c r="M294" s="1" t="inlineStr"/>
-      <c r="N294" s="1" t="inlineStr"/>
-      <c r="O294" s="1" t="inlineStr"/>
-      <c r="P294" s="1" t="inlineStr"/>
-      <c r="Q294" s="1" t="inlineStr"/>
-      <c r="R294" s="1" t="inlineStr"/>
-      <c r="S294" s="1" t="inlineStr"/>
-      <c r="T294" s="1" t="inlineStr"/>
-      <c r="U294" s="1" t="inlineStr"/>
-      <c r="V294" s="1" t="inlineStr"/>
-      <c r="W294" s="1" t="inlineStr"/>
-      <c r="X294" s="1" t="inlineStr"/>
-      <c r="Y294" s="1" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="inlineStr"/>
-      <c r="B295" s="1" t="inlineStr"/>
-      <c r="C295" s="1" t="inlineStr"/>
-      <c r="D295" s="1" t="inlineStr"/>
-      <c r="E295" s="1" t="inlineStr"/>
-      <c r="F295" s="1" t="inlineStr"/>
-      <c r="G295" s="1" t="inlineStr"/>
-      <c r="H295" s="1" t="inlineStr"/>
-      <c r="I295" s="1" t="inlineStr"/>
-      <c r="J295" s="1" t="inlineStr"/>
-      <c r="K295" s="1" t="inlineStr">
-        <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: genres de propriÃ©tÃ©s par toutes les pro-</t>
-        </is>
-      </c>
-      <c r="L295" s="1" t="inlineStr"/>
-      <c r="M295" s="1" t="inlineStr"/>
-      <c r="N295" s="1" t="inlineStr"/>
-      <c r="O295" s="1" t="inlineStr"/>
-      <c r="P295" s="1" t="inlineStr"/>
-      <c r="Q295" s="1" t="inlineStr"/>
-      <c r="R295" s="1" t="inlineStr"/>
-      <c r="S295" s="1" t="inlineStr"/>
-      <c r="T295" s="1" t="inlineStr"/>
-      <c r="U295" s="1" t="inlineStr"/>
-      <c r="V295" s="1" t="inlineStr"/>
-      <c r="W295" s="1" t="inlineStr"/>
-      <c r="X295" s="1" t="inlineStr"/>
-      <c r="Y295" s="1" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="1" t="inlineStr"/>
-      <c r="B296" s="1" t="inlineStr"/>
-      <c r="C296" s="1" t="inlineStr"/>
-      <c r="D296" s="1" t="inlineStr"/>
-      <c r="E296" s="1" t="inlineStr"/>
-      <c r="F296" s="1" t="inlineStr"/>
-      <c r="G296" s="1" t="inlineStr"/>
-      <c r="H296" s="1" t="inlineStr"/>
-      <c r="I296" s="1" t="inlineStr"/>
-      <c r="J296" s="1" t="inlineStr"/>
-      <c r="K296" s="1" t="inlineStr">
-        <is>
-          <t>L998: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: Q. C. P. 627, TÃ©l.: 1657-M.</t>
-        </is>
-      </c>
-      <c r="L296" s="1" t="inlineStr"/>
-      <c r="M296" s="1" t="inlineStr"/>
-      <c r="N296" s="1" t="inlineStr"/>
-      <c r="O296" s="1" t="inlineStr"/>
-      <c r="P296" s="1" t="inlineStr"/>
-      <c r="Q296" s="1" t="inlineStr"/>
-      <c r="R296" s="1" t="inlineStr"/>
-      <c r="S296" s="1" t="inlineStr"/>
-      <c r="T296" s="1" t="inlineStr"/>
-      <c r="U296" s="1" t="inlineStr"/>
-      <c r="V296" s="1" t="inlineStr"/>
-      <c r="W296" s="1" t="inlineStr"/>
-      <c r="X296" s="1" t="inlineStr"/>
-      <c r="Y296" s="1" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="1" t="inlineStr"/>
-      <c r="B297" s="1" t="inlineStr"/>
-      <c r="C297" s="1" t="inlineStr"/>
-      <c r="D297" s="1" t="inlineStr"/>
-      <c r="E297" s="1" t="inlineStr"/>
-      <c r="F297" s="1" t="inlineStr"/>
-      <c r="G297" s="1" t="inlineStr"/>
-      <c r="H297" s="1" t="inlineStr"/>
-      <c r="I297" s="1" t="inlineStr"/>
-      <c r="J297" s="1" t="inlineStr"/>
-      <c r="K297" s="1" t="inlineStr">
-        <is>
-          <t>L1006: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bijoutier â€” Horloger</t>
-        </is>
-      </c>
-      <c r="L297" s="1" t="inlineStr"/>
-      <c r="M297" s="1" t="inlineStr"/>
-      <c r="N297" s="1" t="inlineStr"/>
-      <c r="O297" s="1" t="inlineStr"/>
-      <c r="P297" s="1" t="inlineStr"/>
-      <c r="Q297" s="1" t="inlineStr"/>
-      <c r="R297" s="1" t="inlineStr"/>
-      <c r="S297" s="1" t="inlineStr"/>
-      <c r="T297" s="1" t="inlineStr"/>
-      <c r="U297" s="1" t="inlineStr"/>
-      <c r="V297" s="1" t="inlineStr"/>
-      <c r="W297" s="1" t="inlineStr"/>
-      <c r="X297" s="1" t="inlineStr"/>
-      <c r="Y297" s="1" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="1" t="inlineStr"/>
-      <c r="B298" s="1" t="inlineStr"/>
-      <c r="C298" s="1" t="inlineStr"/>
-      <c r="D298" s="1" t="inlineStr"/>
-      <c r="E298" s="1" t="inlineStr"/>
-      <c r="F298" s="1" t="inlineStr"/>
-      <c r="G298" s="1" t="inlineStr"/>
-      <c r="H298" s="1" t="inlineStr"/>
-      <c r="I298" s="1" t="inlineStr"/>
-      <c r="J298" s="1" t="inlineStr"/>
-      <c r="K298" s="1" t="inlineStr">
-        <is>
-          <t>L1015: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: RÃ©parages, Redoublage, Remodelage</t>
-        </is>
-      </c>
-      <c r="L298" s="1" t="inlineStr"/>
-      <c r="M298" s="1" t="inlineStr"/>
-      <c r="N298" s="1" t="inlineStr"/>
-      <c r="O298" s="1" t="inlineStr"/>
-      <c r="P298" s="1" t="inlineStr"/>
-      <c r="Q298" s="1" t="inlineStr"/>
-      <c r="R298" s="1" t="inlineStr"/>
-      <c r="S298" s="1" t="inlineStr"/>
-      <c r="T298" s="1" t="inlineStr"/>
-      <c r="U298" s="1" t="inlineStr"/>
-      <c r="V298" s="1" t="inlineStr"/>
-      <c r="W298" s="1" t="inlineStr"/>
-      <c r="X298" s="1" t="inlineStr"/>
-      <c r="Y298" s="1" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="1" t="inlineStr"/>
-      <c r="B299" s="1" t="inlineStr"/>
-      <c r="C299" s="1" t="inlineStr"/>
-      <c r="D299" s="1" t="inlineStr"/>
-      <c r="E299" s="1" t="inlineStr"/>
-      <c r="F299" s="1" t="inlineStr"/>
-      <c r="G299" s="1" t="inlineStr"/>
-      <c r="H299" s="1" t="inlineStr"/>
-      <c r="I299" s="1" t="inlineStr"/>
-      <c r="J299" s="1" t="inlineStr"/>
-      <c r="K299" s="1" t="inlineStr">
-        <is>
-          <t>L1022: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: TÃ©l. 22213</t>
-        </is>
-      </c>
-      <c r="L299" s="1" t="inlineStr"/>
-      <c r="M299" s="1" t="inlineStr"/>
-      <c r="N299" s="1" t="inlineStr"/>
-      <c r="O299" s="1" t="inlineStr"/>
-      <c r="P299" s="1" t="inlineStr"/>
-      <c r="Q299" s="1" t="inlineStr"/>
-      <c r="R299" s="1" t="inlineStr"/>
-      <c r="S299" s="1" t="inlineStr"/>
-      <c r="T299" s="1" t="inlineStr"/>
-      <c r="U299" s="1" t="inlineStr"/>
-      <c r="V299" s="1" t="inlineStr"/>
-      <c r="W299" s="1" t="inlineStr"/>
-      <c r="X299" s="1" t="inlineStr"/>
-      <c r="Y299" s="1" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="inlineStr"/>
-      <c r="B300" s="1" t="inlineStr"/>
-      <c r="C300" s="1" t="inlineStr"/>
-      <c r="D300" s="1" t="inlineStr"/>
-      <c r="E300" s="1" t="inlineStr"/>
-      <c r="F300" s="1" t="inlineStr"/>
-      <c r="G300" s="1" t="inlineStr"/>
-      <c r="H300" s="1" t="inlineStr"/>
-      <c r="I300" s="1" t="inlineStr"/>
-      <c r="J300" s="1" t="inlineStr"/>
-      <c r="K300" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: 4 Ã©difice Christie Grant-TÃ©l. 28639</t>
-        </is>
-      </c>
-      <c r="L300" s="1" t="inlineStr"/>
-      <c r="M300" s="1" t="inlineStr"/>
-      <c r="N300" s="1" t="inlineStr"/>
-      <c r="O300" s="1" t="inlineStr"/>
-      <c r="P300" s="1" t="inlineStr"/>
-      <c r="Q300" s="1" t="inlineStr"/>
-      <c r="R300" s="1" t="inlineStr"/>
-      <c r="S300" s="1" t="inlineStr"/>
-      <c r="T300" s="1" t="inlineStr"/>
-      <c r="U300" s="1" t="inlineStr"/>
-      <c r="V300" s="1" t="inlineStr"/>
-      <c r="W300" s="1" t="inlineStr"/>
-      <c r="X300" s="1" t="inlineStr"/>
-      <c r="Y300" s="1" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="inlineStr"/>
-      <c r="B301" s="1" t="inlineStr"/>
-      <c r="C301" s="1" t="inlineStr"/>
-      <c r="D301" s="1" t="inlineStr"/>
-      <c r="E301" s="1" t="inlineStr"/>
-      <c r="F301" s="1" t="inlineStr"/>
-      <c r="G301" s="1" t="inlineStr"/>
-      <c r="H301" s="1" t="inlineStr"/>
-      <c r="I301" s="1" t="inlineStr"/>
-      <c r="J301" s="1" t="inlineStr"/>
-      <c r="K301" s="1" t="inlineStr">
-        <is>
-          <t>L1031: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: EATONâ€™S</t>
-        </is>
-      </c>
-      <c r="L301" s="1" t="inlineStr"/>
-      <c r="M301" s="1" t="inlineStr"/>
-      <c r="N301" s="1" t="inlineStr"/>
-      <c r="O301" s="1" t="inlineStr"/>
-      <c r="P301" s="1" t="inlineStr"/>
-      <c r="Q301" s="1" t="inlineStr"/>
-      <c r="R301" s="1" t="inlineStr"/>
-      <c r="S301" s="1" t="inlineStr"/>
-      <c r="T301" s="1" t="inlineStr"/>
-      <c r="U301" s="1" t="inlineStr"/>
-      <c r="V301" s="1" t="inlineStr"/>
-      <c r="W301" s="1" t="inlineStr"/>
-      <c r="X301" s="1" t="inlineStr"/>
-      <c r="Y301" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
